--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FD8CE5-042B-426D-8D11-F3472D0A6531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8EFC03-C3AC-41E3-B9A5-94370CBC47BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="219">
   <si>
     <t>type</t>
   </si>
@@ -1518,272 +1518,277 @@
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="2" t="b">
+      <c r="B4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C5" s="12"/>
+      <c r="D5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="2"/>
-      <c r="N7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R7"/>
-      <c r="S7"/>
-      <c r="W7" s="2" t="b">
-        <v>1</v>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="G8" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="8"/>
+      <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C9" s="12"/>
+      <c r="D9" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C10" s="12"/>
       <c r="D10" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" s="2" t="b">
+        <v>62</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C11" s="12"/>
-      <c r="D11" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="C13" s="12"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C14" s="12"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
     </row>
-    <row r="15" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="2" t="b">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="D17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="26"/>
+      <c r="K17" s="2"/>
+      <c r="N17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="W17" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C16" s="12"/>
-      <c r="D16" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C18" s="13"/>
-      <c r="D18" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>59</v>
-      </c>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="G18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C19" s="12"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C20" s="12"/>
       <c r="D20" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="31.5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="L20" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C21" s="12"/>
       <c r="D21" s="13" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="13" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="12"/>
+      <c r="D22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" s="12"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
-        <v>63</v>
-      </c>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C24" s="12"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
       <c r="D26" s="13" t="s">
         <v>10</v>
       </c>
@@ -1797,7 +1802,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
       <c r="D27" s="13" t="s">
         <v>117</v>
       </c>
@@ -1808,9 +1813,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C28" s="12"/>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E28"/>
@@ -1821,7 +1826,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C29" s="13"/>
       <c r="D29" s="13" t="s">
         <v>10</v>
@@ -1836,7 +1841,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C30" s="12"/>
       <c r="D30" s="13" t="s">
         <v>117</v>
@@ -1849,7 +1854,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C31" s="13"/>
       <c r="D31" s="13" t="s">
         <v>10</v>
@@ -1864,7 +1869,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C32" s="12"/>
       <c r="D32" s="13" t="s">
         <v>10</v>
@@ -1898,6 +1903,9 @@
       <c r="S33"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="C34" s="12"/>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8EFC03-C3AC-41E3-B9A5-94370CBC47BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6EB25E-550D-47CF-A84B-9F33D266AC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="223">
   <si>
     <t>type</t>
   </si>
@@ -344,9 +344,6 @@
     <t>comentario_2</t>
   </si>
   <si>
-    <t>Introduza o numero se serie do cartao</t>
-  </si>
-  <si>
     <t>idade_mes</t>
   </si>
   <si>
@@ -374,12 +371,6 @@
     <t>display.adate.toYear</t>
   </si>
   <si>
-    <t>texto_display</t>
-  </si>
-  <si>
-    <t>calculates.idade_mes()&lt;3 ? ("Menor que 3 meses") : calculates.idade_mes()&gt;59 ? ("Maior de 59 meses") : ("")</t>
-  </si>
-  <si>
     <t>Consulta</t>
   </si>
   <si>
@@ -711,6 +702,27 @@
   </si>
   <si>
     <t>resultado_tdr</t>
+  </si>
+  <si>
+    <t>chill_adult</t>
+  </si>
+  <si>
+    <t>calculates.idade_mes()&lt;216 ? "C" : "A"</t>
+  </si>
+  <si>
+    <t>letra_codigo</t>
+  </si>
+  <si>
+    <t>Centro de saude:</t>
+  </si>
+  <si>
+    <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
+  </si>
+  <si>
+    <t>cs</t>
+  </si>
+  <si>
+    <t>concat(data('cs') , calculates.chill_adult())</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1371,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1375,7 +1387,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,7 +1395,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1399,7 +1411,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y104"/>
+  <dimension ref="A1:Y105"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1464,10 +1476,10 @@
         <v>35</v>
       </c>
       <c r="O1" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="P1" s="22" t="s">
         <v>104</v>
-      </c>
-      <c r="P1" s="22" t="s">
-        <v>105</v>
       </c>
       <c r="Q1" t="s">
         <v>36</v>
@@ -1507,7 +1519,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="13"/>
@@ -1517,13 +1529,15 @@
       <c r="J3" s="1"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="E4" s="13"/>
+    <row r="4" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="13"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C5" s="12"/>
@@ -1531,113 +1545,107 @@
         <v>10</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="G5" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="2" t="b">
+      <c r="L6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C7" s="13"/>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13" t="s">
+      <c r="E8" s="13"/>
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+      <c r="L8" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C9" s="12"/>
-      <c r="D9" s="13" t="s">
-        <v>5</v>
-      </c>
       <c r="E9" s="13"/>
-      <c r="F9" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C10" s="12"/>
       <c r="D10" s="13" t="s">
         <v>5</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C11" s="12"/>
+      <c r="D11" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L10" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="2" t="b">
-        <v>1</v>
+      <c r="L11" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -1649,29 +1657,33 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="5"/>
+      <c r="C15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
@@ -1682,309 +1694,313 @@
       <c r="J16" s="3"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="D17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J17" s="26"/>
-      <c r="K17" s="2"/>
-      <c r="N17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R17"/>
-      <c r="S17"/>
-      <c r="W17" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="11"/>
-      <c r="G18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="C19" s="12"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-    </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C20" s="12"/>
-      <c r="D20" s="13" t="s">
-        <v>4</v>
-      </c>
       <c r="E20" s="13"/>
-      <c r="F20" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L20" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C21" s="12"/>
       <c r="D21" s="13" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="13" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="L21" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C22" s="12"/>
       <c r="D22" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="12"/>
+      <c r="D23" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G23" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L22" s="2" t="b">
+      <c r="L23" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C24" s="12"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="D26" s="13" t="s">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D27" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F27" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D28" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="D27" s="13" t="s">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C29" s="12"/>
+      <c r="D29" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29"/>
+      <c r="F29" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C30" s="13"/>
+      <c r="D30" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="G30" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G27" s="2" t="s">
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C31" s="12"/>
+      <c r="D31" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="C28" s="12"/>
-      <c r="D28" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28"/>
-      <c r="F28" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="C29" s="13"/>
-      <c r="D29" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="13" t="s">
+      <c r="G31" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="C30" s="12"/>
-      <c r="D30" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="C31" s="13"/>
-      <c r="D31" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="C32" s="12"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C32" s="13"/>
       <c r="D32" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C33" s="12"/>
+      <c r="D33" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="13" t="s">
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J33" s="7"/>
-      <c r="K33" s="2"/>
-      <c r="R33"/>
-      <c r="S33"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
+      <c r="J34" s="7"/>
+      <c r="K34" s="2"/>
+      <c r="R34"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C34" s="12"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35"/>
-      <c r="B35" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C35" s="12"/>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D36" s="13" t="s">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+      <c r="B36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D37" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="D37" s="13" t="s">
+      <c r="F37" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+      <c r="D38" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
+      <c r="E38" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C39" s="12"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="13"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C40" s="12"/>
       <c r="E40" s="14"/>
       <c r="F40" s="13"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C41" s="12"/>
-      <c r="D41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="H41"/>
-      <c r="I41"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D45" s="13" t="s">
+      <c r="E41" s="14"/>
+      <c r="F41" s="13"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C42" s="12"/>
+      <c r="D42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="H42"/>
+      <c r="I42"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D46" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F46" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C48" s="13"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="13"/>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D48" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J48" s="26"/>
+      <c r="K48" s="2"/>
+      <c r="N48" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="R48"/>
+      <c r="S48"/>
+      <c r="W48" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="12"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="11"/>
+      <c r="G49" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="8"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C50" s="12"/>
-      <c r="E50" s="14"/>
+      <c r="E50" s="13"/>
       <c r="F50" s="13"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
@@ -2013,13 +2029,13 @@
       <c r="F55" s="13"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C56" s="13"/>
+      <c r="C56" s="12"/>
       <c r="E56" s="14"/>
       <c r="F56" s="13"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C57" s="12"/>
-      <c r="E57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="E57" s="14"/>
       <c r="F57" s="13"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
@@ -2028,13 +2044,9 @@
       <c r="F58" s="13"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
+      <c r="C59" s="12"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="14"/>
@@ -2044,7 +2056,6 @@
       <c r="F60" s="17"/>
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
-      <c r="K60" s="6"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="14"/>
@@ -2064,6 +2075,7 @@
       <c r="F62" s="17"/>
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
+      <c r="K62" s="6"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="14"/>
@@ -2102,12 +2114,12 @@
       <c r="H66" s="14"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="27"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="14"/>
       <c r="H67" s="14"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
@@ -2120,12 +2132,12 @@
       <c r="H68" s="14"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="17"/>
-      <c r="G69" s="14"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="27"/>
       <c r="H69" s="14"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
@@ -2183,9 +2195,13 @@
       <c r="H75" s="14"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="13"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="17"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D77" s="12"/>
@@ -2327,15 +2343,20 @@
       <c r="E104" s="12"/>
       <c r="F104" s="13"/>
     </row>
+    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="13"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:F69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2394,7 +2415,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2405,7 +2426,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2446,101 +2467,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2610,332 +2631,332 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3412,16 +3433,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
         <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
         <v>88</v>
@@ -3430,7 +3451,7 @@
         <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H5" s="24" t="s">
         <v>87</v>
@@ -3505,7 +3526,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02CAEF6-746F-4DFF-99B1-6DB036574858}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -3522,34 +3543,42 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
         <v>101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>107</v>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3585,10 +3614,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3620,7 +3649,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3652,15 +3681,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3668,7 +3697,7 @@
         <v>71</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3676,15 +3705,15 @@
         <v>10</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3692,7 +3721,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3700,7 +3729,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3708,7 +3737,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3716,7 +3745,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3724,31 +3753,39 @@
         <v>10</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>132</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6EB25E-550D-47CF-A84B-9F33D266AC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED84421-A753-4AAC-B45B-9952280D67EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="215">
   <si>
     <t>type</t>
   </si>
@@ -126,15 +126,6 @@
     <t>mes</t>
   </si>
   <si>
-    <t>region_csv</t>
-  </si>
-  <si>
-    <t>sector_csv</t>
-  </si>
-  <si>
-    <t>local_csv</t>
-  </si>
-  <si>
     <t>choice_filter</t>
   </si>
   <si>
@@ -165,26 +156,6 @@
     <t>hideInContents</t>
   </si>
   <si>
-    <t>csv</t>
-  </si>
-  <si>
-    <t>_.chain(context)
-.uniq(function(x){return x.sector;})
-.map(function(place){
-    return {
-        data_value:place.sector, 
-        region: place.region,
-        display:{title: {text: place.sector} }
-    } 
-    })
-.value()</t>
-  </si>
-  <si>
-    <t>_.chain(context).pluck('region').uniq().map(function(region){
-return {data_value:region, display:{title: {text: region} } };
-}).value()</t>
-  </si>
-  <si>
     <t>callback</t>
   </si>
   <si>
@@ -197,9 +168,6 @@
     <t>query_name</t>
   </si>
   <si>
-    <t>"tabancas.csv"</t>
-  </si>
-  <si>
     <t>Idade ou data de nascimento?</t>
   </si>
   <si>
@@ -317,18 +285,6 @@
     <t>[data('id_paciente')]</t>
   </si>
   <si>
-    <t>_.chain(context)
-.map(function(place){
-    return {
-        data_value:place.tabanca, 
-        region: place.region,
-        sector: place.sector,
-               display:{title: {text: place.tabanca} }
-    } 
-    })
-.value()</t>
-  </si>
-  <si>
     <t>data('mes')&lt;12</t>
   </si>
   <si>
@@ -638,9 +594,6 @@
     <t>Doencas inflamatorias pelvicas</t>
   </si>
   <si>
-    <t>CS</t>
-  </si>
-  <si>
     <t>Buba</t>
   </si>
   <si>
@@ -662,9 +615,6 @@
     <t>SH</t>
   </si>
   <si>
-    <t>SG</t>
-  </si>
-  <si>
     <t>SBM</t>
   </si>
   <si>
@@ -710,26 +660,32 @@
     <t>calculates.idade_mes()&lt;216 ? "C" : "A"</t>
   </si>
   <si>
-    <t>letra_codigo</t>
-  </si>
-  <si>
     <t>Centro de saude:</t>
   </si>
   <si>
     <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
   </si>
   <si>
-    <t>cs</t>
-  </si>
-  <si>
-    <t>concat(data('cs') , calculates.chill_adult())</t>
+    <t>SGC</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>select_one_dropdown</t>
+  </si>
+  <si>
+    <t>centro</t>
+  </si>
+  <si>
+    <t>ccc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -766,12 +722,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -854,7 +804,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -907,16 +857,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1371,7 +1318,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1387,7 +1334,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1395,7 +1342,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1417,7 +1364,7 @@
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="25.375" style="13" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="12" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
@@ -1434,7 +1381,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
@@ -1454,8 +1401,8 @@
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="19" t="s">
-        <v>33</v>
+      <c r="H1" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="I1" t="s">
         <v>21</v>
@@ -1470,37 +1417,37 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="P1" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>36</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>37</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>38</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" t="s">
-        <v>42</v>
       </c>
       <c r="X1" t="s">
         <v>19</v>
@@ -1542,16 +1489,16 @@
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C5" s="12"/>
       <c r="D5" s="13" t="s">
-        <v>10</v>
+        <v>212</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1560,13 +1507,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>1</v>
@@ -1574,10 +1521,10 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
@@ -1586,7 +1533,7 @@
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C8" s="13"/>
       <c r="D8" s="13" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13" t="s">
@@ -1596,12 +1543,12 @@
         <v>26</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C9" s="12"/>
       <c r="E9" s="13"/>
@@ -1617,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
@@ -1636,21 +1583,21 @@
         <v>29</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C13" s="12"/>
       <c r="E13" s="13"/>
@@ -1664,10 +1611,10 @@
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="11" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -1696,7 +1643,7 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="11"/>
@@ -1723,7 +1670,7 @@
         <v>23</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>1</v>
@@ -1732,14 +1679,14 @@
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C22" s="12"/>
       <c r="D22" s="13" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1762,7 +1709,7 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C24" s="12"/>
       <c r="E24" s="13"/>
@@ -1775,7 +1722,7 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
@@ -1783,37 +1730,37 @@
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D28" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C29" s="12"/>
       <c r="D29" s="10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E29"/>
-      <c r="F29" s="20" t="s">
-        <v>110</v>
+      <c r="F29" s="19" t="s">
+        <v>102</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
@@ -1822,26 +1769,26 @@
         <v>10</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C31" s="12"/>
       <c r="D31" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="13" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
@@ -1850,13 +1797,13 @@
         <v>10</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
@@ -1865,13 +1812,13 @@
         <v>10</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -1879,13 +1826,13 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="2"/>
@@ -1894,7 +1841,7 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C35" s="12"/>
       <c r="E35" s="13"/>
@@ -1903,7 +1850,7 @@
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="B36" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C36" s="12"/>
       <c r="E36" s="13"/>
@@ -1911,27 +1858,27 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D37" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="13" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
@@ -1956,26 +1903,26 @@
         <v>4</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D48" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J48" s="26"/>
+        <v>94</v>
+      </c>
+      <c r="J48" s="25"/>
       <c r="K48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="R48"/>
       <c r="S48"/>
@@ -1987,11 +1934,11 @@
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E49" s="11"/>
       <c r="G49" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -2123,21 +2070,21 @@
       <c r="H67" s="14"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="27"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="26"/>
       <c r="H68" s="14"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="27"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="26"/>
       <c r="H69" s="14"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
@@ -2371,7 +2318,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr defaultColWidth="21.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.75" style="2" customWidth="1"/>
@@ -2399,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2410,12 +2357,12 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2426,13 +2373,13 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2441,24 +2388,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2467,506 +2414,517 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+      <c r="A23" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="A24" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
+      <c r="A25" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
+      <c r="A26" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
+      <c r="A27" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="A28" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
+      <c r="A29" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="A30" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+      <c r="A31" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
+      <c r="A32" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
+      <c r="A33" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
+      <c r="A34" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="C35" s="1"/>
+      <c r="A35" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="C36" s="1"/>
+      <c r="A36" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="A37" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
+      <c r="A38" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="A39" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="C40" s="1"/>
+      <c r="A40" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>130</v>
+        <v>163</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>131</v>
+        <v>165</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>133</v>
+        <v>169</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="A52" s="1"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>159</v>
-      </c>
+      <c r="A53" s="1"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="A54" s="1"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="A55" s="1"/>
+      <c r="C55" s="1"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="A56" s="1"/>
+      <c r="C56" s="1"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>167</v>
-      </c>
+      <c r="A57" s="1"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>193</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="C58" s="1"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>170</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="C59" s="1"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="C60" s="1"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="A61" s="1"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>176</v>
-      </c>
+      <c r="A62" s="1"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>178</v>
-      </c>
+      <c r="A63" s="1"/>
+      <c r="C63" s="1"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>180</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="C64" s="1"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>182</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="C65" s="1"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="A66" s="1"/>
+      <c r="C66" s="1"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>186</v>
-      </c>
+      <c r="A67" s="1"/>
+      <c r="C67" s="1"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>188</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="C68" s="1"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>190</v>
-      </c>
+      <c r="A69" s="1"/>
+      <c r="C69" s="1"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="A70" s="1"/>
+      <c r="C70" s="1"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
+      <c r="C71" s="1"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
+      <c r="C72" s="1"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
+      <c r="C73" s="1"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
@@ -2978,6 +2936,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
+      <c r="C76" s="1"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
@@ -2993,9 +2952,11 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
+      <c r="C80" s="1"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
+      <c r="C81" s="1"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
@@ -3151,82 +3112,82 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
-      <c r="C120" s="1"/>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="1"/>
-      <c r="C121" s="1"/>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="1"/>
-      <c r="C122" s="1"/>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="1"/>
-      <c r="C123" s="1"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
-      <c r="C124" s="1"/>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
-      <c r="C125" s="1"/>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="1"/>
-      <c r="C126" s="1"/>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="1"/>
-      <c r="C127" s="1"/>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="1"/>
-      <c r="C128" s="1"/>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="1"/>
-      <c r="C129" s="1"/>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="1"/>
-      <c r="C130" s="1"/>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="1"/>
-      <c r="C131" s="1"/>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="1"/>
-      <c r="C132" s="1"/>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="1"/>
-      <c r="C133" s="1"/>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="1"/>
-      <c r="C134" s="1"/>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="1"/>
-      <c r="C135" s="1"/>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="1"/>
-      <c r="C136" s="1"/>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="1"/>
-      <c r="C137" s="1"/>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="1"/>
-      <c r="C138" s="1"/>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="1"/>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="1"/>
+      <c r="C196" s="1"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="1"/>
+      <c r="C197" s="1"/>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="1"/>
+      <c r="C198" s="1"/>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="1"/>
+      <c r="C199" s="1"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="1"/>
+      <c r="C200" s="1"/>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="1"/>
+      <c r="C201" s="1"/>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="1"/>
+      <c r="C202" s="1"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="1"/>
+      <c r="C203" s="1"/>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="1"/>
+      <c r="C204" s="1"/>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="1"/>
+      <c r="C205" s="1"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="1"/>
+      <c r="C206" s="1"/>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="1"/>
+      <c r="C207" s="1"/>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="1"/>
+      <c r="C208" s="1"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="1"/>
+      <c r="C209" s="1"/>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="1"/>
+      <c r="C210" s="1"/>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="1"/>
+      <c r="C211" s="1"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="1"/>
+      <c r="C212" s="1"/>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="1"/>
+      <c r="C213" s="1"/>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="1"/>
+      <c r="C214" s="1"/>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
@@ -3247,82 +3208,6 @@
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="C219" s="1"/>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="1"/>
-      <c r="C220" s="1"/>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="1"/>
-      <c r="C221" s="1"/>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="1"/>
-      <c r="C222" s="1"/>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="1"/>
-      <c r="C223" s="1"/>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="1"/>
-      <c r="C224" s="1"/>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="1"/>
-      <c r="C225" s="1"/>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="1"/>
-      <c r="C226" s="1"/>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="1"/>
-      <c r="C227" s="1"/>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="1"/>
-      <c r="C228" s="1"/>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="1"/>
-      <c r="C229" s="1"/>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="1"/>
-      <c r="C230" s="1"/>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="1"/>
-      <c r="C231" s="1"/>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="1"/>
-      <c r="C232" s="1"/>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="1"/>
-      <c r="C233" s="1"/>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="1"/>
-      <c r="C234" s="1"/>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="1"/>
-      <c r="C235" s="1"/>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="1"/>
-      <c r="C236" s="1"/>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="1"/>
-      <c r="C237" s="1"/>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="1"/>
-      <c r="C238" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3338,7 +3223,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C574FB-861C-4A83-BA50-230986D05032}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
@@ -3353,112 +3238,69 @@
     <col min="11" max="11" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="25" t="s">
+    <row r="1" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H2" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="J2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" t="s">
-        <v>205</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H6" s="24"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3477,46 +3319,46 @@
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="22" t="s">
+    <row r="1" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>70</v>
+      <c r="C1" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
         <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3526,7 +3368,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02CAEF6-746F-4DFF-99B1-6DB036574858}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -3535,50 +3377,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3597,27 +3431,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3630,10 +3464,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3649,12 +3483,12 @@
         <v>10</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>27</v>
@@ -3681,23 +3515,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>110</v>
+      <c r="A13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3705,15 +3539,15 @@
         <v>10</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3721,7 +3555,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3729,7 +3563,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3737,7 +3571,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3745,7 +3579,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3753,7 +3587,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3761,31 +3595,31 @@
         <v>10</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED84421-A753-4AAC-B45B-9952280D67EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42FADA0-C81E-4153-AC10-E81C007C7A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="214">
   <si>
     <t>type</t>
   </si>
@@ -672,13 +672,10 @@
     <t>SGH</t>
   </si>
   <si>
-    <t>select_one_dropdown</t>
-  </si>
-  <si>
     <t>centro</t>
   </si>
   <si>
-    <t>ccc</t>
+    <t>cs</t>
   </si>
 </sst>
 </file>
@@ -1489,13 +1486,13 @@
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C5" s="12"/>
       <c r="D5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>213</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>214</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>208</v>
@@ -2458,7 +2455,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>191</v>
@@ -2469,7 +2466,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>192</v>
@@ -2480,7 +2477,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>210</v>
@@ -2491,7 +2488,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>211</v>
@@ -2502,7 +2499,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>193</v>
@@ -3595,7 +3592,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42FADA0-C81E-4153-AC10-E81C007C7A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14DA56B-7FCD-4DF1-98C3-1309CCEF4C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="216">
   <si>
     <t>type</t>
   </si>
@@ -648,9 +648,6 @@
     <t>data('DOB_idade')=='2'</t>
   </si>
   <si>
-    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : sc.getMonths(data('ano'), data('mes'))</t>
-  </si>
-  <si>
     <t>resultado_tdr</t>
   </si>
   <si>
@@ -676,6 +673,15 @@
   </si>
   <si>
     <t>cs</t>
+  </si>
+  <si>
+    <t>letra_codigo</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : adate.getMonths(data('ano'), data('mes'))</t>
+  </si>
+  <si>
+    <t>data('cs') + calculates.chill_adult()</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1361,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y105"/>
+  <dimension ref="A1:Y98"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1484,194 +1490,210 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C5" s="12"/>
-      <c r="D5" s="13" t="s">
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" s="25"/>
+      <c r="K6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="W6" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="G7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C8" s="12"/>
+      <c r="D8" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E8" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C6" s="12"/>
-      <c r="D6" s="13" t="s">
+      <c r="G8" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C9" s="12"/>
+      <c r="D9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E9" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G9" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="2" t="b">
+      <c r="L9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C10" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C8" s="13"/>
-      <c r="D8" s="13" t="s">
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13" t="s">
         <v>70</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="12"/>
-      <c r="D10" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C11" s="12"/>
-      <c r="D11" s="13" t="s">
-        <v>5</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C13" s="12"/>
+      <c r="D13" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C14" s="12"/>
+      <c r="D14" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L14" s="12" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="5"/>
+      <c r="C16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-      <c r="D21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L21" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C22" s="12"/>
@@ -1680,131 +1702,132 @@
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C23" s="12"/>
       <c r="D23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="12"/>
+      <c r="D24" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E24" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F24" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G24" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L23" s="2" t="b">
+      <c r="L24" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C25" s="12"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D27" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D28" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D29" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F29" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C29" s="12"/>
-      <c r="D29" s="10" t="s">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C30" s="12"/>
+      <c r="D30" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E29"/>
-      <c r="F29" s="19" t="s">
+      <c r="E30"/>
+      <c r="F30" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G30" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="13"/>
-      <c r="D30" s="13" t="s">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C31" s="13"/>
+      <c r="D31" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E31" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F31" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C31" s="12"/>
-      <c r="D31" s="13" t="s">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C32" s="12"/>
+      <c r="D32" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13" t="s">
+      <c r="E32" s="13"/>
+      <c r="F32" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C32" s="13"/>
-      <c r="D32" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C33" s="12"/>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C33" s="13"/>
       <c r="D33" s="13" t="s">
         <v>10</v>
       </c>
@@ -1812,185 +1835,217 @@
         <v>113</v>
       </c>
       <c r="F33" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C34" s="12"/>
+      <c r="D34" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="D34" s="2" t="s">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="J34" s="7"/>
-      <c r="K34" s="2"/>
-      <c r="R34"/>
-      <c r="S34"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
+      <c r="J35" s="7"/>
+      <c r="K35" s="2"/>
+      <c r="R35"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C35" s="12"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36"/>
-      <c r="B36" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C36" s="12"/>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="D37" s="13" t="s">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="B37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="12"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D38" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F38" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-      <c r="D38" s="13" t="s">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="D39" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C40" s="12"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="13"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C41" s="12"/>
       <c r="E41" s="14"/>
       <c r="F41" s="13"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C42" s="12"/>
-      <c r="D42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="H42"/>
-      <c r="I42"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="D46" s="13" t="s">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D42" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F42" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="D48" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J48" s="25"/>
-      <c r="K48" s="2"/>
-      <c r="N48" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="R48"/>
-      <c r="S48"/>
-      <c r="W48" s="2" t="b">
-        <v>1</v>
-      </c>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C43" s="12"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C44" s="12"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C45" s="12"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="13"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C46" s="12"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="13"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C47" s="12"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="13"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C48" s="12"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="13"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" s="11"/>
-      <c r="G49" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="8"/>
+      <c r="C49" s="12"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="13"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="12"/>
-      <c r="E50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="E50" s="14"/>
       <c r="F50" s="13"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C51" s="12"/>
-      <c r="E51" s="14"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="13"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C52" s="12"/>
-      <c r="E52" s="14"/>
+      <c r="E52" s="13"/>
       <c r="F52" s="13"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C53" s="12"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="16"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="13"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C54" s="12"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="16"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="13"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="K54" s="6"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C55" s="12"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="16"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="13"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="K55" s="6"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C56" s="12"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="16"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="13"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C57" s="13"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="16"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="13"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C58" s="12"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C59" s="12"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="14"/>
@@ -2002,24 +2057,22 @@
       <c r="H60" s="14"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="14"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="26"/>
       <c r="H61" s="14"/>
-      <c r="K61" s="6"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="14"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="26"/>
       <c r="H62" s="14"/>
-      <c r="K62" s="6"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="14"/>
@@ -2067,85 +2120,57 @@
       <c r="H67" s="14"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="27"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="26"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="14"/>
       <c r="H68" s="14"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="26"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="14"/>
       <c r="H69" s="14"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="17"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="13"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="13"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="13"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="17"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="13"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="17"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="13"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="17"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="13"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="17"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="13"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D77" s="12"/>
@@ -2257,50 +2282,15 @@
       <c r="E98" s="12"/>
       <c r="F98" s="13"/>
     </row>
-    <row r="99" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="12"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="13"/>
-    </row>
-    <row r="100" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="12"/>
-      <c r="E100" s="12"/>
-      <c r="F100" s="13"/>
-    </row>
-    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="12"/>
-      <c r="E101" s="12"/>
-      <c r="F101" s="13"/>
-    </row>
-    <row r="102" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D102" s="12"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="13"/>
-    </row>
-    <row r="103" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D103" s="12"/>
-      <c r="E103" s="12"/>
-      <c r="F103" s="13"/>
-    </row>
-    <row r="104" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D104" s="12"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="13"/>
-    </row>
-    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D105" s="12"/>
-      <c r="E105" s="12"/>
-      <c r="F105" s="13"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G61:G62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2411,7 +2401,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -2422,7 +2412,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -2433,7 +2423,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
@@ -2444,7 +2434,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
@@ -2455,7 +2445,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>191</v>
@@ -2466,7 +2456,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>192</v>
@@ -2477,10 +2467,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>188</v>
@@ -2488,10 +2478,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>189</v>
@@ -2499,7 +2489,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>193</v>
@@ -3365,7 +3355,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02CAEF6-746F-4DFF-99B1-6DB036574858}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -3401,15 +3391,23 @@
         <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>207</v>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3437,7 +3435,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>59</v>
@@ -3453,7 +3451,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>23</v>
@@ -3592,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14DA56B-7FCD-4DF1-98C3-1309CCEF4C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80035136-5A77-44F7-B589-0E6812F61A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="221">
   <si>
     <t>type</t>
   </si>
@@ -297,9 +297,6 @@
     <t>Comentário</t>
   </si>
   <si>
-    <t>comentario_2</t>
-  </si>
-  <si>
     <t>idade_mes</t>
   </si>
   <si>
@@ -318,9 +315,6 @@
     <t>adate.display(calculates.hoje())</t>
   </si>
   <si>
-    <t>Data:</t>
-  </si>
-  <si>
     <t>display.adate.fromYear</t>
   </si>
   <si>
@@ -682,6 +676,27 @@
   </si>
   <si>
     <t>data('cs') + calculates.chill_adult()</t>
+  </si>
+  <si>
+    <t>id_formssentinela</t>
+  </si>
+  <si>
+    <t>data('temperatura')&lt;46 &amp; data('temperatura')&gt;32</t>
+  </si>
+  <si>
+    <t>data('peso')&lt;200</t>
+  </si>
+  <si>
+    <t>select_one_dropdown</t>
+  </si>
+  <si>
+    <t>data('sexo')=='2' &amp;&amp; (calculates.idade_mes()&lt;=660 &amp;&amp; calculates.idade_mes()&gt;=144)</t>
+  </si>
+  <si>
+    <t>comentario</t>
+  </si>
+  <si>
+    <t>comentario_1</t>
   </si>
 </sst>
 </file>
@@ -807,7 +822,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -828,9 +843,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1321,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1337,7 +1349,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1345,7 +1357,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1367,9 +1379,9 @@
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="25.375" style="12" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.75" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.75" style="11" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.125" style="2" customWidth="1"/>
     <col min="9" max="9" width="29.75" style="2" customWidth="1"/>
@@ -1392,19 +1404,19 @@
       <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>30</v>
       </c>
       <c r="I1" t="s">
@@ -1425,11 +1437,11 @@
       <c r="N1" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="P1" s="21" t="s">
-        <v>96</v>
+      <c r="O1" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="Q1" t="s">
         <v>33</v>
@@ -1460,9 +1472,9 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="13"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="12"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1470,9 +1482,9 @@
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="13"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="12"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1480,9 +1492,9 @@
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="13"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1496,18 +1508,18 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J6" s="25"/>
+        <v>88</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J6" s="24"/>
       <c r="K6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R6"/>
       <c r="S6"/>
@@ -1516,162 +1528,161 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="G7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="8"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C8" s="12"/>
-      <c r="D8" s="13" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>207</v>
+      <c r="E8" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C9" s="12"/>
-      <c r="D9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="B9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C12" s="11"/>
+      <c r="D12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F9" s="13" t="s">
+    </row>
+    <row r="13" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C13" s="11"/>
+      <c r="D13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C11" s="13"/>
-      <c r="D11" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C13" s="12"/>
-      <c r="D13" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C14" s="12"/>
-      <c r="D14" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>203</v>
-      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+        <v>56</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="C17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11" t="s">
+      <c r="E19" s="9"/>
+      <c r="F19" s="10" t="s">
         <v>59</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -1682,178 +1693,183 @@
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C22" s="12"/>
-      <c r="D22" s="13" t="s">
+      <c r="C20" s="11"/>
+      <c r="D20" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13" t="s">
+      <c r="E20" s="12"/>
+      <c r="F20" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="L20" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C21" s="11"/>
+      <c r="D21" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="11"/>
+      <c r="D22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C23" s="12"/>
-      <c r="D23" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="12"/>
-      <c r="D24" s="13" t="s">
+    <row r="23" spans="2:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D24" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="2" t="b">
-        <v>1</v>
+      <c r="E24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C26" s="12"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
+      <c r="C26" s="11"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="11"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D28" s="13" t="s">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D29" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C30" s="11"/>
+      <c r="D30" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E31" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F31" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C32" s="11"/>
+      <c r="D32" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D29" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="12"/>
-      <c r="D30" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30"/>
-      <c r="F30" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="G30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C31" s="13"/>
-      <c r="D31" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="13" t="s">
+      <c r="E32" s="12"/>
+      <c r="F32" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C32" s="12"/>
-      <c r="D32" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13" t="s">
+      <c r="J32" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C33" s="12"/>
+      <c r="D33" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="F33" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C33" s="13"/>
-      <c r="D33" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="13" t="s">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C34" s="11"/>
+      <c r="D34" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C34" s="12"/>
-      <c r="D34" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -1864,10 +1880,10 @@
         <v>48</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="2"/>
@@ -1878,37 +1894,37 @@
       <c r="B36" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
+      <c r="C36" s="11"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="B37" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="12"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
+      <c r="C37" s="11"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="12" t="s">
-        <v>196</v>
+      <c r="F38" s="11" t="s">
+        <v>194</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39"/>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="12" t="s">
         <v>79</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -1917,370 +1933,370 @@
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C41" s="12"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="13"/>
+      <c r="C41" s="11"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="12"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>87</v>
+      <c r="F42" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C43" s="12"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="C43" s="11"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C44" s="12"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="13"/>
+      <c r="C44" s="11"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="12"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C45" s="12"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="13"/>
+      <c r="C45" s="11"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="12"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C46" s="12"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="13"/>
+      <c r="C46" s="11"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C47" s="12"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="13"/>
+      <c r="C47" s="11"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="12"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C48" s="12"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="13"/>
+      <c r="C48" s="11"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="12"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="12"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="13"/>
+      <c r="C49" s="11"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="12"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="13"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="13"/>
+      <c r="C50" s="12"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="12"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C51" s="12"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
+      <c r="C51" s="11"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C52" s="12"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
+      <c r="C52" s="11"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
       <c r="K54" s="6"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
       <c r="K55" s="6"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="14"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="13"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="14"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="13"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="17"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="17"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="17"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="13"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="12"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="13"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="12"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="13"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="12"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="13"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="12"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D74" s="12"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="13"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="12"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="13"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="12"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="13"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="12"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="13"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="12"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="13"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="12"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="13"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="12"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="13"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="12"/>
     </row>
     <row r="81" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="13"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="12"/>
     </row>
     <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="13"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="12"/>
     </row>
     <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="13"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="12"/>
     </row>
     <row r="84" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="13"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="12"/>
     </row>
     <row r="85" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="13"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="12"/>
     </row>
     <row r="86" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="13"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="12"/>
     </row>
     <row r="87" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="13"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="12"/>
     </row>
     <row r="88" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="13"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="12"/>
     </row>
     <row r="89" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D89" s="12"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="13"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="12"/>
     </row>
     <row r="90" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="13"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="12"/>
     </row>
     <row r="91" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D91" s="12"/>
-      <c r="E91" s="12"/>
-      <c r="F91" s="13"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="12"/>
     </row>
     <row r="92" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D92" s="12"/>
-      <c r="E92" s="12"/>
-      <c r="F92" s="13"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="12"/>
     </row>
     <row r="93" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D93" s="12"/>
-      <c r="E93" s="12"/>
-      <c r="F93" s="13"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="12"/>
     </row>
     <row r="94" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="12"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="13"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="12"/>
     </row>
     <row r="95" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="12"/>
-      <c r="E95" s="12"/>
-      <c r="F95" s="13"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="12"/>
     </row>
     <row r="96" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="12"/>
-      <c r="E96" s="12"/>
-      <c r="F96" s="13"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="12"/>
     </row>
     <row r="97" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="12"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="13"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="12"/>
     </row>
     <row r="98" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="12"/>
-      <c r="E98" s="12"/>
-      <c r="F98" s="13"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2349,7 +2365,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2360,7 +2376,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2400,435 +2416,435 @@
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>204</v>
+      <c r="A11" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>204</v>
+      <c r="A12" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>204</v>
+      <c r="A13" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>204</v>
+      <c r="A14" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>113</v>
+      <c r="A22" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="2" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="2" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" s="2" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="2" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="2" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B32" s="2" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="2" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B34" s="2" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B36" s="2" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="2" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B38" s="2" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B40" s="2" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B41" s="2" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B42" s="2" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43" s="2" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B44" s="2" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B45" s="2" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="2" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B48" s="2" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B49" s="2" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B50" s="2" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3225,53 +3241,53 @@
     <col min="11" max="11" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="23" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>81</v>
@@ -3280,14 +3296,14 @@
         <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H2" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H3" s="23"/>
+      <c r="H3" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3306,17 +3322,17 @@
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3372,42 +3388,42 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
         <v>92</v>
-      </c>
-      <c r="B3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" t="s">
         <v>213</v>
-      </c>
-      <c r="B6" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3418,155 +3434,155 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="22.125" customWidth="1"/>
     <col min="2" max="2" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B6" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="11" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="s">
+      <c r="B15" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="13" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="13" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3574,64 +3590,75 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="12"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="12"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80035136-5A77-44F7-B589-0E6812F61A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9218ECA6-73EA-4435-A214-80ABF55B904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -672,9 +672,6 @@
     <t>letra_codigo</t>
   </si>
   <si>
-    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : adate.getMonths(data('ano'), data('mes'))</t>
-  </si>
-  <si>
     <t>data('cs') + calculates.chill_adult()</t>
   </si>
   <si>
@@ -697,6 +694,9 @@
   </si>
   <si>
     <t>comentario_1</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : sc.getMonths(data('ano'), data('mes'))</t>
   </si>
 </sst>
 </file>
@@ -1744,7 +1744,7 @@
         <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
@@ -1795,7 +1795,7 @@
         <v>106</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
@@ -1839,13 +1839,13 @@
         <v>110</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C33" s="12"/>
       <c r="D33" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>111</v>
@@ -1860,7 +1860,7 @@
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C34" s="11"/>
       <c r="D34" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>111</v>
@@ -1942,7 +1942,7 @@
         <v>4</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>86</v>
@@ -3407,7 +3407,7 @@
         <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3423,7 +3423,7 @@
         <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>111</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>113</v>
@@ -3598,7 +3598,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3606,7 +3606,7 @@
         <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3657,7 +3657,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9218ECA6-73EA-4435-A214-80ABF55B904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C7AD99-E773-49EB-85C1-3EC9852AA967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -696,7 +696,7 @@
     <t>comentario_1</t>
   </si>
   <si>
-    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : sc.getMonths(data('ano'), data('mes'))</t>
+    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10) + parseInt(data('mes'),10)</t>
   </si>
 </sst>
 </file>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C7AD99-E773-49EB-85C1-3EC9852AA967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D26846-315D-4A57-A0B1-66EABFAE8334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -279,12 +279,6 @@
     <t>{}</t>
   </si>
   <si>
-    <t>id_paciente=?</t>
-  </si>
-  <si>
-    <t>[data('id_paciente')]</t>
-  </si>
-  <si>
     <t>data('mes')&lt;12</t>
   </si>
   <si>
@@ -333,9 +327,6 @@
     <t>data_consulta</t>
   </si>
   <si>
-    <t>Data de consulta da criança: {{calculates.hoje_display}}</t>
-  </si>
-  <si>
     <t>procedencia</t>
   </si>
   <si>
@@ -615,9 +606,6 @@
     <t xml:space="preserve">resultado </t>
   </si>
   <si>
-    <t>{id_paciente: data('id_paciente'), nome: data('nome'), nome_casa: data('nome_casa'), sexo: data('sexo'), dn: data('dn'), ano: data('ano'), mes: data('mes'), af: data('af'), id_formssentinela: data('_id')}</t>
-  </si>
-  <si>
     <t>intro_resultado</t>
   </si>
   <si>
@@ -697,6 +685,18 @@
   </si>
   <si>
     <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10) + parseInt(data('mes'),10)</t>
+  </si>
+  <si>
+    <t>_id=?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data de consulta da criança: {{calculates.hoje_display}} </t>
+  </si>
+  <si>
+    <t>[opendatakit.getCurrentInstanceId()]</t>
+  </si>
+  <si>
+    <t>{id_formssentinela: opendatakit.getCurrentInstanceId(), id_paciente: data('id_paciente'), nome: data('nome'), nome_casa: data('nome_casa'), sexo: data('sexo'), dn: data('dn'), ano: data('ano'), mes: data('mes')}</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1349,7 +1349,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1357,7 +1357,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1438,10 +1438,10 @@
         <v>32</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q1" t="s">
         <v>33</v>
@@ -1508,18 +1508,18 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>99</v>
+        <v>218</v>
       </c>
       <c r="J6" s="24"/>
       <c r="K6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R6"/>
       <c r="S6"/>
@@ -1533,13 +1533,13 @@
         <v>10</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -1548,10 +1548,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>44</v>
@@ -1565,7 +1565,7 @@
         <v>51</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1584,7 +1584,7 @@
         <v>26</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -1608,10 +1608,10 @@
         <v>54</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
@@ -1627,13 +1627,13 @@
         <v>55</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>59</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -1744,7 +1744,7 @@
         <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
@@ -1755,10 +1755,10 @@
         <v>48</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
@@ -1786,16 +1786,16 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D29" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
@@ -1805,10 +1805,10 @@
       </c>
       <c r="E30"/>
       <c r="F30" s="18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
@@ -1820,56 +1820,56 @@
         <v>48</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C32" s="11"/>
       <c r="D32" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C33" s="12"/>
       <c r="D33" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C34" s="11"/>
       <c r="D34" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E34" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -1880,10 +1880,10 @@
         <v>48</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="2"/>
@@ -1912,10 +1912,10 @@
         <v>69</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -1924,7 +1924,7 @@
         <v>79</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -1942,10 +1942,10 @@
         <v>4</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -2365,7 +2365,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2417,101 +2417,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2519,332 +2519,332 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,13 +3229,13 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
     <col min="3" max="3" width="15.125" customWidth="1"/>
     <col min="4" max="4" width="15.375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="20.5" customWidth="1"/>
-    <col min="7" max="7" width="50.375" customWidth="1"/>
+    <col min="7" max="7" width="167.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="46.5" customWidth="1"/>
     <col min="10" max="10" width="22.125" customWidth="1"/>
     <col min="11" max="11" width="61" customWidth="1"/>
@@ -3278,25 +3278,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="G2" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>80</v>
@@ -3388,42 +3388,42 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3434,7 +3434,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3462,7 +3462,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3470,7 +3470,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3534,15 +3534,15 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3550,7 +3550,7 @@
         <v>64</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3558,31 +3558,31 @@
         <v>10</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3590,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3598,7 +3598,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3606,58 +3606,55 @@
         <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D26846-315D-4A57-A0B1-66EABFAE8334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E171FF-CA20-49B9-9070-203D7C231518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="227">
   <si>
     <t>type</t>
   </si>
@@ -697,6 +697,24 @@
   </si>
   <si>
     <t>{id_formssentinela: opendatakit.getCurrentInstanceId(), id_paciente: data('id_paciente'), nome: data('nome'), nome_casa: data('nome_casa'), sexo: data('sexo'), dn: data('dn'), ano: data('ano'), mes: data('mes')}</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>calculates.letra_codigo() + data('numero_codigo')</t>
+  </si>
+  <si>
+    <t>numero_codigo</t>
+  </si>
+  <si>
+    <t>nota_1</t>
+  </si>
+  <si>
+    <t>data('ano')&lt;5</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='2' &amp;&amp; data('ano')&lt;5</t>
   </si>
 </sst>
 </file>
@@ -822,7 +840,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -879,6 +897,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1309,7 +1330,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
@@ -1358,6 +1379,14 @@
       </c>
       <c r="B5" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1373,7 +1402,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y98"/>
+  <dimension ref="A1:Y101"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1513,9 +1542,6 @@
       <c r="F6" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="J6" s="24"/>
       <c r="K6" s="2"/>
       <c r="N6" s="2" t="s">
@@ -1528,19 +1554,19 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C7" s="11"/>
-      <c r="D7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>201</v>
-      </c>
+      <c r="D7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J7" s="25"/>
+      <c r="K7" s="2"/>
+      <c r="R7"/>
+      <c r="S7"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C8" s="11"/>
@@ -1548,424 +1574,448 @@
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C9" s="11"/>
+      <c r="D9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="2" t="b">
+      <c r="L9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C10" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="12"/>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12" t="s">
+      <c r="E11" s="12"/>
+      <c r="F11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C12" s="11"/>
-      <c r="D12" s="12" t="s">
-        <v>5</v>
-      </c>
       <c r="E12" s="12"/>
-      <c r="F12" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C13" s="11"/>
       <c r="D13" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="L14" s="11"/>
+    </row>
+    <row r="15" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C15" s="11"/>
+      <c r="D15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C17" s="11"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="B19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C20" s="11"/>
-      <c r="D20" s="12" t="s">
-        <v>64</v>
-      </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="11"/>
-      <c r="D21" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="11"/>
-      <c r="D22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>25</v>
-      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="5"/>
       <c r="L22" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C23" s="11"/>
+      <c r="D23" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C24" s="11"/>
+      <c r="D24" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="11"/>
+      <c r="D25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D24" s="12" t="s">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D27" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F27" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C27" s="11"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D29" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>211</v>
-      </c>
+      <c r="B29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="11"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C30" s="11"/>
-      <c r="D30" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30"/>
-      <c r="F30" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" t="s">
-        <v>98</v>
-      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C31" s="12"/>
-      <c r="D31" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C32" s="11"/>
+      <c r="B31" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D32" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C33" s="11"/>
+      <c r="D33" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33"/>
+      <c r="F33" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C34" s="12"/>
+      <c r="D34" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C35" s="11"/>
+      <c r="D35" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C33" s="12"/>
-      <c r="D33" s="12" t="s">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C36" s="12"/>
+      <c r="D36" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E36" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F36" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C34" s="11"/>
-      <c r="D34" s="12" t="s">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C37" s="11"/>
+      <c r="D37" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E37" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F37" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D35" s="2" t="s">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="2"/>
-      <c r="R35"/>
-      <c r="S35"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
+      <c r="J38" s="7"/>
+      <c r="K38" s="2"/>
+      <c r="R38"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="B37" s="2" t="s">
+      <c r="C39" s="11"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="B40" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="11"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D38" s="12" t="s">
+      <c r="C40" s="11"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D41" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F41" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G41" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="D39" s="12" t="s">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+      <c r="D42" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C41" s="11"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D42" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C43" s="11"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C44" s="11"/>
+      <c r="D44" s="12" t="s">
+        <v>86</v>
+      </c>
       <c r="E44" s="13"/>
-      <c r="F44" s="12"/>
+      <c r="F44" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N44" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C45" s="11"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="12"/>
+      <c r="D45" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C46" s="11"/>
-      <c r="E46" s="13"/>
+      <c r="E46" s="12"/>
       <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -1984,48 +2034,34 @@
       <c r="F49" s="12"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="12"/>
+      <c r="C50" s="11"/>
       <c r="E50" s="13"/>
       <c r="F50" s="12"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C51" s="11"/>
-      <c r="E51" s="12"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="12"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C52" s="11"/>
-      <c r="E52" s="12"/>
+      <c r="E52" s="13"/>
       <c r="F52" s="12"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="15"/>
+      <c r="C53" s="12"/>
       <c r="E53" s="13"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
+      <c r="F53" s="12"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="K54" s="6"/>
+      <c r="C54" s="11"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="K55" s="6"/>
+      <c r="C55" s="11"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="13"/>
@@ -2044,6 +2080,7 @@
       <c r="F57" s="16"/>
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
+      <c r="K57" s="6"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" s="13"/>
@@ -2053,6 +2090,7 @@
       <c r="F58" s="16"/>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
+      <c r="K58" s="6"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="13"/>
@@ -2073,21 +2111,21 @@
       <c r="H60" s="13"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="25"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="13"/>
       <c r="H61" s="13"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="25"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="13"/>
       <c r="H62" s="13"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
@@ -2100,21 +2138,21 @@
       <c r="H63" s="13"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="13"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="26"/>
       <c r="H64" s="13"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="13"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="26"/>
       <c r="H65" s="13"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
@@ -2154,19 +2192,31 @@
       <c r="H69" s="13"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="12"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="12"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="12"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D73" s="11"/>
@@ -2298,15 +2348,30 @@
       <c r="E98" s="11"/>
       <c r="F98" s="12"/>
     </row>
+    <row r="99" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="12"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -3498,8 +3563,8 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>5</v>
+      <c r="A8" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>59</v>
@@ -3609,6 +3674,14 @@
         <v>209</v>
       </c>
     </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
@@ -3659,6 +3732,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E171FF-CA20-49B9-9070-203D7C231518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BDEA40-F7EB-4078-B2F3-FD8115F9450C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="221">
   <si>
     <t>type</t>
   </si>
@@ -378,15 +378,9 @@
     <t>Hospitalização</t>
   </si>
   <si>
-    <t>tdr</t>
-  </si>
-  <si>
     <t>resultado</t>
   </si>
   <si>
-    <t>tdr_resultado</t>
-  </si>
-  <si>
     <t>Paludismo (malária)</t>
   </si>
   <si>
@@ -612,15 +606,6 @@
     <t>Introducão dos resultados de laboratorio</t>
   </si>
   <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>leuco</t>
-  </si>
-  <si>
-    <t>hb</t>
-  </si>
-  <si>
     <t>DOB_idade</t>
   </si>
   <si>
@@ -666,12 +651,6 @@
     <t>id_formssentinela</t>
   </si>
   <si>
-    <t>data('temperatura')&lt;46 &amp; data('temperatura')&gt;32</t>
-  </si>
-  <si>
-    <t>data('peso')&lt;200</t>
-  </si>
-  <si>
     <t>select_one_dropdown</t>
   </si>
   <si>
@@ -681,18 +660,12 @@
     <t>comentario</t>
   </si>
   <si>
-    <t>comentario_1</t>
-  </si>
-  <si>
     <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10) + parseInt(data('mes'),10)</t>
   </si>
   <si>
     <t>_id=?</t>
   </si>
   <si>
-    <t xml:space="preserve">Data de consulta da criança: {{calculates.hoje_display}} </t>
-  </si>
-  <si>
     <t>[opendatakit.getCurrentInstanceId()]</t>
   </si>
   <si>
@@ -715,6 +688,15 @@
   </si>
   <si>
     <t>data('DOB_idade')=='2' &amp;&amp; data('ano')&lt;5</t>
+  </si>
+  <si>
+    <t>data('temperatura')&lt;46 &amp; data('temperatura')&gt;25</t>
+  </si>
+  <si>
+    <t>data('peso')&lt;250</t>
+  </si>
+  <si>
+    <t>Data de consulta da criança: {{calculates.hoje_display}}</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1365,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>59</v>
@@ -1558,10 +1540,10 @@
         <v>69</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="2"/>
@@ -1574,13 +1556,13 @@
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -1589,10 +1571,10 @@
         <v>10</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>44</v>
@@ -1606,7 +1588,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1625,7 +1607,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -1652,7 +1634,7 @@
         <v>83</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1660,7 +1642,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1685,15 +1667,15 @@
         <v>81</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>57</v>
       </c>
@@ -1701,7 +1683,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>56</v>
       </c>
@@ -1709,12 +1691,12 @@
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C20" s="11"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
@@ -1728,7 +1710,7 @@
       <c r="J21" s="3"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="9" t="s">
@@ -1736,10 +1718,10 @@
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="10" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -1749,7 +1731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C23" s="11"/>
       <c r="D23" s="12" t="s">
         <v>64</v>
@@ -1765,7 +1747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C24" s="11"/>
       <c r="D24" s="12" t="s">
         <v>64</v>
@@ -1778,7 +1760,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="11"/>
       <c r="D25" s="12" t="s">
         <v>10</v>
@@ -1796,15 +1778,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D27" s="12" t="s">
         <v>10</v>
       </c>
@@ -1818,12 +1800,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
@@ -1831,175 +1813,175 @@
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C30" s="11"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
+      <c r="D30" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="F30" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C31" s="11"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D32" s="12" t="s">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D33" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F33" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G33" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C33" s="11"/>
-      <c r="D33" s="9" t="s">
+      <c r="J33" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C34" s="11"/>
+      <c r="D34" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E33"/>
-      <c r="F33" s="18" t="s">
+      <c r="E34"/>
+      <c r="F34" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G34" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C34" s="12"/>
-      <c r="D34" s="12" t="s">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C35" s="12"/>
+      <c r="D35" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E35" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F35" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C35" s="11"/>
-      <c r="D35" s="12" t="s">
+    <row r="36" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C36" s="11"/>
+      <c r="D36" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12" t="s">
+      <c r="E36" s="12"/>
+      <c r="F36" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J35" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C36" s="12"/>
-      <c r="D36" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>109</v>
+      <c r="J36" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C37" s="11"/>
+      <c r="C37" s="12"/>
       <c r="D37" s="12" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>108</v>
       </c>
       <c r="F37" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C38" s="11"/>
+      <c r="D38" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D38" s="2" t="s">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G39" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="2"/>
-      <c r="R38"/>
-      <c r="S38"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
+      <c r="J39" s="7"/>
+      <c r="K39" s="2"/>
+      <c r="R39"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="B40" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C40" s="11"/>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D41" s="12" t="s">
+      <c r="A41"/>
+      <c r="B41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="11"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D42" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F41" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-      <c r="D42" s="12" t="s">
+      <c r="F42" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+      <c r="D43" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
+      <c r="E43" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C44" s="11"/>
-      <c r="D44" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="N44" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -2007,7 +1989,7 @@
         <v>4</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>84</v>
@@ -2430,7 +2412,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2441,7 +2423,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2482,101 +2464,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2587,10 +2569,10 @@
         <v>108</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2598,10 +2580,10 @@
         <v>108</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2609,10 +2591,10 @@
         <v>108</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2620,10 +2602,10 @@
         <v>108</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2631,10 +2613,10 @@
         <v>108</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2642,10 +2624,10 @@
         <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2653,10 +2635,10 @@
         <v>108</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2664,10 +2646,10 @@
         <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2675,10 +2657,10 @@
         <v>108</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2686,10 +2668,10 @@
         <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2697,10 +2679,10 @@
         <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2708,10 +2690,10 @@
         <v>108</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2719,10 +2701,10 @@
         <v>108</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2730,10 +2712,10 @@
         <v>108</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2741,10 +2723,10 @@
         <v>108</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2752,10 +2734,10 @@
         <v>108</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2763,10 +2745,10 @@
         <v>108</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2774,10 +2756,10 @@
         <v>108</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2785,10 +2767,10 @@
         <v>108</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2796,10 +2778,10 @@
         <v>108</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2807,10 +2789,10 @@
         <v>108</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2818,10 +2800,10 @@
         <v>108</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2829,10 +2811,10 @@
         <v>108</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2840,10 +2822,10 @@
         <v>108</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2851,10 +2833,10 @@
         <v>108</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2862,10 +2844,10 @@
         <v>108</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2873,10 +2855,10 @@
         <v>108</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2884,10 +2866,10 @@
         <v>108</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2895,10 +2877,10 @@
         <v>108</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2906,10 +2888,10 @@
         <v>108</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3343,25 +3325,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G2" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>80</v>
@@ -3472,23 +3454,23 @@
         <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3499,7 +3481,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -3527,7 +3509,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3535,7 +3517,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3636,7 +3618,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>108</v>
@@ -3644,7 +3626,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>110</v>
@@ -3663,7 +3645,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3671,7 +3653,7 @@
         <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3679,55 +3661,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BDEA40-F7EB-4078-B2F3-FD8115F9450C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADE8BDA-5EB5-4CF1-9F00-3E02F42DB26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="221">
   <si>
     <t>type</t>
   </si>
@@ -624,9 +624,6 @@
     <t>calculates.idade_mes()&lt;216 ? "C" : "A"</t>
   </si>
   <si>
-    <t>Centro de saude:</t>
-  </si>
-  <si>
     <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
   </si>
   <si>
@@ -696,7 +693,10 @@
     <t>data('peso')&lt;250</t>
   </si>
   <si>
-    <t>Data de consulta da criança: {{calculates.hoje_display}}</t>
+    <t>csname</t>
+  </si>
+  <si>
+    <t>Centro: {{data('csname')}} Data: {{calculates.hoje_display}}</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>59</v>
@@ -1384,7 +1384,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y101"/>
+  <dimension ref="A1:Y100"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1540,7 +1540,7 @@
         <v>69</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>220</v>
@@ -1556,177 +1556,178 @@
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C9" s="11"/>
-      <c r="D9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="B9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C12" s="11"/>
+      <c r="D12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C11" s="12"/>
-      <c r="D11" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C13" s="11"/>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="L13" s="11"/>
+    </row>
+    <row r="14" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C14" s="11"/>
+      <c r="D14" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="E14" s="12"/>
+      <c r="F14" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="L14" s="11"/>
-    </row>
-    <row r="15" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C15" s="11"/>
-      <c r="D15" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>217</v>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="C17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="11"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="C19" s="11"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="11"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="3"/>
+      <c r="D21" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="5"/>
+      <c r="L21" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="5"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="L22" s="2" t="b">
         <v>1</v>
       </c>
@@ -1738,266 +1739,255 @@
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L23" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="11"/>
       <c r="D24" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="F24" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="11"/>
-      <c r="D25" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D26" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L25" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>206</v>
+      <c r="E26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D27" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>100</v>
+      <c r="B27" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>57</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="C29" s="11"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
+      <c r="D29" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="13"/>
+      <c r="F29" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C30" s="11"/>
-      <c r="D30" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="N30" t="s">
-        <v>213</v>
-      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C31" s="11"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="B31" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>53</v>
+      <c r="D32" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D33" s="12" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33"/>
+      <c r="F33" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C34" s="12"/>
+      <c r="D34" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C35" s="11"/>
+      <c r="D35" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C34" s="11"/>
-      <c r="D34" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34"/>
-      <c r="F34" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G34" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C35" s="12"/>
-      <c r="D35" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="E35" s="12"/>
       <c r="F35" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C36" s="11"/>
+        <v>107</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C36" s="12"/>
       <c r="D36" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" s="12"/>
+        <v>204</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="F36" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>218</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C37" s="12"/>
+      <c r="C37" s="11"/>
       <c r="D37" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>108</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C38" s="11"/>
-      <c r="D38" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>110</v>
+      <c r="D38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>111</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="J38" s="7"/>
+      <c r="K38" s="2"/>
+      <c r="R38"/>
+      <c r="S38"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J39" s="7"/>
-      <c r="K39" s="2"/>
-      <c r="R39"/>
-      <c r="S39"/>
+      <c r="B39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="11"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40"/>
       <c r="B40" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C40" s="11"/>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
+      <c r="D41" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42"/>
       <c r="D42" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>189</v>
+        <v>79</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43"/>
-      <c r="D43" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>114</v>
+      <c r="B43" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>56</v>
+      <c r="D44" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D45" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="C45" s="11"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C46" s="11"/>
-      <c r="E46" s="12"/>
+      <c r="E46" s="13"/>
       <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -2026,13 +2016,13 @@
       <c r="F51" s="12"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C52" s="11"/>
+      <c r="C52" s="12"/>
       <c r="E52" s="13"/>
       <c r="F52" s="12"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C53" s="12"/>
-      <c r="E53" s="13"/>
+      <c r="C53" s="11"/>
+      <c r="E53" s="12"/>
       <c r="F53" s="12"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
@@ -2041,9 +2031,13 @@
       <c r="F54" s="12"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C55" s="11"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="13"/>
@@ -2053,6 +2047,7 @@
       <c r="F56" s="16"/>
       <c r="G56" s="13"/>
       <c r="H56" s="13"/>
+      <c r="K56" s="6"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" s="13"/>
@@ -2072,7 +2067,6 @@
       <c r="F58" s="16"/>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
-      <c r="K58" s="6"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="13"/>
@@ -2111,12 +2105,12 @@
       <c r="H62" s="13"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="13"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="26"/>
       <c r="H63" s="13"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
@@ -2129,12 +2123,12 @@
       <c r="H64" s="13"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="26"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="13"/>
       <c r="H65" s="13"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
@@ -2192,13 +2186,9 @@
       <c r="H71" s="13"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="12"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D73" s="11"/>
@@ -2340,20 +2330,15 @@
       <c r="E100" s="11"/>
       <c r="F100" s="12"/>
     </row>
-    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="12"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="F63:F64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2508,7 +2493,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>184</v>
@@ -2519,7 +2504,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>185</v>
@@ -2530,10 +2515,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>181</v>
@@ -2541,10 +2526,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>182</v>
@@ -2552,7 +2537,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>186</v>
@@ -3337,13 +3322,13 @@
         <v>114</v>
       </c>
       <c r="E2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F2" t="s">
         <v>209</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>210</v>
-      </c>
-      <c r="G2" t="s">
-        <v>211</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>80</v>
@@ -3418,14 +3403,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02CAEF6-746F-4DFF-99B1-6DB036574858}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
     <col min="2" max="2" width="69.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -3433,7 +3418,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -3441,7 +3426,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -3449,15 +3434,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>194</v>
       </c>
@@ -3465,13 +3450,33 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" t="s">
         <v>202</v>
       </c>
-      <c r="B6" t="s">
-        <v>203</v>
-      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3481,7 +3486,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -3509,7 +3514,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3618,7 +3623,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>108</v>
@@ -3626,7 +3631,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>110</v>
@@ -3645,7 +3650,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3653,7 +3658,7 @@
         <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3661,7 +3666,15 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\consulta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADE8BDA-5EB5-4CF1-9F00-3E02F42DB26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B88FA0-FA29-4B72-AE01-E5A8782D0B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="222">
   <si>
     <t>type</t>
   </si>
@@ -697,6 +697,9 @@
   </si>
   <si>
     <t>Centro: {{data('csname')}} Data: {{calculates.hoje_display}}</t>
+  </si>
+  <si>
+    <t>consultor</t>
   </si>
 </sst>
 </file>
@@ -3486,7 +3489,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -3675,6 +3678,14 @@
       </c>
       <c r="B23" s="10" t="s">
         <v>219</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B88FA0-FA29-4B72-AE01-E5A8782D0B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A08C69-C22E-44B9-AF01-F042B2F22530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -24,8 +24,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">survey!$D$1:$K$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -111,595 +118,595 @@
     <t>sexo</t>
   </si>
   <si>
+    <t>Data de Nascimento</t>
+  </si>
+  <si>
+    <t>dn</t>
+  </si>
+  <si>
+    <t>ano</t>
+  </si>
+  <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>calculation_name</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>display.prompt.audio</t>
+  </si>
+  <si>
+    <t>display.prompt.image</t>
+  </si>
+  <si>
+    <t>templatePath</t>
+  </si>
+  <si>
+    <t>inputAttributes.type</t>
+  </si>
+  <si>
+    <t>inputAttributes.min</t>
+  </si>
+  <si>
+    <t>inputAttributes.max</t>
+  </si>
+  <si>
+    <t>hideInContents</t>
+  </si>
+  <si>
+    <t>callback</t>
+  </si>
+  <si>
+    <t>uri</t>
+  </si>
+  <si>
+    <t>query_type</t>
+  </si>
+  <si>
+    <t>query_name</t>
+  </si>
+  <si>
+    <t>Idade ou data de nascimento?</t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t>Feminino</t>
+  </si>
+  <si>
+    <t>Idade</t>
+  </si>
+  <si>
+    <t>yesno</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>else</t>
+  </si>
+  <si>
+    <t>begin screen</t>
+  </si>
+  <si>
+    <t>Idades em anos</t>
+  </si>
+  <si>
+    <t>Idade em meses</t>
+  </si>
+  <si>
+    <t>end screen</t>
+  </si>
+  <si>
+    <t>end if</t>
+  </si>
+  <si>
+    <t>Nome e Apelido</t>
+  </si>
+  <si>
+    <t>id_paciente</t>
+  </si>
+  <si>
+    <t>custom_date</t>
+  </si>
+  <si>
+    <t>prompt_type_name</t>
+  </si>
+  <si>
+    <t>elementType</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Makes the date widget DD/MM/YYYY</t>
+  </si>
+  <si>
+    <t>nome_casa</t>
+  </si>
+  <si>
+    <t>Nome de Casa</t>
+  </si>
+  <si>
+    <t>branch_label</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>adate</t>
+  </si>
+  <si>
+    <t>Save only mm.dd.yyyy with support for ?? at all positions</t>
+  </si>
+  <si>
+    <t>linked_form_id</t>
+  </si>
+  <si>
+    <t>linked_table_id</t>
+  </si>
+  <si>
+    <t>selection</t>
+  </si>
+  <si>
+    <t>selectionArgs</t>
+  </si>
+  <si>
+    <t>newRowInitialElementKeyToValueMap</t>
+  </si>
+  <si>
+    <t>openRowInitialElementKeyToValueMap</t>
+  </si>
+  <si>
+    <t>fieldName</t>
+  </si>
+  <si>
+    <t>linked_table</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>data('mes')&lt;12</t>
+  </si>
+  <si>
+    <t>se nao souber coloca zero, se for 12 acrescenta 1 ano</t>
+  </si>
+  <si>
+    <t>se for menos de 1 ano coloca zero</t>
+  </si>
+  <si>
+    <t>Comentário</t>
+  </si>
+  <si>
+    <t>idade_mes</t>
+  </si>
+  <si>
+    <t>assign</t>
+  </si>
+  <si>
+    <t>adate.today()</t>
+  </si>
+  <si>
+    <t>hoje</t>
+  </si>
+  <si>
+    <t>hoje_display</t>
+  </si>
+  <si>
+    <t>adate.display(calculates.hoje())</t>
+  </si>
+  <si>
+    <t>display.adate.fromYear</t>
+  </si>
+  <si>
+    <t>display.adate.toYear</t>
+  </si>
+  <si>
+    <t>Consulta</t>
+  </si>
+  <si>
+    <t>sentinela</t>
+  </si>
+  <si>
+    <t>consulta</t>
+  </si>
+  <si>
+    <t>data_consulta</t>
+  </si>
+  <si>
+    <t>procedencia</t>
+  </si>
+  <si>
+    <t>gravidez</t>
+  </si>
+  <si>
+    <t>Gravida</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>peso</t>
+  </si>
+  <si>
+    <t>Peso</t>
+  </si>
+  <si>
+    <t>febre</t>
+  </si>
+  <si>
+    <t>Febre</t>
+  </si>
+  <si>
+    <t>temperatura</t>
+  </si>
+  <si>
+    <t>Temperatura</t>
+  </si>
+  <si>
+    <t>diagnostico</t>
+  </si>
+  <si>
+    <t>Diagnóstico Principal</t>
+  </si>
+  <si>
+    <t>diagno_secund</t>
+  </si>
+  <si>
+    <t>Diagnósticos secundarios</t>
+  </si>
+  <si>
+    <t>hospitaliza</t>
+  </si>
+  <si>
+    <t>Hospitalização</t>
+  </si>
+  <si>
+    <t>resultado</t>
+  </si>
+  <si>
+    <t>Paludismo (malária)</t>
+  </si>
+  <si>
+    <t>Anemia</t>
+  </si>
+  <si>
+    <t>Febre Tifoide</t>
+  </si>
+  <si>
+    <t>Disenteria</t>
+  </si>
+  <si>
+    <t>Positivo</t>
+  </si>
+  <si>
+    <t>Negativo</t>
+  </si>
+  <si>
+    <t>Não Concluente (Indeterminado)</t>
+  </si>
+  <si>
+    <t>Inválido</t>
+  </si>
+  <si>
+    <t>1F4Z</t>
+  </si>
+  <si>
+    <t>3A9Z</t>
+  </si>
+  <si>
+    <t>1A07.Z</t>
+  </si>
+  <si>
+    <t>1A40.Z</t>
+  </si>
+  <si>
+    <t>RA01</t>
+  </si>
+  <si>
+    <t>COVID-19</t>
+  </si>
+  <si>
+    <t>CA40.Z</t>
+  </si>
+  <si>
+    <t>Pneumonia</t>
+  </si>
+  <si>
+    <t>ME05.1</t>
+  </si>
+  <si>
+    <t>Diarrea</t>
+  </si>
+  <si>
+    <t>1B1Z</t>
+  </si>
+  <si>
+    <t>Tuberculosis</t>
+  </si>
+  <si>
+    <t>1C62.Z</t>
+  </si>
+  <si>
+    <t>HIV</t>
+  </si>
+  <si>
+    <t>DA42.Z</t>
+  </si>
+  <si>
+    <t>Gastritis</t>
+  </si>
+  <si>
+    <t>DB97.Z</t>
+  </si>
+  <si>
+    <t>Hepatitis</t>
+  </si>
+  <si>
+    <t>9A60.Z</t>
+  </si>
+  <si>
+    <t>Conjuntivite</t>
+  </si>
+  <si>
+    <t>1A40.0</t>
+  </si>
+  <si>
+    <t>Gastroentetites</t>
+  </si>
+  <si>
+    <t>BA00.Z</t>
+  </si>
+  <si>
+    <t>Hipertensão arterial</t>
+  </si>
+  <si>
+    <t>5A14</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
+  </si>
+  <si>
+    <t>1A9Z</t>
+  </si>
+  <si>
+    <t>Infecões de transmissão sexual</t>
+  </si>
+  <si>
+    <t>GC08.Z</t>
+  </si>
+  <si>
+    <t>Infecões de tracto urinario</t>
+  </si>
+  <si>
+    <t>GA05.Z</t>
+  </si>
+  <si>
+    <t>CA08.1Y</t>
+  </si>
+  <si>
+    <t>Gravidez</t>
+  </si>
+  <si>
+    <t>ME05.0</t>
+  </si>
+  <si>
+    <t>constipação</t>
+  </si>
+  <si>
+    <t>AA3Z</t>
+  </si>
+  <si>
+    <t>Otitis externa o Media</t>
+  </si>
+  <si>
+    <t>CA0Y</t>
+  </si>
+  <si>
+    <t>Faringoamigdalites</t>
+  </si>
+  <si>
+    <t>FA2Z</t>
+  </si>
+  <si>
+    <t>Atrites</t>
+  </si>
+  <si>
+    <t>ND56.Z</t>
+  </si>
+  <si>
+    <t>Traumatismo</t>
+  </si>
+  <si>
+    <t>8A80.Z</t>
+  </si>
+  <si>
+    <t>Migranha</t>
+  </si>
+  <si>
+    <t>MG27</t>
+  </si>
+  <si>
+    <t>Hemorragia</t>
+  </si>
+  <si>
+    <t>DD5Z</t>
+  </si>
+  <si>
+    <t>Hernias</t>
+  </si>
+  <si>
+    <t>4A8Z</t>
+  </si>
+  <si>
+    <t>Alergia</t>
+  </si>
+  <si>
+    <t>1F28.Z</t>
+  </si>
+  <si>
+    <t>Micosis Superficial</t>
+  </si>
+  <si>
+    <t>1B7Y</t>
+  </si>
+  <si>
+    <t>Infeccoes bacterianas da pele e partes blando</t>
+  </si>
+  <si>
+    <t>Doencas inflamatorias pelvicas</t>
+  </si>
+  <si>
+    <t>Buba</t>
+  </si>
+  <si>
+    <t>Canchungo</t>
+  </si>
+  <si>
+    <t>Gabú (CMI)</t>
+  </si>
+  <si>
+    <t>Gabú (hospital)</t>
+  </si>
+  <si>
+    <t>B. Militar</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>SBM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resultado </t>
+  </si>
+  <si>
+    <t>intro_resultado</t>
+  </si>
+  <si>
+    <t>Introducão dos resultados de laboratorio</t>
+  </si>
+  <si>
+    <t>DOB_idade</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='1'</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='2'</t>
+  </si>
+  <si>
+    <t>resultado_tdr</t>
+  </si>
+  <si>
+    <t>calculates.idade_mes()&lt;216 ? "C" : "A"</t>
+  </si>
+  <si>
+    <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
+  </si>
+  <si>
+    <t>SGC</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>centro</t>
+  </si>
+  <si>
+    <t>cs</t>
+  </si>
+  <si>
+    <t>letra_codigo</t>
+  </si>
+  <si>
+    <t>id_formssentinela</t>
+  </si>
+  <si>
+    <t>select_one_dropdown</t>
+  </si>
+  <si>
+    <t>comentario</t>
+  </si>
+  <si>
+    <t>_id=?</t>
+  </si>
+  <si>
+    <t>[opendatakit.getCurrentInstanceId()]</t>
+  </si>
+  <si>
+    <t>{id_formssentinela: opendatakit.getCurrentInstanceId(), id_paciente: data('id_paciente'), nome: data('nome'), nome_casa: data('nome_casa'), sexo: data('sexo'), dn: data('dn'), ano: data('ano'), mes: data('mes')}</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>calculates.letra_codigo() + data('numero_codigo')</t>
+  </si>
+  <si>
+    <t>numero_codigo</t>
+  </si>
+  <si>
+    <t>nota_1</t>
+  </si>
+  <si>
+    <t>data('ano')&lt;5</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='2' &amp;&amp; data('ano')&lt;5</t>
+  </si>
+  <si>
+    <t>data('temperatura')&lt;46 &amp; data('temperatura')&gt;25</t>
+  </si>
+  <si>
+    <t>data('peso')&lt;250</t>
+  </si>
+  <si>
+    <t>csname</t>
+  </si>
+  <si>
+    <t>Centro: {{data('csname')}} Data: {{calculates.hoje_display}}</t>
+  </si>
+  <si>
+    <t>consultor</t>
+  </si>
+  <si>
+    <t>Proveniência</t>
+  </si>
+  <si>
+    <t>child_adult</t>
+  </si>
+  <si>
+    <t>data('cs') + calculates.child_adult()</t>
+  </si>
+  <si>
+    <t>data('sexo')=='2' &amp;&amp; calculates.idade_mes() &gt;= 144 &amp;&amp; calculates.idade_mes() &lt;= 660</t>
+  </si>
+  <si>
     <t>Sexo</t>
   </si>
   <si>
-    <t>Data de Nascimento</t>
-  </si>
-  <si>
-    <t>dn</t>
-  </si>
-  <si>
-    <t>ano</t>
-  </si>
-  <si>
-    <t>mes</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>calculation_name</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>display.prompt.audio</t>
-  </si>
-  <si>
-    <t>display.prompt.image</t>
-  </si>
-  <si>
-    <t>templatePath</t>
-  </si>
-  <si>
-    <t>inputAttributes.type</t>
-  </si>
-  <si>
-    <t>inputAttributes.min</t>
-  </si>
-  <si>
-    <t>inputAttributes.max</t>
-  </si>
-  <si>
-    <t>hideInContents</t>
-  </si>
-  <si>
-    <t>callback</t>
-  </si>
-  <si>
-    <t>uri</t>
-  </si>
-  <si>
-    <t>query_type</t>
-  </si>
-  <si>
-    <t>query_name</t>
-  </si>
-  <si>
-    <t>Idade ou data de nascimento?</t>
-  </si>
-  <si>
-    <t>Masculino</t>
-  </si>
-  <si>
-    <t>Feminino</t>
-  </si>
-  <si>
-    <t>Idade</t>
-  </si>
-  <si>
-    <t>yesno</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>if</t>
-  </si>
-  <si>
-    <t>else</t>
-  </si>
-  <si>
-    <t>begin screen</t>
-  </si>
-  <si>
-    <t>Idades em anos</t>
-  </si>
-  <si>
-    <t>Idade em meses</t>
-  </si>
-  <si>
-    <t>end screen</t>
-  </si>
-  <si>
-    <t>end if</t>
-  </si>
-  <si>
-    <t>Nome e Apelido</t>
-  </si>
-  <si>
-    <t>id_paciente</t>
-  </si>
-  <si>
-    <t>custom_date</t>
-  </si>
-  <si>
-    <t>prompt_type_name</t>
-  </si>
-  <si>
-    <t>elementType</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Makes the date widget DD/MM/YYYY</t>
-  </si>
-  <si>
-    <t>nome_casa</t>
-  </si>
-  <si>
-    <t>Nome de Casa</t>
-  </si>
-  <si>
-    <t>branch_label</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>adate</t>
-  </si>
-  <si>
-    <t>Save only mm.dd.yyyy with support for ?? at all positions</t>
-  </si>
-  <si>
-    <t>linked_form_id</t>
-  </si>
-  <si>
-    <t>linked_table_id</t>
-  </si>
-  <si>
-    <t>selection</t>
-  </si>
-  <si>
-    <t>selectionArgs</t>
-  </si>
-  <si>
-    <t>newRowInitialElementKeyToValueMap</t>
-  </si>
-  <si>
-    <t>openRowInitialElementKeyToValueMap</t>
-  </si>
-  <si>
-    <t>fieldName</t>
-  </si>
-  <si>
-    <t>linked_table</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
-    <t>data('mes')&lt;12</t>
-  </si>
-  <si>
-    <t>se nao souber coloca zero, se for 12 acrescenta 1 ano</t>
-  </si>
-  <si>
-    <t>se for menos de 1 ano coloca zero</t>
-  </si>
-  <si>
-    <t>Comentário</t>
-  </si>
-  <si>
-    <t>idade_mes</t>
-  </si>
-  <si>
-    <t>assign</t>
-  </si>
-  <si>
-    <t>adate.today()</t>
-  </si>
-  <si>
-    <t>hoje</t>
-  </si>
-  <si>
-    <t>hoje_display</t>
-  </si>
-  <si>
-    <t>adate.display(calculates.hoje())</t>
-  </si>
-  <si>
-    <t>display.adate.fromYear</t>
-  </si>
-  <si>
-    <t>display.adate.toYear</t>
-  </si>
-  <si>
-    <t>Consulta</t>
-  </si>
-  <si>
-    <t>sentinela</t>
-  </si>
-  <si>
-    <t>consulta</t>
-  </si>
-  <si>
-    <t>data_consulta</t>
-  </si>
-  <si>
-    <t>procedencia</t>
-  </si>
-  <si>
-    <t>Procedencia</t>
-  </si>
-  <si>
-    <t>gravidez</t>
-  </si>
-  <si>
-    <t>Gravida</t>
-  </si>
-  <si>
-    <t>decimal</t>
-  </si>
-  <si>
-    <t>peso</t>
-  </si>
-  <si>
-    <t>Peso</t>
-  </si>
-  <si>
-    <t>febre</t>
-  </si>
-  <si>
-    <t>Febre</t>
-  </si>
-  <si>
-    <t>temperatura</t>
-  </si>
-  <si>
-    <t>Temperatura</t>
-  </si>
-  <si>
-    <t>diagnostico</t>
-  </si>
-  <si>
-    <t>Diagnóstico Principal</t>
-  </si>
-  <si>
-    <t>diagno_secund</t>
-  </si>
-  <si>
-    <t>Diagnósticos secundarios</t>
-  </si>
-  <si>
-    <t>hospitaliza</t>
-  </si>
-  <si>
-    <t>Hospitalização</t>
-  </si>
-  <si>
-    <t>resultado</t>
-  </si>
-  <si>
-    <t>Paludismo (malária)</t>
-  </si>
-  <si>
-    <t>Anemia</t>
-  </si>
-  <si>
-    <t>Febre Tifoide</t>
-  </si>
-  <si>
-    <t>Disenteria</t>
-  </si>
-  <si>
-    <t>Positivo</t>
-  </si>
-  <si>
-    <t>Negativo</t>
-  </si>
-  <si>
-    <t>Não Concluente (Indeterminado)</t>
-  </si>
-  <si>
-    <t>Inválido</t>
-  </si>
-  <si>
-    <t>1F4Z</t>
-  </si>
-  <si>
-    <t>3A9Z</t>
-  </si>
-  <si>
-    <t>1A07.Z</t>
-  </si>
-  <si>
-    <t>1A40.Z</t>
-  </si>
-  <si>
-    <t>RA01</t>
-  </si>
-  <si>
-    <t>COVID-19</t>
-  </si>
-  <si>
-    <t>CA40.Z</t>
-  </si>
-  <si>
-    <t>Pneumonia</t>
-  </si>
-  <si>
-    <t>ME05.1</t>
-  </si>
-  <si>
-    <t>Diarrea</t>
-  </si>
-  <si>
-    <t>1B1Z</t>
-  </si>
-  <si>
-    <t>Tuberculosis</t>
-  </si>
-  <si>
-    <t>1C62.Z</t>
-  </si>
-  <si>
-    <t>HIV</t>
-  </si>
-  <si>
-    <t>DA42.Z</t>
-  </si>
-  <si>
-    <t>Gastritis</t>
-  </si>
-  <si>
-    <t>DB97.Z</t>
-  </si>
-  <si>
-    <t>Hepatitis</t>
-  </si>
-  <si>
-    <t>9A60.Z</t>
-  </si>
-  <si>
-    <t>Conjuntivite</t>
-  </si>
-  <si>
-    <t>1A40.0</t>
-  </si>
-  <si>
-    <t>Gastroentetites</t>
-  </si>
-  <si>
-    <t>BA00.Z</t>
-  </si>
-  <si>
-    <t>Hipertensão arterial</t>
-  </si>
-  <si>
-    <t>5A14</t>
-  </si>
-  <si>
-    <t>Diabetes</t>
-  </si>
-  <si>
-    <t>1A9Z</t>
-  </si>
-  <si>
-    <t>Infecões de transmissão sexual</t>
-  </si>
-  <si>
-    <t>GC08.Z</t>
-  </si>
-  <si>
-    <t>Infecões de tracto urinario</t>
-  </si>
-  <si>
-    <t>GA05.Z</t>
-  </si>
-  <si>
-    <t>CA08.1Y</t>
-  </si>
-  <si>
-    <t>Gravidez</t>
-  </si>
-  <si>
-    <t>ME05.0</t>
-  </si>
-  <si>
-    <t>constipação</t>
-  </si>
-  <si>
-    <t>AA3Z</t>
-  </si>
-  <si>
-    <t>Otitis externa o Media</t>
-  </si>
-  <si>
-    <t>CA0Y</t>
-  </si>
-  <si>
-    <t>Faringoamigdalites</t>
-  </si>
-  <si>
-    <t>FA2Z</t>
-  </si>
-  <si>
-    <t>Atrites</t>
-  </si>
-  <si>
-    <t>ND56.Z</t>
-  </si>
-  <si>
-    <t>Traumatismo</t>
-  </si>
-  <si>
-    <t>8A80.Z</t>
-  </si>
-  <si>
-    <t>Migranha</t>
-  </si>
-  <si>
-    <t>MG27</t>
-  </si>
-  <si>
-    <t>Hemorragia</t>
-  </si>
-  <si>
-    <t>DD5Z</t>
-  </si>
-  <si>
-    <t>Hernias</t>
-  </si>
-  <si>
-    <t>4A8Z</t>
-  </si>
-  <si>
-    <t>Alergia</t>
-  </si>
-  <si>
-    <t>1F28.Z</t>
-  </si>
-  <si>
-    <t>Micosis Superficial</t>
-  </si>
-  <si>
-    <t>1B7Y</t>
-  </si>
-  <si>
-    <t>Infeccoes bacterianas da pele e partes blando</t>
-  </si>
-  <si>
-    <t>Doencas inflamatorias pelvicas</t>
-  </si>
-  <si>
-    <t>Buba</t>
-  </si>
-  <si>
-    <t>Canchungo</t>
-  </si>
-  <si>
-    <t>Gabú (CMI)</t>
-  </si>
-  <si>
-    <t>Gabú (hospital)</t>
-  </si>
-  <si>
-    <t>B. Militar</t>
-  </si>
-  <si>
-    <t>SB</t>
-  </si>
-  <si>
-    <t>SH</t>
-  </si>
-  <si>
-    <t>SBM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resultado </t>
-  </si>
-  <si>
-    <t>intro_resultado</t>
-  </si>
-  <si>
-    <t>Introducão dos resultados de laboratorio</t>
-  </si>
-  <si>
-    <t>DOB_idade</t>
-  </si>
-  <si>
-    <t>data('DOB_idade')=='1'</t>
-  </si>
-  <si>
-    <t>data('DOB_idade')=='2'</t>
-  </si>
-  <si>
-    <t>resultado_tdr</t>
-  </si>
-  <si>
-    <t>chill_adult</t>
-  </si>
-  <si>
-    <t>calculates.idade_mes()&lt;216 ? "C" : "A"</t>
-  </si>
-  <si>
-    <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
-  </si>
-  <si>
-    <t>SGC</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>centro</t>
-  </si>
-  <si>
-    <t>cs</t>
-  </si>
-  <si>
-    <t>letra_codigo</t>
-  </si>
-  <si>
-    <t>data('cs') + calculates.chill_adult()</t>
-  </si>
-  <si>
-    <t>id_formssentinela</t>
-  </si>
-  <si>
-    <t>select_one_dropdown</t>
-  </si>
-  <si>
-    <t>data('sexo')=='2' &amp;&amp; (calculates.idade_mes()&lt;=660 &amp;&amp; calculates.idade_mes()&gt;=144)</t>
-  </si>
-  <si>
-    <t>comentario</t>
-  </si>
-  <si>
-    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10) + parseInt(data('mes'),10)</t>
-  </si>
-  <si>
-    <t>_id=?</t>
-  </si>
-  <si>
-    <t>[opendatakit.getCurrentInstanceId()]</t>
-  </si>
-  <si>
-    <t>{id_formssentinela: opendatakit.getCurrentInstanceId(), id_paciente: data('id_paciente'), nome: data('nome'), nome_casa: data('nome_casa'), sexo: data('sexo'), dn: data('dn'), ano: data('ano'), mes: data('mes')}</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>calculates.letra_codigo() + data('numero_codigo')</t>
-  </si>
-  <si>
-    <t>numero_codigo</t>
-  </si>
-  <si>
-    <t>nota_1</t>
-  </si>
-  <si>
-    <t>data('ano')&lt;5</t>
-  </si>
-  <si>
-    <t>data('DOB_idade')=='2' &amp;&amp; data('ano')&lt;5</t>
-  </si>
-  <si>
-    <t>data('temperatura')&lt;46 &amp; data('temperatura')&gt;25</t>
-  </si>
-  <si>
-    <t>data('peso')&lt;250</t>
-  </si>
-  <si>
-    <t>csname</t>
-  </si>
-  <si>
-    <t>Centro: {{data('csname')}} Data: {{calculates.hoje_display}}</t>
-  </si>
-  <si>
-    <t>consultor</t>
+    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10)</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1346,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1355,7 +1362,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1363,15 +1370,15 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1410,7 +1417,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
@@ -1431,7 +1438,7 @@
         <v>20</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
         <v>21</v>
@@ -1446,37 +1453,37 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q1" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>33</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>34</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>35</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>36</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>37</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>38</v>
-      </c>
-      <c r="W1" t="s">
-        <v>39</v>
       </c>
       <c r="X1" t="s">
         <v>19</v>
@@ -1517,20 +1524,20 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J6" s="24"/>
       <c r="K6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R6"/>
       <c r="S6"/>
@@ -1540,13 +1547,13 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F7" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="2"/>
@@ -1559,13 +1566,13 @@
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>1</v>
@@ -1573,10 +1580,10 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1585,22 +1592,22 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="11"/>
       <c r="E11" s="12"/>
@@ -1613,24 +1620,24 @@
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1643,29 +1650,29 @@
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="11"/>
       <c r="E17" s="12"/>
@@ -1673,7 +1680,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" s="11"/>
       <c r="E18" s="12"/>
@@ -1686,7 +1693,7 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="10"/>
@@ -1706,10 +1713,10 @@
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="10" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -1722,14 +1729,14 @@
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C22" s="11"/>
       <c r="D22" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
         <v>23</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>1</v>
@@ -1738,14 +1745,14 @@
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C23" s="11"/>
       <c r="D23" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1760,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="L24" s="2" t="b">
         <v>1</v>
@@ -1768,10 +1775,10 @@
     </row>
     <row r="25" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
@@ -1779,23 +1786,23 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" s="11"/>
       <c r="E28" s="12"/>
@@ -1804,14 +1811,14 @@
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C29" s="11"/>
       <c r="D29" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N29" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
@@ -1821,34 +1828,34 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D32" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="J32" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C33" s="11"/>
       <c r="D33" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>98</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -1857,59 +1864,59 @@
         <v>10</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C35" s="11"/>
       <c r="D35" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C36" s="12"/>
       <c r="D36" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C37" s="11"/>
       <c r="D37" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E37" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F37" s="12" t="s">
-        <v>110</v>
-      </c>
       <c r="G37" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -1917,13 +1924,13 @@
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="2"/>
@@ -1932,7 +1939,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" s="11"/>
       <c r="E39" s="12"/>
@@ -1941,7 +1948,7 @@
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="B40" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="11"/>
       <c r="E40" s="12"/>
@@ -1949,27 +1956,27 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D41" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
@@ -1977,10 +1984,10 @@
         <v>4</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -2384,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2395,29 +2402,29 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2426,24 +2433,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2452,101 +2459,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2554,332 +2561,332 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,63 +3285,63 @@
   <sheetData>
     <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="E1" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="F1" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="G1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="H1" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="I1" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="23" t="s">
-        <v>78</v>
-      </c>
       <c r="J1" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -3359,44 +3366,44 @@
   <sheetData>
     <row r="1" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
         <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3415,50 +3422,50 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
         <v>31</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
         <v>89</v>
-      </c>
-      <c r="B3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3506,10 +3513,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3517,7 +3524,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3525,15 +3532,15 @@
         <v>10</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3541,7 +3548,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3549,20 +3556,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>23</v>
@@ -3570,10 +3577,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3589,23 +3596,23 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3613,31 +3620,31 @@
         <v>10</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3645,7 +3652,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3653,15 +3660,15 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3669,23 +3676,23 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A08C69-C22E-44B9-AF01-F042B2F22530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B601285B-BD1E-47B7-B2A2-15E31B3421A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -685,9 +685,6 @@
     <t>csname</t>
   </si>
   <si>
-    <t>Centro: {{data('csname')}} Data: {{calculates.hoje_display}}</t>
-  </si>
-  <si>
     <t>consultor</t>
   </si>
   <si>
@@ -707,6 +704,9 @@
   </si>
   <si>
     <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10)</t>
+  </si>
+  <si>
+    <t>Centro: {{data.csname}} Data: {{calculates.hoje_display}}</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1553,7 @@
         <v>208</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="2"/>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L24" s="2" t="b">
         <v>1</v>
@@ -1778,7 +1778,7 @@
         <v>50</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
@@ -1855,7 +1855,7 @@
         <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -3449,12 +3449,12 @@
         <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>192</v>
@@ -3465,7 +3465,7 @@
         <v>198</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3692,7 +3692,7 @@
         <v>63</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B601285B-BD1E-47B7-B2A2-15E31B3421A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E22FCAF-874C-4DBB-AEBB-27E461949679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,15 +24,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">survey!$D$1:$K$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -118,6 +111,9 @@
     <t>sexo</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
     <t>Data de Nascimento</t>
   </si>
   <si>
@@ -646,6 +642,9 @@
     <t>select_one_dropdown</t>
   </si>
   <si>
+    <t>data('sexo')=='2' &amp;&amp; (calculates.idade_mes()&lt;=660 &amp;&amp; calculates.idade_mes()&gt;=144)</t>
+  </si>
+  <si>
     <t>comentario</t>
   </si>
   <si>
@@ -685,28 +684,22 @@
     <t>csname</t>
   </si>
   <si>
+    <t>Centro: {{data.csname}} Data: {{calculates.hoje_display}}</t>
+  </si>
+  <si>
     <t>consultor</t>
   </si>
   <si>
+    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10)</t>
+  </si>
+  <si>
+    <t>child_adult</t>
+  </si>
+  <si>
+    <t>data('cs') + calculates.child_adult()</t>
+  </si>
+  <si>
     <t>Proveniência</t>
-  </si>
-  <si>
-    <t>child_adult</t>
-  </si>
-  <si>
-    <t>data('cs') + calculates.child_adult()</t>
-  </si>
-  <si>
-    <t>data('sexo')=='2' &amp;&amp; calculates.idade_mes() &gt;= 144 &amp;&amp; calculates.idade_mes() &lt;= 660</t>
-  </si>
-  <si>
-    <t>Sexo</t>
-  </si>
-  <si>
-    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10)</t>
-  </si>
-  <si>
-    <t>Centro: {{data.csname}} Data: {{calculates.hoje_display}}</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1339,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1362,7 +1355,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1370,15 +1363,15 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1417,7 +1410,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
@@ -1438,7 +1431,7 @@
         <v>20</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
         <v>21</v>
@@ -1453,37 +1446,37 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X1" t="s">
         <v>19</v>
@@ -1524,20 +1517,20 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J6" s="24"/>
       <c r="K6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R6"/>
       <c r="S6"/>
@@ -1547,13 +1540,13 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="2"/>
@@ -1566,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>1</v>
@@ -1580,10 +1573,10 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1592,22 +1585,22 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>25</v>
-      </c>
       <c r="L10" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" s="11"/>
       <c r="E11" s="12"/>
@@ -1620,24 +1613,24 @@
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1650,29 +1643,29 @@
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="L14" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="11"/>
       <c r="E17" s="12"/>
@@ -1680,7 +1673,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C18" s="11"/>
       <c r="E18" s="12"/>
@@ -1693,7 +1686,7 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="10"/>
@@ -1713,10 +1706,10 @@
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -1729,14 +1722,14 @@
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C22" s="11"/>
       <c r="D22" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
         <v>23</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>1</v>
@@ -1745,14 +1738,14 @@
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C23" s="11"/>
       <c r="D23" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1767,7 +1760,7 @@
         <v>24</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>219</v>
+        <v>25</v>
       </c>
       <c r="L24" s="2" t="b">
         <v>1</v>
@@ -1775,10 +1768,10 @@
     </row>
     <row r="25" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
@@ -1786,23 +1779,23 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C28" s="11"/>
       <c r="E28" s="12"/>
@@ -1811,14 +1804,14 @@
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C29" s="11"/>
       <c r="D29" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
@@ -1828,34 +1821,34 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D32" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C33" s="11"/>
       <c r="D33" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G33" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -1864,59 +1857,59 @@
         <v>10</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C35" s="11"/>
       <c r="D35" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C36" s="12"/>
       <c r="D36" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C37" s="11"/>
       <c r="D37" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -1924,13 +1917,13 @@
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="2"/>
@@ -1939,7 +1932,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C39" s="11"/>
       <c r="E39" s="12"/>
@@ -1948,7 +1941,7 @@
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="B40" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C40" s="11"/>
       <c r="E40" s="12"/>
@@ -1956,27 +1949,27 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D41" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
@@ -1984,10 +1977,10 @@
         <v>4</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -2391,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2402,29 +2395,29 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2433,24 +2426,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2459,101 +2452,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2561,332 +2554,332 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3285,63 +3278,63 @@
   <sheetData>
     <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="J1" s="23" t="s">
+      <c r="K1" s="23" t="s">
         <v>40</v>
-      </c>
-      <c r="K1" s="23" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -3366,44 +3359,44 @@
   <sheetData>
     <row r="1" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3422,50 +3415,50 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
         <v>87</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3513,10 +3506,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3524,7 +3517,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3532,15 +3525,15 @@
         <v>10</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3548,7 +3541,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3556,20 +3549,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>23</v>
@@ -3577,10 +3570,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3596,23 +3589,23 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3620,31 +3613,31 @@
         <v>10</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3652,7 +3645,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3660,15 +3653,15 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3676,23 +3669,23 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>214</v>
+      <c r="A24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E22FCAF-874C-4DBB-AEBB-27E461949679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA35828-4A66-4627-AF18-32C666F52FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="222">
   <si>
     <t>type</t>
   </si>
@@ -1774,7 +1774,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" ht="63" x14ac:dyDescent="0.25">
       <c r="D26" s="12" t="s">
         <v>10</v>
       </c>
@@ -1786,6 +1786,9 @@
       </c>
       <c r="G26" s="2" t="s">
         <v>99</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
@@ -1837,6 +1840,9 @@
       <c r="J32" s="2" t="s">
         <v>214</v>
       </c>
+      <c r="L32" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C33" s="11"/>
@@ -1850,6 +1856,9 @@
       <c r="G33" t="s">
         <v>221</v>
       </c>
+      <c r="L33" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C34" s="12"/>
@@ -1865,6 +1874,9 @@
       <c r="G34" s="2" t="s">
         <v>104</v>
       </c>
+      <c r="L34" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C35" s="11"/>
@@ -1881,6 +1893,9 @@
       <c r="J35" s="2" t="s">
         <v>213</v>
       </c>
+      <c r="L35" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C36" s="12"/>
@@ -1896,6 +1911,9 @@
       <c r="G36" s="2" t="s">
         <v>108</v>
       </c>
+      <c r="L36" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C37" s="11"/>
@@ -1927,6 +1945,9 @@
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="2"/>
+      <c r="L38" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="R38"/>
       <c r="S38"/>
     </row>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA35828-4A66-4627-AF18-32C666F52FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CBF433-09D3-4066-AD5A-827A3575DD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="230">
   <si>
     <t>type</t>
   </si>
@@ -700,6 +700,30 @@
   </si>
   <si>
     <t>Proveniência</t>
+  </si>
+  <si>
+    <t>Outro</t>
+  </si>
+  <si>
+    <t>data('diagnostico')=='outro'</t>
+  </si>
+  <si>
+    <t>data('diagno_secund')=='outro'</t>
+  </si>
+  <si>
+    <t>esp_diagnostico</t>
+  </si>
+  <si>
+    <t>esp_diagnostico_secudario</t>
+  </si>
+  <si>
+    <t>Diagnóstico Principal: Especifique</t>
+  </si>
+  <si>
+    <t>Diagnósticos secundarios: Espeficique</t>
+  </si>
+  <si>
+    <t>outro</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1411,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y100"/>
+  <dimension ref="A1:Y106"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1916,199 +1940,211 @@
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C37" s="11"/>
-      <c r="D37" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>110</v>
-      </c>
+      <c r="B37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>111</v>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R38"/>
-      <c r="S38"/>
+        <v>227</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="11"/>
+        <v>57</v>
+      </c>
+      <c r="C39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="B40" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="C40" s="11"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
+      <c r="D40" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D41" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42"/>
+      <c r="B41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C42" s="12"/>
       <c r="D42" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>64</v>
+      </c>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="D44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J44" s="7"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R44"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D44" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C45" s="11"/>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C46" s="11"/>
-      <c r="E46" s="13"/>
+      <c r="E46" s="12"/>
       <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C47" s="11"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="12"/>
+      <c r="D47" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C48" s="11"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="12"/>
+      <c r="A48"/>
+      <c r="D48" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="11"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="12"/>
+      <c r="B49" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="11"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="12"/>
+      <c r="D50" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C51" s="11"/>
-      <c r="E51" s="13"/>
+      <c r="E51" s="12"/>
       <c r="F51" s="12"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C52" s="12"/>
+      <c r="C52" s="11"/>
       <c r="E52" s="13"/>
       <c r="F52" s="12"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C53" s="11"/>
-      <c r="E53" s="12"/>
+      <c r="E53" s="13"/>
       <c r="F53" s="12"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C54" s="11"/>
-      <c r="E54" s="12"/>
+      <c r="E54" s="13"/>
       <c r="F54" s="12"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="15"/>
+      <c r="C55" s="11"/>
       <c r="E55" s="13"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
+      <c r="F55" s="12"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="15"/>
+      <c r="C56" s="11"/>
       <c r="E56" s="13"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="K56" s="6"/>
+      <c r="F56" s="12"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="15"/>
+      <c r="C57" s="11"/>
       <c r="E57" s="13"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="K57" s="6"/>
+      <c r="F57" s="12"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="15"/>
+      <c r="C58" s="12"/>
       <c r="E58" s="13"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
+      <c r="F58" s="12"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
+      <c r="C59" s="11"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
+      <c r="C60" s="11"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="13"/>
@@ -2127,23 +2163,25 @@
       <c r="F62" s="16"/>
       <c r="G62" s="13"/>
       <c r="H62" s="13"/>
+      <c r="K62" s="6"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="26"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="13"/>
       <c r="H63" s="13"/>
+      <c r="K63" s="6"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="26"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="13"/>
       <c r="H64" s="13"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
@@ -2183,21 +2221,21 @@
       <c r="H68" s="13"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="13"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="26"/>
       <c r="H69" s="13"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="13"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="26"/>
       <c r="H70" s="13"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
@@ -2210,34 +2248,58 @@
       <c r="H71" s="13"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="12"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="12"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="12"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="12"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="12"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="12"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D78" s="11"/>
@@ -2354,15 +2416,45 @@
       <c r="E100" s="11"/>
       <c r="F100" s="12"/>
     </row>
+    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="102" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="12"/>
+    </row>
+    <row r="103" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="12"/>
+    </row>
+    <row r="104" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="12"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2904,7 +2996,15 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
+      <c r="A52" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
@@ -3510,7 +3610,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -3707,6 +3807,22 @@
       </c>
       <c r="B24" s="2" t="s">
         <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CBF433-09D3-4066-AD5A-827A3575DD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45895126-525A-451F-BA33-EA3C2D272FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="296">
   <si>
     <t>type</t>
   </si>
@@ -111,9 +111,6 @@
     <t>sexo</t>
   </si>
   <si>
-    <t>Sexo</t>
-  </si>
-  <si>
     <t>Data de Nascimento</t>
   </si>
   <si>
@@ -168,9 +165,6 @@
     <t>query_name</t>
   </si>
   <si>
-    <t>Idade ou data de nascimento?</t>
-  </si>
-  <si>
     <t>Masculino</t>
   </si>
   <si>
@@ -192,27 +186,15 @@
     <t>if</t>
   </si>
   <si>
-    <t>else</t>
-  </si>
-  <si>
     <t>begin screen</t>
   </si>
   <si>
-    <t>Idades em anos</t>
-  </si>
-  <si>
-    <t>Idade em meses</t>
-  </si>
-  <si>
     <t>end screen</t>
   </si>
   <si>
     <t>end if</t>
   </si>
   <si>
-    <t>Nome e Apelido</t>
-  </si>
-  <si>
     <t>id_paciente</t>
   </si>
   <si>
@@ -237,9 +219,6 @@
     <t>nome_casa</t>
   </si>
   <si>
-    <t>Nome de Casa</t>
-  </si>
-  <si>
     <t>branch_label</t>
   </si>
   <si>
@@ -279,15 +258,6 @@
     <t>{}</t>
   </si>
   <si>
-    <t>data('mes')&lt;12</t>
-  </si>
-  <si>
-    <t>se nao souber coloca zero, se for 12 acrescenta 1 ano</t>
-  </si>
-  <si>
-    <t>se for menos de 1 ano coloca zero</t>
-  </si>
-  <si>
     <t>Comentário</t>
   </si>
   <si>
@@ -342,9 +312,6 @@
     <t>peso</t>
   </si>
   <si>
-    <t>Peso</t>
-  </si>
-  <si>
     <t>febre</t>
   </si>
   <si>
@@ -378,18 +345,9 @@
     <t>resultado</t>
   </si>
   <si>
-    <t>Paludismo (malária)</t>
-  </si>
-  <si>
-    <t>Anemia</t>
-  </si>
-  <si>
     <t>Febre Tifoide</t>
   </si>
   <si>
-    <t>Disenteria</t>
-  </si>
-  <si>
     <t>Positivo</t>
   </si>
   <si>
@@ -414,12 +372,6 @@
     <t>1A40.Z</t>
   </si>
   <si>
-    <t>RA01</t>
-  </si>
-  <si>
-    <t>COVID-19</t>
-  </si>
-  <si>
     <t>CA40.Z</t>
   </si>
   <si>
@@ -429,147 +381,33 @@
     <t>ME05.1</t>
   </si>
   <si>
-    <t>Diarrea</t>
-  </si>
-  <si>
     <t>1B1Z</t>
   </si>
   <si>
-    <t>Tuberculosis</t>
-  </si>
-  <si>
     <t>1C62.Z</t>
   </si>
   <si>
-    <t>HIV</t>
-  </si>
-  <si>
-    <t>DA42.Z</t>
-  </si>
-  <si>
-    <t>Gastritis</t>
-  </si>
-  <si>
-    <t>DB97.Z</t>
-  </si>
-  <si>
-    <t>Hepatitis</t>
-  </si>
-  <si>
     <t>9A60.Z</t>
   </si>
   <si>
-    <t>Conjuntivite</t>
-  </si>
-  <si>
-    <t>1A40.0</t>
-  </si>
-  <si>
-    <t>Gastroentetites</t>
-  </si>
-  <si>
     <t>BA00.Z</t>
   </si>
   <si>
-    <t>Hipertensão arterial</t>
-  </si>
-  <si>
     <t>5A14</t>
   </si>
   <si>
-    <t>Diabetes</t>
-  </si>
-  <si>
-    <t>1A9Z</t>
-  </si>
-  <si>
-    <t>Infecões de transmissão sexual</t>
-  </si>
-  <si>
-    <t>GC08.Z</t>
-  </si>
-  <si>
-    <t>Infecões de tracto urinario</t>
-  </si>
-  <si>
-    <t>GA05.Z</t>
-  </si>
-  <si>
-    <t>CA08.1Y</t>
-  </si>
-  <si>
-    <t>Gravidez</t>
-  </si>
-  <si>
-    <t>ME05.0</t>
-  </si>
-  <si>
-    <t>constipação</t>
-  </si>
-  <si>
-    <t>AA3Z</t>
-  </si>
-  <si>
-    <t>Otitis externa o Media</t>
-  </si>
-  <si>
     <t>CA0Y</t>
   </si>
   <si>
-    <t>Faringoamigdalites</t>
-  </si>
-  <si>
-    <t>FA2Z</t>
-  </si>
-  <si>
-    <t>Atrites</t>
-  </si>
-  <si>
-    <t>ND56.Z</t>
-  </si>
-  <si>
-    <t>Traumatismo</t>
-  </si>
-  <si>
-    <t>8A80.Z</t>
-  </si>
-  <si>
-    <t>Migranha</t>
-  </si>
-  <si>
-    <t>MG27</t>
-  </si>
-  <si>
-    <t>Hemorragia</t>
-  </si>
-  <si>
-    <t>DD5Z</t>
-  </si>
-  <si>
-    <t>Hernias</t>
-  </si>
-  <si>
     <t>4A8Z</t>
   </si>
   <si>
     <t>Alergia</t>
   </si>
   <si>
-    <t>1F28.Z</t>
-  </si>
-  <si>
-    <t>Micosis Superficial</t>
-  </si>
-  <si>
     <t>1B7Y</t>
   </si>
   <si>
-    <t>Infeccoes bacterianas da pele e partes blando</t>
-  </si>
-  <si>
-    <t>Doencas inflamatorias pelvicas</t>
-  </si>
-  <si>
     <t>Buba</t>
   </si>
   <si>
@@ -606,21 +444,12 @@
     <t>DOB_idade</t>
   </si>
   <si>
-    <t>data('DOB_idade')=='1'</t>
-  </si>
-  <si>
-    <t>data('DOB_idade')=='2'</t>
-  </si>
-  <si>
     <t>resultado_tdr</t>
   </si>
   <si>
     <t>calculates.idade_mes()&lt;216 ? "C" : "A"</t>
   </si>
   <si>
-    <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
-  </si>
-  <si>
     <t>SGC</t>
   </si>
   <si>
@@ -666,27 +495,9 @@
     <t>numero_codigo</t>
   </si>
   <si>
-    <t>nota_1</t>
-  </si>
-  <si>
-    <t>data('ano')&lt;5</t>
-  </si>
-  <si>
-    <t>data('DOB_idade')=='2' &amp;&amp; data('ano')&lt;5</t>
-  </si>
-  <si>
-    <t>data('temperatura')&lt;46 &amp; data('temperatura')&gt;25</t>
-  </si>
-  <si>
-    <t>data('peso')&lt;250</t>
-  </si>
-  <si>
     <t>csname</t>
   </si>
   <si>
-    <t>Centro: {{data.csname}} Data: {{calculates.hoje_display}}</t>
-  </si>
-  <si>
     <t>consultor</t>
   </si>
   <si>
@@ -699,12 +510,6 @@
     <t>data('cs') + calculates.child_adult()</t>
   </si>
   <si>
-    <t>Proveniência</t>
-  </si>
-  <si>
-    <t>Outro</t>
-  </si>
-  <si>
     <t>data('diagnostico')=='outro'</t>
   </si>
   <si>
@@ -723,7 +528,400 @@
     <t>Diagnósticos secundarios: Espeficique</t>
   </si>
   <si>
-    <t>outro</t>
+    <t>1B75</t>
+  </si>
+  <si>
+    <t>Abcesso</t>
+  </si>
+  <si>
+    <t>MA01</t>
+  </si>
+  <si>
+    <t>Adenopatias</t>
+  </si>
+  <si>
+    <t>PJ20</t>
+  </si>
+  <si>
+    <t>Agressão física</t>
+  </si>
+  <si>
+    <t>JA40.0</t>
+  </si>
+  <si>
+    <t>Ameaça de aborto</t>
+  </si>
+  <si>
+    <t>CA03020Y</t>
+  </si>
+  <si>
+    <t>Amigdalites/Faringite/Faringamidalites</t>
+  </si>
+  <si>
+    <t>Anemia (ligeira, moderada e grave)</t>
+  </si>
+  <si>
+    <t>CA23</t>
+  </si>
+  <si>
+    <t>Asma Bronquial</t>
+  </si>
+  <si>
+    <t>CA20</t>
+  </si>
+  <si>
+    <t>Bronquites</t>
+  </si>
+  <si>
+    <t>CA07</t>
+  </si>
+  <si>
+    <t>IRA</t>
+  </si>
+  <si>
+    <t>CA20.Y</t>
+  </si>
+  <si>
+    <t>Broncopneumonia</t>
+  </si>
+  <si>
+    <t>CA41</t>
+  </si>
+  <si>
+    <t>Bronquiolites</t>
+  </si>
+  <si>
+    <t>CA00</t>
+  </si>
+  <si>
+    <t>Gripe /Catarro comum/ Resfriado/Constipação</t>
+  </si>
+  <si>
+    <t>1F23.0</t>
+  </si>
+  <si>
+    <t>Candidíase oral</t>
+  </si>
+  <si>
+    <t>1F23.10</t>
+  </si>
+  <si>
+    <t>Candidíase vaginal</t>
+  </si>
+  <si>
+    <t>MD81.4</t>
+  </si>
+  <si>
+    <t>Cólicas abdominal</t>
+  </si>
+  <si>
+    <t>Conjuntivites (Alérgica, Bacteriana, Viral)</t>
+  </si>
+  <si>
+    <t>EB7Y</t>
+  </si>
+  <si>
+    <t>Dermatose</t>
+  </si>
+  <si>
+    <t>Disenteria (Basilar. Amebiana)</t>
+  </si>
+  <si>
+    <t>Diarreia /EDA (Ligeira ou Plano A, Moderada ou Plano B, Grave ou Plano C)</t>
+  </si>
+  <si>
+    <t>Diabetes Melitos (Tipo I, Tipo II)</t>
+  </si>
+  <si>
+    <t>GA34.3</t>
+  </si>
+  <si>
+    <t>Dismenorreia</t>
+  </si>
+  <si>
+    <t>Enterites</t>
+  </si>
+  <si>
+    <t>DA01</t>
+  </si>
+  <si>
+    <t>Estomatites</t>
+  </si>
+  <si>
+    <t>1G04</t>
+  </si>
+  <si>
+    <t>Escabiose</t>
+  </si>
+  <si>
+    <t>1A7Z</t>
+  </si>
+  <si>
+    <t>Gonorreia</t>
+  </si>
+  <si>
+    <t>Hipertensão Arterial</t>
+  </si>
+  <si>
+    <t>BA2Z</t>
+  </si>
+  <si>
+    <t>Hipotensão Arterial</t>
+  </si>
+  <si>
+    <t>JA60.Z</t>
+  </si>
+  <si>
+    <t>Hiperémese Gravídica</t>
+  </si>
+  <si>
+    <t>FB.ME</t>
+  </si>
+  <si>
+    <t>Mialgia/ Lombalgia</t>
+  </si>
+  <si>
+    <t>AAZ1.90</t>
+  </si>
+  <si>
+    <t>Otites (Externo, Media, Purulenta)</t>
+  </si>
+  <si>
+    <t>Paludismo/Malaria (Simples, Grave)</t>
+  </si>
+  <si>
+    <t>1A36.0Z</t>
+  </si>
+  <si>
+    <t>Parasitismo Intestinal</t>
+  </si>
+  <si>
+    <t>Pio dermites</t>
+  </si>
+  <si>
+    <t>1F03</t>
+  </si>
+  <si>
+    <t>Sarampo (suspeita)</t>
+  </si>
+  <si>
+    <t>MG26</t>
+  </si>
+  <si>
+    <t>Síndrome Febril</t>
+  </si>
+  <si>
+    <t>Tuberculose (Suspeita)</t>
+  </si>
+  <si>
+    <t>DA60</t>
+  </si>
+  <si>
+    <t>Ulcera Gástrica</t>
+  </si>
+  <si>
+    <t>GC02</t>
+  </si>
+  <si>
+    <t>Uretrites</t>
+  </si>
+  <si>
+    <t>1A92 </t>
+  </si>
+  <si>
+    <t>Tricomoníase</t>
+  </si>
+  <si>
+    <t>1E90</t>
+  </si>
+  <si>
+    <t>Varicela</t>
+  </si>
+  <si>
+    <t>VIH/Sida</t>
+  </si>
+  <si>
+    <t>otro</t>
+  </si>
+  <si>
+    <t>Outras</t>
+  </si>
+  <si>
+    <t>Amigdalites</t>
+  </si>
+  <si>
+    <t>Faringite</t>
+  </si>
+  <si>
+    <t>Faringamidalites</t>
+  </si>
+  <si>
+    <t>CA03</t>
+  </si>
+  <si>
+    <t>CA02</t>
+  </si>
+  <si>
+    <t>Anemia ligeira</t>
+  </si>
+  <si>
+    <t>Anemia moderada</t>
+  </si>
+  <si>
+    <t>Anemia grave</t>
+  </si>
+  <si>
+    <t>XS5W</t>
+  </si>
+  <si>
+    <t>XS0T</t>
+  </si>
+  <si>
+    <t>XS25</t>
+  </si>
+  <si>
+    <t>Conjuntivites Alérgica</t>
+  </si>
+  <si>
+    <t>Conjuntivites Bacteriana</t>
+  </si>
+  <si>
+    <t>Conjuntivites Viral</t>
+  </si>
+  <si>
+    <t>9A60.02</t>
+  </si>
+  <si>
+    <t>9A60.Y</t>
+  </si>
+  <si>
+    <t>1D84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diarreia /EDA Ligeira ou Plano A </t>
+  </si>
+  <si>
+    <t>Diabetes Melitos Tipo I</t>
+  </si>
+  <si>
+    <t>Diarreia /EDA  Moderada ou Plano B</t>
+  </si>
+  <si>
+    <t>Diabetes MelitosTipo II</t>
+  </si>
+  <si>
+    <t>Diarreia /EDA Grave ou Plano C</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>5A10</t>
+  </si>
+  <si>
+    <t>PB</t>
+  </si>
+  <si>
+    <t>5A11</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Mialgia</t>
+  </si>
+  <si>
+    <t>Otites Externo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paludismo/Malaria Simples </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lombalgia</t>
+  </si>
+  <si>
+    <t>Otites Media</t>
+  </si>
+  <si>
+    <t>Paludismo/Malaria Grave</t>
+  </si>
+  <si>
+    <t>Otites  Purulenta</t>
+  </si>
+  <si>
+    <t>FB56.2</t>
+  </si>
+  <si>
+    <t>AA1Z</t>
+  </si>
+  <si>
+    <t>1F4.S</t>
+  </si>
+  <si>
+    <t>ME84.2</t>
+  </si>
+  <si>
+    <t>AA80</t>
+  </si>
+  <si>
+    <t>1F4.G</t>
+  </si>
+  <si>
+    <t>AA90</t>
+  </si>
+  <si>
+    <t>esp</t>
+  </si>
+  <si>
+    <t>Especifique</t>
+  </si>
+  <si>
+    <t>subdx</t>
+  </si>
+  <si>
+    <t>saida</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Fuga</t>
+  </si>
+  <si>
+    <t>Óbito</t>
+  </si>
+  <si>
+    <t>Transferido</t>
+  </si>
+  <si>
+    <t>Desconhecido</t>
+  </si>
+  <si>
+    <t>sub_dx</t>
+  </si>
+  <si>
+    <t>sub_dx2</t>
+  </si>
+  <si>
+    <t>choice_item.diagnostico === data('diagno_secund')</t>
+  </si>
+  <si>
+    <t>Paciente foi:</t>
+  </si>
+  <si>
+    <t>data('hospitaliza')==2</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>especifique:</t>
+  </si>
+  <si>
+    <t>choice_list_name.diagnostico === data('diagnostico')</t>
+  </si>
+  <si>
+    <t>(data('temperatura')&lt;46 &amp; data('temperatura')&gt;25) || !data('temperatura')</t>
   </si>
 </sst>
 </file>
@@ -798,12 +996,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -849,7 +1053,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -909,9 +1113,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1363,7 +1584,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1379,7 +1600,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1387,15 +1608,15 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1411,7 +1632,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y106"/>
+  <dimension ref="A1:AA93"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1419,22 +1640,24 @@
     <col min="3" max="3" width="33.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.375" style="12" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.75" style="11" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="11" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.125" style="2" customWidth="1"/>
     <col min="9" max="9" width="29.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="24.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.75" style="7"/>
     <col min="12" max="12" width="28.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17" style="2" customWidth="1"/>
-    <col min="14" max="14" width="60" style="2" customWidth="1"/>
-    <col min="15" max="16" width="15.625" customWidth="1"/>
-    <col min="17" max="16384" width="10.75" style="2"/>
+    <col min="13" max="13" width="13.25" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17" style="2" customWidth="1"/>
+    <col min="15" max="15" width="60" style="2" customWidth="1"/>
+    <col min="16" max="16" width="43.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="15.625" customWidth="1"/>
+    <col min="19" max="16384" width="10.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
@@ -1455,7 +1678,7 @@
         <v>20</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
         <v>21</v>
@@ -1470,46 +1693,52 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
+        <v>292</v>
+      </c>
+      <c r="N1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="S1" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>33</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>34</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>35</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>36</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>37</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>38</v>
       </c>
-      <c r="W1" t="s">
-        <v>39</v>
-      </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="12"/>
@@ -1519,7 +1748,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="12"/>
@@ -1529,7 +1758,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="12"/>
@@ -1539,612 +1768,556 @@
       <c r="J4" s="1"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C5" s="11"/>
+      <c r="D5" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="W6" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="2"/>
-      <c r="R7"/>
-      <c r="S7"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C8" s="11"/>
+      <c r="O5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:27" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="2" t="b">
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C10" s="11"/>
+      <c r="D10" s="9"/>
+      <c r="E10"/>
+      <c r="F10" s="18"/>
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="12"/>
-      <c r="D10" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C12" s="11"/>
       <c r="D12" s="12" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>211</v>
-      </c>
+      <c r="C13" s="11"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
-      <c r="L13" s="11"/>
-    </row>
-    <row r="14" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C14" s="11"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="12"/>
+        <v>144</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="F14" s="12" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C16" s="12"/>
+      <c r="D16" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="11"/>
+        <v>52</v>
+      </c>
+      <c r="C17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C19" s="11"/>
+    <row r="18" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C22" s="11"/>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C20" s="11"/>
+      <c r="D20" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" s="2" t="b">
+        <v>163</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="M22" s="12"/>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="2:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="29"/>
+      <c r="D24" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="K24" s="31"/>
+      <c r="P24" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C25" s="12"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J26" s="7"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C23" s="11"/>
-      <c r="D23" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="11"/>
-      <c r="D24" s="12" t="s">
+      <c r="T26"/>
+      <c r="U26"/>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="D27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="2"/>
+      <c r="T27"/>
+      <c r="U27"/>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="2"/>
+      <c r="T28"/>
+      <c r="U28"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+      <c r="E29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="2"/>
+      <c r="T29"/>
+      <c r="U29"/>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="2"/>
+      <c r="T30"/>
+      <c r="U30"/>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="D31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="2"/>
+      <c r="T31"/>
+      <c r="U31"/>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C32" s="11"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+      <c r="B33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D34" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+      <c r="D35" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" ht="63" x14ac:dyDescent="0.25">
-      <c r="D26" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C29" s="11"/>
-      <c r="D29" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="N29" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C30" s="11"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D32" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="L32" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C33" s="11"/>
-      <c r="D33" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33"/>
-      <c r="F33" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" t="s">
-        <v>221</v>
-      </c>
-      <c r="L33" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C34" s="12"/>
-      <c r="D34" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L34" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C35" s="11"/>
-      <c r="D35" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="L35" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C36" s="12"/>
-      <c r="D36" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L36" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C38" s="12"/>
-      <c r="D38" s="12" t="s">
-        <v>64</v>
-      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D37" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C38" s="11"/>
       <c r="E38" s="12"/>
-      <c r="F38" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="12"/>
-      <c r="E39" s="12"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C39" s="11"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C40" s="11"/>
-      <c r="D40" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="E41" s="12"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C41" s="11"/>
+      <c r="E41" s="13"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C42" s="12"/>
-      <c r="D42" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="12"/>
-      <c r="E43" s="12"/>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C42" s="11"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C43" s="11"/>
+      <c r="E43" s="13"/>
       <c r="F43" s="12"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J44" s="7"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R44"/>
-      <c r="S44"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" s="11"/>
-      <c r="E45" s="12"/>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C44" s="11"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C45" s="12"/>
+      <c r="E45" s="13"/>
       <c r="F45" s="12"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46" s="2" t="s">
-        <v>53</v>
-      </c>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C46" s="11"/>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D47" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-      <c r="D48" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>113</v>
-      </c>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C47" s="11"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="K49" s="6"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D50" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="K50" s="6"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C51" s="11"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C52" s="11"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="15"/>
       <c r="E52" s="13"/>
-      <c r="F52" s="12"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C53" s="11"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="15"/>
       <c r="E53" s="13"/>
-      <c r="F53" s="12"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C54" s="11"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="15"/>
       <c r="E54" s="13"/>
-      <c r="F54" s="12"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C55" s="11"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="15"/>
       <c r="E55" s="13"/>
-      <c r="F55" s="12"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C56" s="11"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="12"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="13"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C57" s="11"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="12"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="13"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="15"/>
       <c r="E58" s="13"/>
-      <c r="F58" s="12"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C59" s="11"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C60" s="11"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="13"/>
@@ -2163,7 +2336,6 @@
       <c r="F62" s="16"/>
       <c r="G62" s="13"/>
       <c r="H62" s="13"/>
-      <c r="K62" s="6"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="13"/>
@@ -2173,7 +2345,6 @@
       <c r="F63" s="16"/>
       <c r="G63" s="13"/>
       <c r="H63" s="13"/>
-      <c r="K63" s="6"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="13"/>
@@ -2184,134 +2355,82 @@
       <c r="G64" s="13"/>
       <c r="H64" s="13"/>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="13"/>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="13"/>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="12"/>
+    </row>
+    <row r="66" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="12"/>
+    </row>
+    <row r="67" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="12"/>
+    </row>
+    <row r="70" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="12"/>
+    </row>
+    <row r="72" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="12"/>
+    </row>
+    <row r="73" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
       <c r="F78" s="12"/>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
       <c r="F79" s="12"/>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D80" s="11"/>
       <c r="E80" s="11"/>
       <c r="F80" s="12"/>
@@ -2381,80 +2500,15 @@
       <c r="E93" s="11"/>
       <c r="F93" s="12"/>
     </row>
-    <row r="94" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="12"/>
-    </row>
-    <row r="95" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="12"/>
-    </row>
-    <row r="96" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="12"/>
-    </row>
-    <row r="97" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="12"/>
-    </row>
-    <row r="98" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="12"/>
-    </row>
-    <row r="99" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="12"/>
-    </row>
-    <row r="100" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="12"/>
-    </row>
-    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="12"/>
-    </row>
-    <row r="102" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="12"/>
-    </row>
-    <row r="103" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="12"/>
-    </row>
-    <row r="104" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="12"/>
-    </row>
-    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="12"/>
-    </row>
-    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="12"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2469,7 +2523,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr defaultColWidth="21.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.75" style="2" customWidth="1"/>
@@ -2478,7 +2532,7 @@
     <col min="5" max="16384" width="21.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -2488,8 +2542,11 @@
       <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -2497,10 +2554,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -2508,158 +2565,158 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>196</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2667,531 +2724,884 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>129</v>
+        <v>172</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>131</v>
+        <v>109</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>135</v>
+        <v>177</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>183</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>149</v>
+        <v>189</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>158</v>
+        <v>114</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>162</v>
+        <v>199</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>168</v>
+        <v>204</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>170</v>
+        <v>110</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="C55" s="1"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="C56" s="1"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="C58" s="1"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="C59" s="1"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="C60" s="1"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="C63" s="1"/>
+      <c r="A63" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="C64" s="1"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="C65" s="1"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="C66" s="1"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="C69" s="1"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="C70" s="1"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="C71" s="1"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="C72" s="1"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="C73" s="1"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-      <c r="C74" s="1"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-      <c r="C75" s="1"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="C76" s="1"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="C77" s="1"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="C78" s="1"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-      <c r="C79" s="1"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="C80" s="1"/>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="C81" s="1"/>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="C82" s="1"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-      <c r="C83" s="1"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-      <c r="C84" s="1"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
-      <c r="C85" s="1"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-      <c r="C86" s="1"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="C87" s="1"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="C88" s="1"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="C89" s="1"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="C90" s="1"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-      <c r="C91" s="1"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="D70" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="C71" t="s">
+        <v>238</v>
+      </c>
+      <c r="D71" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C72" t="s">
+        <v>239</v>
+      </c>
+      <c r="D72" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>248</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C77" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>254</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C83" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B84" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="D84" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C85" t="s">
+        <v>267</v>
+      </c>
+      <c r="D85" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B86" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D86" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="D87" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B88" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="C88" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="D88" t="s">
+        <v>215</v>
+      </c>
+      <c r="E88" s="27"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="C89" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="D89" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C90" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="D90" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C91" s="25" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
-      <c r="C92" s="1"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="C93" s="1"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="C94" s="1"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="C95" s="1"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
-      <c r="C96" s="1"/>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B95" s="2">
+        <v>1</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B96" s="2">
+        <v>2</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1"/>
-      <c r="C97" s="1"/>
+      <c r="A97" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B97" s="2">
+        <v>3</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="1"/>
-      <c r="C98" s="1"/>
+      <c r="A98" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B98" s="2">
+        <v>4</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="1"/>
-      <c r="C99" s="1"/>
+      <c r="A99" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B99" s="2">
+        <v>5</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
-      <c r="C100" s="1"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
@@ -3251,26 +3661,26 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
-      <c r="C115" s="1"/>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="1"/>
-      <c r="C116" s="1"/>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="1"/>
-      <c r="C117" s="1"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="1"/>
-      <c r="C118" s="1"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
-      <c r="C119" s="1"/>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="1"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="1"/>
+      <c r="C191" s="1"/>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="1"/>
+      <c r="C192" s="1"/>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="1"/>
+      <c r="C193" s="1"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="1"/>
+      <c r="C194" s="1"/>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="1"/>
+      <c r="C195" s="1"/>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
@@ -3348,27 +3758,10 @@
       <c r="A214" s="1"/>
       <c r="C214" s="1"/>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="1"/>
-      <c r="C215" s="1"/>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="1"/>
-      <c r="C216" s="1"/>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="1"/>
-      <c r="C217" s="1"/>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="1"/>
-      <c r="C218" s="1"/>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="1"/>
-      <c r="C219" s="1"/>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B22:C52">
+    <sortCondition ref="C22:C52"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <extLst>
@@ -3399,63 +3792,63 @@
   <sheetData>
     <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="J1" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="G2" t="s">
-        <v>206</v>
+        <v>149</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -3480,44 +3873,44 @@
   <sheetData>
     <row r="1" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3536,50 +3929,50 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
         <v>31</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>218</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>219</v>
+        <v>156</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3627,10 +4020,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3638,7 +4031,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>198</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3646,15 +4039,15 @@
         <v>10</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3662,7 +4055,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3670,20 +4063,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>23</v>
@@ -3691,10 +4084,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3710,23 +4103,23 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3734,31 +4127,31 @@
         <v>10</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>201</v>
+        <v>144</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>201</v>
+        <v>144</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3766,7 +4159,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3774,15 +4167,15 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3790,39 +4183,39 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>215</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>217</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>225</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>226</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45895126-525A-451F-BA33-EA3C2D272FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CECAF4B-7D85-49CF-905A-3800778C825A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="310">
   <si>
     <t>type</t>
   </si>
@@ -922,6 +922,68 @@
   </si>
   <si>
     <t>(data('temperatura')&lt;46 &amp; data('temperatura')&gt;25) || !data('temperatura')</t>
+  </si>
+  <si>
+    <t>lab</t>
+  </si>
+  <si>
+    <t>Inicias de Laboratorista</t>
+  </si>
+  <si>
+    <t>med</t>
+  </si>
+  <si>
+    <t>inicias de medico assistente</t>
+  </si>
+  <si>
+    <t>envio_tdr</t>
+  </si>
+  <si>
+    <t>inq</t>
+  </si>
+  <si>
+    <t>dx_csv</t>
+  </si>
+  <si>
+    <t>csv</t>
+  </si>
+  <si>
+    <t>"dx.csv"</t>
+  </si>
+  <si>
+    <t>_.chain(context).pluck('diagnostico').uniq().map(function(diagnostico){
+return {data_value:diagnostico, display:{title: {text: diagnostico_label} } };
+}).value()</t>
+  </si>
+  <si>
+    <t>sub_csv</t>
+  </si>
+  <si>
+    <t>_.chain(context)
+.uniq(function(x){return x.sub;})
+.map(function(place){
+    return {
+        data_value:place.sub, 
+        diagnostico: place.diagnostico,
+        display:{title: {text: place.sub} }
+    } 
+    })
+.value()</t>
+  </si>
+  <si>
+    <t>subdx_csv</t>
+  </si>
+  <si>
+    <t>_.chain(context)
+.map(function(place){
+    return {
+        data_value:place.subdx, 
+        diagnostico: place.diagnostico,
+        sub: place.sub,
+               display:{title: {text: place.subdx_label} }
+    } 
+    })
+.value()</t>
   </si>
 </sst>
 </file>
@@ -1592,7 +1654,7 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2022010501</v>
+        <v>2022022800</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1877,7 +1939,7 @@
         <v>144</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>96</v>
+        <v>302</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>96</v>
@@ -1930,7 +1992,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>287</v>
@@ -1953,7 +2015,7 @@
         <v>144</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>96</v>
+        <v>302</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>98</v>
@@ -2140,29 +2202,45 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C37" s="11"/>
       <c r="D37" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>146</v>
+        <v>58</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="12" t="s">
+        <v>296</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>74</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C38" s="11"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
+      <c r="D38" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C39" s="11"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="12"/>
+      <c r="D39" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C40" s="11"/>
-      <c r="E40" s="13"/>
+      <c r="E40" s="12"/>
       <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3775,7 +3853,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C574FB-861C-4A83-BA50-230986D05032}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
@@ -3851,8 +3929,48 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H3" s="22"/>
+    <row r="3" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="J3" t="s">
+        <v>304</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4" t="s">
+        <v>303</v>
+      </c>
+      <c r="J4" t="s">
+        <v>304</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" t="s">
+        <v>303</v>
+      </c>
+      <c r="J5" t="s">
+        <v>304</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>309</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4003,7 +4121,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -4216,6 +4334,38 @@
       </c>
       <c r="B26" s="12" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CECAF4B-7D85-49CF-905A-3800778C825A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DD2B77-CD4C-4C5C-919E-41C6AB5B581D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -951,11 +951,6 @@
     <t>"dx.csv"</t>
   </si>
   <si>
-    <t>_.chain(context).pluck('diagnostico').uniq().map(function(diagnostico){
-return {data_value:diagnostico, display:{title: {text: diagnostico_label} } };
-}).value()</t>
-  </si>
-  <si>
     <t>sub_csv</t>
   </si>
   <si>
@@ -984,6 +979,11 @@
     } 
     })
 .value()</t>
+  </si>
+  <si>
+    <t>_.chain(context).pluck('diagnostico').uniq().map(function(diagnostico){
+return {data_value:diagnostico, display:{title: {text: diagnostico} } };
+}).value()</t>
   </si>
 </sst>
 </file>
@@ -1936,7 +1936,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>302</v>
@@ -1992,7 +1992,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>287</v>
@@ -3929,7 +3929,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>302</v>
       </c>
@@ -3941,12 +3941,12 @@
         <v>304</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B4" t="s">
         <v>303</v>
@@ -3955,12 +3955,12 @@
         <v>304</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B5" t="s">
         <v>303</v>
@@ -3969,7 +3969,7 @@
         <v>304</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DD2B77-CD4C-4C5C-919E-41C6AB5B581D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F031470E-1D7F-4AEF-976A-EBE43A62E490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="model" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">survey!$D$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">survey!$D$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="310">
   <si>
     <t>type</t>
   </si>
@@ -918,9 +918,6 @@
     <t>especifique:</t>
   </si>
   <si>
-    <t>choice_list_name.diagnostico === data('diagnostico')</t>
-  </si>
-  <si>
     <t>(data('temperatura')&lt;46 &amp; data('temperatura')&gt;25) || !data('temperatura')</t>
   </si>
   <si>
@@ -951,46 +948,39 @@
     <t>"dx.csv"</t>
   </si>
   <si>
-    <t>sub_csv</t>
+    <t>subdx_csv</t>
+  </si>
+  <si>
+    <t>_.chain(context).uniq(x =&gt; x.diagnostico).map(function(x){
+return {data_value:x.diagnostico, display:{title: {text: x.diagnostico_label} } };
+}).value()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if </t>
+  </si>
+  <si>
+    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "otro"].indexOf(data('diagnostico'))&lt;0</t>
   </si>
   <si>
     <t>_.chain(context)
-.uniq(function(x){return x.sub;})
-.map(function(place){
+.map(function(x){
     return {
-        data_value:place.sub, 
-        diagnostico: place.diagnostico,
-        display:{title: {text: place.sub} }
+        data_value:x.subdx, 
+        diagnostico: x.diagnostico,
+        display:{title: {text: x.subdx_label} }
     } 
     })
 .value()</t>
   </si>
   <si>
-    <t>subdx_csv</t>
-  </si>
-  <si>
-    <t>_.chain(context)
-.map(function(place){
-    return {
-        data_value:place.subdx, 
-        diagnostico: place.diagnostico,
-        sub: place.sub,
-               display:{title: {text: place.subdx_label} }
-    } 
-    })
-.value()</t>
-  </si>
-  <si>
-    <t>_.chain(context).pluck('diagnostico').uniq().map(function(diagnostico){
-return {data_value:diagnostico, display:{title: {text: diagnostico} } };
-}).value()</t>
+    <t>choice_item.diagnostico === data('diagnostico')</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1024,13 +1014,6 @@
       <u/>
       <sz val="12"/>
       <color theme="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF404040"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1115,7 +1098,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1165,13 +1148,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1694,30 +1676,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA93"/>
+  <dimension ref="A1:Z97"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="33.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="48.125" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.375" style="12" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5" style="11" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="29.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="24.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.75" style="7"/>
-    <col min="12" max="12" width="28.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="13.25" style="2" customWidth="1"/>
-    <col min="14" max="14" width="17" style="2" customWidth="1"/>
-    <col min="15" max="15" width="60" style="2" customWidth="1"/>
-    <col min="16" max="16" width="43.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="15.625" customWidth="1"/>
-    <col min="19" max="16384" width="10.75" style="2"/>
+    <col min="8" max="8" width="29.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="24.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.75" style="7"/>
+    <col min="11" max="11" width="28.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.25" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17" style="2" customWidth="1"/>
+    <col min="14" max="14" width="60" style="2" customWidth="1"/>
+    <col min="15" max="15" width="59.25" style="2" customWidth="1"/>
+    <col min="16" max="17" width="15.625" customWidth="1"/>
+    <col min="18" max="16384" width="10.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>61</v>
       </c>
@@ -1739,111 +1720,105 @@
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" t="s">
+        <v>292</v>
+      </c>
+      <c r="M1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q1" s="20" t="s">
+      <c r="P1" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="Q1" s="19" t="s">
         <v>82</v>
       </c>
+      <c r="R1" t="s">
+        <v>32</v>
+      </c>
       <c r="S1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="Z1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="12"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="12"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="12"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="24"/>
+      <c r="E5" s="23"/>
       <c r="F5" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>50</v>
       </c>
@@ -1854,10 +1829,9 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:27" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
@@ -1865,7 +1839,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D8" s="12" t="s">
         <v>10</v>
       </c>
@@ -1879,19 +1853,19 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C10" s="11"/>
       <c r="D10" s="9"/>
       <c r="E10"/>
-      <c r="F10" s="18"/>
+      <c r="F10" s="17"/>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
         <v>10</v>
@@ -1905,11 +1879,11 @@
       <c r="G11" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L11" s="2" t="b">
+      <c r="K11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C12" s="11"/>
       <c r="D12" s="12" t="s">
         <v>90</v>
@@ -1921,11 +1895,11 @@
       <c r="G12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I12" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>51</v>
       </c>
@@ -1933,13 +1907,13 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>96</v>
@@ -1947,11 +1921,11 @@
       <c r="G14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L14" s="2" t="b">
+      <c r="K14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
@@ -1961,7 +1935,7 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
         <v>58</v>
@@ -1973,12 +1947,12 @@
       <c r="G16" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="K16" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="M16" s="12"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>52</v>
       </c>
@@ -1986,529 +1960,520 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C18" s="12"/>
-      <c r="D18" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="2:20" ht="126" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="F18" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C20" s="11"/>
+    <row r="20" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>302</v>
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>98</v>
+        <v>287</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="12"/>
     </row>
-    <row r="22" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C22" s="12"/>
-      <c r="D22" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="M22" s="12"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="2:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="29"/>
-      <c r="D24" s="29" t="s">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C24" s="11"/>
+      <c r="D24" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="2:20" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C26" s="12"/>
+      <c r="D26" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="2:20" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="28"/>
+      <c r="D28" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E28" s="29" t="s">
         <v>280</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="K24" s="31"/>
-      <c r="P24" s="28" t="s">
+      <c r="J28" s="30"/>
+      <c r="O28" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C25" s="12"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="D26" s="2" t="s">
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C29" s="12"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2" t="b">
+      <c r="I30" s="7"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T26"/>
-      <c r="U26"/>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="D27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="2"/>
-      <c r="T27"/>
-      <c r="U27"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="2"/>
-      <c r="T28"/>
-      <c r="U28"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="2"/>
-      <c r="T29"/>
-      <c r="U29"/>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="2"/>
+      <c r="S30"/>
       <c r="T30"/>
-      <c r="U30"/>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="D31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="2"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="2"/>
+      <c r="S31"/>
       <c r="T31"/>
-      <c r="U31"/>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C32" s="11"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33"/>
-      <c r="B33" s="2" t="s">
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="2"/>
+      <c r="S32"/>
+      <c r="T32"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I33" s="7"/>
+      <c r="J33" s="2"/>
+      <c r="S33"/>
+      <c r="T33"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="2"/>
+      <c r="S34"/>
+      <c r="T34"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="2"/>
+      <c r="S35"/>
+      <c r="T35"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C36" s="11"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D34" s="12" t="s">
+      <c r="C37" s="11"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D38" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F38" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35"/>
-      <c r="D35" s="12" t="s">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="D39" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="11"/>
-      <c r="D37" s="12" t="s">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C41" s="11"/>
+      <c r="D41" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="12" t="s">
+      <c r="E41" s="13"/>
+      <c r="F41" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G37" s="2" t="s">
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C42" s="11"/>
+      <c r="D42" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="13"/>
+      <c r="F42" s="12" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="11"/>
-      <c r="D38" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="12" t="s">
+      <c r="G42" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D39" s="12" t="s">
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D43" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F43" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G43" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C40" s="11"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C41" s="11"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C42" s="11"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="12"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C43" s="11"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="12"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C44" s="11"/>
-      <c r="E44" s="13"/>
+      <c r="E44" s="12"/>
       <c r="F44" s="12"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C45" s="12"/>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C45" s="11"/>
       <c r="E45" s="13"/>
       <c r="F45" s="12"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C46" s="11"/>
-      <c r="E46" s="12"/>
+      <c r="E46" s="13"/>
       <c r="F46" s="12"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C47" s="11"/>
-      <c r="E47" s="12"/>
+      <c r="E47" s="13"/>
       <c r="F47" s="12"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="15"/>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C48" s="11"/>
       <c r="E48" s="13"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="15"/>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C49" s="12"/>
       <c r="E49" s="13"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="K49" s="6"/>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="K50" s="6"/>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F49" s="12"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C50" s="11"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C51" s="11"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="15"/>
       <c r="E52" s="13"/>
       <c r="F52" s="16"/>
       <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="15"/>
       <c r="E53" s="13"/>
       <c r="F53" s="16"/>
       <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="J53" s="6"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="15"/>
       <c r="E54" s="13"/>
       <c r="F54" s="16"/>
       <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="J54" s="6"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
       <c r="D55" s="15"/>
       <c r="E55" s="13"/>
       <c r="F55" s="16"/>
       <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56" s="33"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="33"/>
-      <c r="H56" s="13"/>
-    </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B57" s="33"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="13"/>
-    </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="13"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="13"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="13"/>
       <c r="C58" s="13"/>
       <c r="D58" s="15"/>
       <c r="E58" s="13"/>
       <c r="F58" s="16"/>
       <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
       <c r="D59" s="15"/>
       <c r="E59" s="13"/>
       <c r="F59" s="16"/>
       <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-    </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="32"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="32"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="15"/>
       <c r="E62" s="13"/>
       <c r="F62" s="16"/>
       <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="13"/>
       <c r="C63" s="13"/>
       <c r="D63" s="15"/>
       <c r="E63" s="13"/>
       <c r="F63" s="16"/>
       <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
       <c r="D64" s="15"/>
       <c r="E64" s="13"/>
       <c r="F64" s="16"/>
       <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-    </row>
-    <row r="65" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="12"/>
-    </row>
-    <row r="66" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="12"/>
-    </row>
-    <row r="67" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="12"/>
-    </row>
-    <row r="68" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="12"/>
-    </row>
-    <row r="69" spans="4:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="13"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="13"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="13"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="13"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
       <c r="F69" s="12"/>
     </row>
-    <row r="70" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
       <c r="F70" s="12"/>
     </row>
-    <row r="71" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D71" s="11"/>
       <c r="E71" s="11"/>
       <c r="F71" s="12"/>
     </row>
-    <row r="72" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
       <c r="F72" s="12"/>
     </row>
-    <row r="73" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
       <c r="F73" s="12"/>
     </row>
-    <row r="74" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D74" s="11"/>
       <c r="E74" s="11"/>
       <c r="F74" s="12"/>
     </row>
-    <row r="75" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="12"/>
     </row>
-    <row r="76" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="12"/>
     </row>
-    <row r="77" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
       <c r="F77" s="12"/>
     </row>
-    <row r="78" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
       <c r="F78" s="12"/>
     </row>
-    <row r="79" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
       <c r="F79" s="12"/>
     </row>
-    <row r="80" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D80" s="11"/>
       <c r="E80" s="11"/>
       <c r="F80" s="12"/>
@@ -2578,15 +2543,35 @@
       <c r="E93" s="11"/>
       <c r="F93" s="12"/>
     </row>
+    <row r="94" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="12"/>
+    </row>
+    <row r="95" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="12"/>
+    </row>
+    <row r="96" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="12"/>
+    </row>
+    <row r="97" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="D1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -3311,10 +3296,10 @@
       <c r="A70" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="24" t="s">
         <v>237</v>
       </c>
       <c r="D70" t="s">
@@ -3325,7 +3310,7 @@
       <c r="A71" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="26" t="s">
         <v>241</v>
       </c>
       <c r="C71" t="s">
@@ -3353,10 +3338,10 @@
       <c r="A73" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B73" s="26" t="s">
+      <c r="B73" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="C73" s="25" t="s">
+      <c r="C73" s="24" t="s">
         <v>242</v>
       </c>
       <c r="D73" s="2" t="s">
@@ -3367,10 +3352,10 @@
       <c r="A74" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B74" s="26" t="s">
+      <c r="B74" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="C74" s="25" t="s">
+      <c r="C74" s="24" t="s">
         <v>243</v>
       </c>
       <c r="D74" s="2" t="s">
@@ -3381,10 +3366,10 @@
       <c r="A75" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B75" s="26" t="s">
+      <c r="B75" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="C75" s="25" t="s">
+      <c r="C75" s="24" t="s">
         <v>244</v>
       </c>
       <c r="D75" s="2" t="s">
@@ -3395,10 +3380,10 @@
       <c r="A76" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C76" s="25" t="s">
+      <c r="C76" s="24" t="s">
         <v>248</v>
       </c>
       <c r="D76" s="2" t="s">
@@ -3409,10 +3394,10 @@
       <c r="A77" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="C77" s="25" t="s">
+      <c r="C77" s="24" t="s">
         <v>249</v>
       </c>
       <c r="D77" s="2" t="s">
@@ -3423,10 +3408,10 @@
       <c r="A78" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B78" s="27" t="s">
+      <c r="B78" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="C78" s="25" t="s">
+      <c r="C78" s="24" t="s">
         <v>250</v>
       </c>
       <c r="D78" s="2" t="s">
@@ -3437,10 +3422,10 @@
       <c r="A79" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B79" s="27" t="s">
+      <c r="B79" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="C79" s="25" t="s">
+      <c r="C79" s="24" t="s">
         <v>254</v>
       </c>
       <c r="D79" s="2" t="s">
@@ -3451,10 +3436,10 @@
       <c r="A80" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="25" t="s">
+      <c r="C80" s="24" t="s">
         <v>256</v>
       </c>
       <c r="D80" s="2" t="s">
@@ -3465,10 +3450,10 @@
       <c r="A81" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C81" s="24" t="s">
         <v>258</v>
       </c>
       <c r="D81" s="2" t="s">
@@ -3479,10 +3464,10 @@
       <c r="A82" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B82" s="27" t="s">
+      <c r="B82" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="C82" s="25" t="s">
+      <c r="C82" s="24" t="s">
         <v>255</v>
       </c>
       <c r="D82" s="2" t="s">
@@ -3493,10 +3478,10 @@
       <c r="A83" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="C83" s="25" t="s">
+      <c r="C83" s="24" t="s">
         <v>257</v>
       </c>
       <c r="D83" s="2" t="s">
@@ -3507,10 +3492,10 @@
       <c r="A84" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B84" s="27" t="s">
+      <c r="B84" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="C84" s="25" t="s">
+      <c r="C84" s="24" t="s">
         <v>264</v>
       </c>
       <c r="D84" t="s">
@@ -3521,7 +3506,7 @@
       <c r="A85" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="26" t="s">
         <v>274</v>
       </c>
       <c r="C85" t="s">
@@ -3535,10 +3520,10 @@
       <c r="A86" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B86" s="27" t="s">
+      <c r="B86" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="C86" s="25" t="s">
+      <c r="C86" s="24" t="s">
         <v>265</v>
       </c>
       <c r="D86" t="s">
@@ -3549,10 +3534,10 @@
       <c r="A87" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="C87" s="25" t="s">
+      <c r="C87" s="24" t="s">
         <v>268</v>
       </c>
       <c r="D87" t="s">
@@ -3563,25 +3548,25 @@
       <c r="A88" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="C88" s="25" t="s">
+      <c r="C88" s="24" t="s">
         <v>270</v>
       </c>
       <c r="D88" t="s">
         <v>215</v>
       </c>
-      <c r="E88" s="27"/>
+      <c r="E88" s="26"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="C89" s="25" t="s">
+      <c r="C89" s="24" t="s">
         <v>266</v>
       </c>
       <c r="D89" t="s">
@@ -3592,10 +3577,10 @@
       <c r="A90" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="C90" s="25" t="s">
+      <c r="C90" s="24" t="s">
         <v>269</v>
       </c>
       <c r="D90" t="s">
@@ -3609,7 +3594,7 @@
       <c r="B91" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C91" s="25" t="s">
+      <c r="C91" s="24" t="s">
         <v>279</v>
       </c>
     </row>
@@ -3853,7 +3838,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C574FB-861C-4A83-BA50-230986D05032}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
@@ -3861,45 +3846,45 @@
     <col min="3" max="3" width="15.125" customWidth="1"/>
     <col min="4" max="4" width="15.375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="6" max="6" width="45.375" customWidth="1"/>
     <col min="7" max="7" width="167.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="46.5" customWidth="1"/>
     <col min="10" max="10" width="22.125" customWidth="1"/>
-    <col min="11" max="11" width="61" customWidth="1"/>
+    <col min="11" max="11" width="87.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="22" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3925,50 +3910,36 @@
       <c r="G2" t="s">
         <v>149</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="63" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B3" t="s">
         <v>302</v>
-      </c>
-      <c r="B3" t="s">
-        <v>303</v>
       </c>
       <c r="D3" s="2"/>
       <c r="J3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>304</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>305</v>
-      </c>
       <c r="B4" t="s">
+        <v>302</v>
+      </c>
+      <c r="J4" t="s">
         <v>303</v>
       </c>
-      <c r="J4" t="s">
-        <v>304</v>
-      </c>
       <c r="K4" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B5" t="s">
-        <v>303</v>
-      </c>
-      <c r="J5" t="s">
-        <v>304</v>
-      </c>
-      <c r="K5" s="2" t="s">
         <v>308</v>
       </c>
     </row>
@@ -3989,17 +3960,17 @@
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4129,10 +4100,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4236,7 +4207,7 @@
       <c r="A14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4341,7 +4312,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4349,7 +4320,7 @@
         <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -4357,7 +4328,7 @@
         <v>58</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -4365,7 +4336,7 @@
         <v>58</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F031470E-1D7F-4AEF-976A-EBE43A62E490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FA5717-D633-4A7D-AA2E-0E60BE19C3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="177">
   <si>
     <t>type</t>
   </si>
@@ -345,9 +345,6 @@
     <t>resultado</t>
   </si>
   <si>
-    <t>Febre Tifoide</t>
-  </si>
-  <si>
     <t>Positivo</t>
   </si>
   <si>
@@ -360,54 +357,6 @@
     <t>Inválido</t>
   </si>
   <si>
-    <t>1F4Z</t>
-  </si>
-  <si>
-    <t>3A9Z</t>
-  </si>
-  <si>
-    <t>1A07.Z</t>
-  </si>
-  <si>
-    <t>1A40.Z</t>
-  </si>
-  <si>
-    <t>CA40.Z</t>
-  </si>
-  <si>
-    <t>Pneumonia</t>
-  </si>
-  <si>
-    <t>ME05.1</t>
-  </si>
-  <si>
-    <t>1B1Z</t>
-  </si>
-  <si>
-    <t>1C62.Z</t>
-  </si>
-  <si>
-    <t>9A60.Z</t>
-  </si>
-  <si>
-    <t>BA00.Z</t>
-  </si>
-  <si>
-    <t>5A14</t>
-  </si>
-  <si>
-    <t>CA0Y</t>
-  </si>
-  <si>
-    <t>4A8Z</t>
-  </si>
-  <si>
-    <t>Alergia</t>
-  </si>
-  <si>
-    <t>1B7Y</t>
-  </si>
-  <si>
     <t>Buba</t>
   </si>
   <si>
@@ -468,9 +417,6 @@
     <t>id_formssentinela</t>
   </si>
   <si>
-    <t>select_one_dropdown</t>
-  </si>
-  <si>
     <t>data('sexo')=='2' &amp;&amp; (calculates.idade_mes()&lt;=660 &amp;&amp; calculates.idade_mes()&gt;=144)</t>
   </si>
   <si>
@@ -528,357 +474,9 @@
     <t>Diagnósticos secundarios: Espeficique</t>
   </si>
   <si>
-    <t>1B75</t>
-  </si>
-  <si>
-    <t>Abcesso</t>
-  </si>
-  <si>
-    <t>MA01</t>
-  </si>
-  <si>
-    <t>Adenopatias</t>
-  </si>
-  <si>
-    <t>PJ20</t>
-  </si>
-  <si>
-    <t>Agressão física</t>
-  </si>
-  <si>
-    <t>JA40.0</t>
-  </si>
-  <si>
-    <t>Ameaça de aborto</t>
-  </si>
-  <si>
-    <t>CA03020Y</t>
-  </si>
-  <si>
-    <t>Amigdalites/Faringite/Faringamidalites</t>
-  </si>
-  <si>
-    <t>Anemia (ligeira, moderada e grave)</t>
-  </si>
-  <si>
-    <t>CA23</t>
-  </si>
-  <si>
-    <t>Asma Bronquial</t>
-  </si>
-  <si>
-    <t>CA20</t>
-  </si>
-  <si>
-    <t>Bronquites</t>
-  </si>
-  <si>
-    <t>CA07</t>
-  </si>
-  <si>
-    <t>IRA</t>
-  </si>
-  <si>
-    <t>CA20.Y</t>
-  </si>
-  <si>
-    <t>Broncopneumonia</t>
-  </si>
-  <si>
-    <t>CA41</t>
-  </si>
-  <si>
-    <t>Bronquiolites</t>
-  </si>
-  <si>
-    <t>CA00</t>
-  </si>
-  <si>
-    <t>Gripe /Catarro comum/ Resfriado/Constipação</t>
-  </si>
-  <si>
-    <t>1F23.0</t>
-  </si>
-  <si>
-    <t>Candidíase oral</t>
-  </si>
-  <si>
-    <t>1F23.10</t>
-  </si>
-  <si>
-    <t>Candidíase vaginal</t>
-  </si>
-  <si>
-    <t>MD81.4</t>
-  </si>
-  <si>
-    <t>Cólicas abdominal</t>
-  </si>
-  <si>
-    <t>Conjuntivites (Alérgica, Bacteriana, Viral)</t>
-  </si>
-  <si>
-    <t>EB7Y</t>
-  </si>
-  <si>
-    <t>Dermatose</t>
-  </si>
-  <si>
-    <t>Disenteria (Basilar. Amebiana)</t>
-  </si>
-  <si>
-    <t>Diarreia /EDA (Ligeira ou Plano A, Moderada ou Plano B, Grave ou Plano C)</t>
-  </si>
-  <si>
-    <t>Diabetes Melitos (Tipo I, Tipo II)</t>
-  </si>
-  <si>
-    <t>GA34.3</t>
-  </si>
-  <si>
-    <t>Dismenorreia</t>
-  </si>
-  <si>
-    <t>Enterites</t>
-  </si>
-  <si>
-    <t>DA01</t>
-  </si>
-  <si>
-    <t>Estomatites</t>
-  </si>
-  <si>
-    <t>1G04</t>
-  </si>
-  <si>
-    <t>Escabiose</t>
-  </si>
-  <si>
-    <t>1A7Z</t>
-  </si>
-  <si>
-    <t>Gonorreia</t>
-  </si>
-  <si>
-    <t>Hipertensão Arterial</t>
-  </si>
-  <si>
-    <t>BA2Z</t>
-  </si>
-  <si>
-    <t>Hipotensão Arterial</t>
-  </si>
-  <si>
-    <t>JA60.Z</t>
-  </si>
-  <si>
-    <t>Hiperémese Gravídica</t>
-  </si>
-  <si>
-    <t>FB.ME</t>
-  </si>
-  <si>
-    <t>Mialgia/ Lombalgia</t>
-  </si>
-  <si>
-    <t>AAZ1.90</t>
-  </si>
-  <si>
-    <t>Otites (Externo, Media, Purulenta)</t>
-  </si>
-  <si>
-    <t>Paludismo/Malaria (Simples, Grave)</t>
-  </si>
-  <si>
-    <t>1A36.0Z</t>
-  </si>
-  <si>
-    <t>Parasitismo Intestinal</t>
-  </si>
-  <si>
-    <t>Pio dermites</t>
-  </si>
-  <si>
-    <t>1F03</t>
-  </si>
-  <si>
-    <t>Sarampo (suspeita)</t>
-  </si>
-  <si>
-    <t>MG26</t>
-  </si>
-  <si>
-    <t>Síndrome Febril</t>
-  </si>
-  <si>
-    <t>Tuberculose (Suspeita)</t>
-  </si>
-  <si>
-    <t>DA60</t>
-  </si>
-  <si>
-    <t>Ulcera Gástrica</t>
-  </si>
-  <si>
-    <t>GC02</t>
-  </si>
-  <si>
-    <t>Uretrites</t>
-  </si>
-  <si>
-    <t>1A92 </t>
-  </si>
-  <si>
-    <t>Tricomoníase</t>
-  </si>
-  <si>
-    <t>1E90</t>
-  </si>
-  <si>
-    <t>Varicela</t>
-  </si>
-  <si>
-    <t>VIH/Sida</t>
-  </si>
-  <si>
-    <t>otro</t>
-  </si>
-  <si>
-    <t>Outras</t>
-  </si>
-  <si>
-    <t>Amigdalites</t>
-  </si>
-  <si>
-    <t>Faringite</t>
-  </si>
-  <si>
-    <t>Faringamidalites</t>
-  </si>
-  <si>
-    <t>CA03</t>
-  </si>
-  <si>
-    <t>CA02</t>
-  </si>
-  <si>
-    <t>Anemia ligeira</t>
-  </si>
-  <si>
-    <t>Anemia moderada</t>
-  </si>
-  <si>
-    <t>Anemia grave</t>
-  </si>
-  <si>
-    <t>XS5W</t>
-  </si>
-  <si>
-    <t>XS0T</t>
-  </si>
-  <si>
-    <t>XS25</t>
-  </si>
-  <si>
-    <t>Conjuntivites Alérgica</t>
-  </si>
-  <si>
-    <t>Conjuntivites Bacteriana</t>
-  </si>
-  <si>
-    <t>Conjuntivites Viral</t>
-  </si>
-  <si>
-    <t>9A60.02</t>
-  </si>
-  <si>
-    <t>9A60.Y</t>
-  </si>
-  <si>
-    <t>1D84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diarreia /EDA Ligeira ou Plano A </t>
-  </si>
-  <si>
-    <t>Diabetes Melitos Tipo I</t>
-  </si>
-  <si>
-    <t>Diarreia /EDA  Moderada ou Plano B</t>
-  </si>
-  <si>
-    <t>Diabetes MelitosTipo II</t>
-  </si>
-  <si>
-    <t>Diarreia /EDA Grave ou Plano C</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>5A10</t>
-  </si>
-  <si>
-    <t>PB</t>
-  </si>
-  <si>
-    <t>5A11</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>Mialgia</t>
-  </si>
-  <si>
-    <t>Otites Externo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paludismo/Malaria Simples </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Lombalgia</t>
-  </si>
-  <si>
-    <t>Otites Media</t>
-  </si>
-  <si>
-    <t>Paludismo/Malaria Grave</t>
-  </si>
-  <si>
-    <t>Otites  Purulenta</t>
-  </si>
-  <si>
-    <t>FB56.2</t>
-  </si>
-  <si>
-    <t>AA1Z</t>
-  </si>
-  <si>
-    <t>1F4.S</t>
-  </si>
-  <si>
-    <t>ME84.2</t>
-  </si>
-  <si>
-    <t>AA80</t>
-  </si>
-  <si>
-    <t>1F4.G</t>
-  </si>
-  <si>
-    <t>AA90</t>
-  </si>
-  <si>
-    <t>esp</t>
-  </si>
-  <si>
     <t>Especifique</t>
   </si>
   <si>
-    <t>subdx</t>
-  </si>
-  <si>
     <t>saida</t>
   </si>
   <si>
@@ -906,9 +504,6 @@
     <t>choice_item.diagnostico === data('diagno_secund')</t>
   </si>
   <si>
-    <t>Paciente foi:</t>
-  </si>
-  <si>
     <t>data('hospitaliza')==2</t>
   </si>
   <si>
@@ -919,12 +514,6 @@
   </si>
   <si>
     <t>(data('temperatura')&lt;46 &amp; data('temperatura')&gt;25) || !data('temperatura')</t>
-  </si>
-  <si>
-    <t>lab</t>
-  </si>
-  <si>
-    <t>Inicias de Laboratorista</t>
   </si>
   <si>
     <t>med</t>
@@ -957,9 +546,6 @@
   </si>
   <si>
     <t xml:space="preserve">if </t>
-  </si>
-  <si>
-    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "otro"].indexOf(data('diagnostico'))&lt;0</t>
   </si>
   <si>
     <t>_.chain(context)
@@ -974,6 +560,21 @@
   </si>
   <si>
     <t>choice_item.diagnostico === data('diagnostico')</t>
+  </si>
+  <si>
+    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "otro"].indexOf(data('diagno_secund'))&lt;0</t>
+  </si>
+  <si>
+    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "otro"].indexOf(data('diagnostico'))&lt;0 ? 1 : 0</t>
+  </si>
+  <si>
+    <t>ysubdx</t>
+  </si>
+  <si>
+    <t>calculates.ysubdx() == 1</t>
+  </si>
+  <si>
+    <t>Paciente foi {{data.hospitaliza}}:</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +699,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1157,13 +758,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1657,7 +1251,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>53</v>
@@ -1676,12 +1270,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z97"/>
+  <dimension ref="A1:Z107"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="48.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="94.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.375" style="12" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5" style="11" customWidth="1"/>
@@ -1733,7 +1327,7 @@
         <v>3</v>
       </c>
       <c r="L1" t="s">
-        <v>292</v>
+        <v>157</v>
       </c>
       <c r="M1" t="s">
         <v>30</v>
@@ -1815,7 +1409,7 @@
         <v>53</v>
       </c>
       <c r="N5" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -1831,12 +1425,12 @@
       <c r="I6" s="3"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -1896,7 +1490,7 @@
         <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>294</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -1908,461 +1502,438 @@
       <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C14" s="12"/>
-      <c r="D14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K14" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="C14" s="11"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>158</v>
-      </c>
+      <c r="C15" s="11"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>164</v>
+      </c>
       <c r="F16" s="12" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L16" s="12"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="K16" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="12"/>
+        <v>49</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>140</v>
+      </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="2:20" ht="126" x14ac:dyDescent="0.25">
+      <c r="F18" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="12"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>307</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
     </row>
-    <row r="20" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C20" s="12"/>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="12"/>
+      <c r="D22" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+      <c r="E22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C22" s="12"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C23" s="12"/>
-      <c r="E23" s="12"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C24" s="11"/>
-      <c r="D24" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>159</v>
-      </c>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C24" s="12"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="2:20" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C26" s="12"/>
-      <c r="D26" s="12" t="s">
-        <v>58</v>
-      </c>
       <c r="E26" s="12"/>
-      <c r="F26" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="L26" s="12"/>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="2:20" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="28"/>
-      <c r="D28" s="28" t="s">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C28" s="11"/>
+      <c r="D28" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>288</v>
-      </c>
-      <c r="J28" s="30"/>
-      <c r="O28" s="27" t="s">
-        <v>289</v>
-      </c>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C29" s="12"/>
-      <c r="E29" s="1"/>
+      <c r="E28" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C29" s="11"/>
+      <c r="E29" s="12"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="D30" s="2" t="s">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="2:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="L31" s="12"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:20" ht="63" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="25"/>
+      <c r="D35" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E35" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="J35" s="27"/>
+      <c r="O35" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C37" s="12"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C38" s="12"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C39" s="12"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2" t="b">
+      <c r="I40" s="7"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="S30"/>
-      <c r="T30"/>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="D31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="2"/>
-      <c r="S31"/>
-      <c r="T31"/>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+      <c r="S40"/>
+      <c r="T40"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="2"/>
+      <c r="S41"/>
+      <c r="T41"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="2"/>
-      <c r="S32"/>
-      <c r="T32"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D33" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="2"/>
+      <c r="S42"/>
+      <c r="T42"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="I33" s="7"/>
-      <c r="J33" s="2"/>
-      <c r="S33"/>
-      <c r="T33"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
+      <c r="E43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I43" s="7"/>
+      <c r="J43" s="2"/>
+      <c r="S43"/>
+      <c r="T43"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="2"/>
-      <c r="S34"/>
-      <c r="T34"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="2"/>
-      <c r="S35"/>
-      <c r="T35"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C36" s="11"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="B37" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D38" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="D39" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+      <c r="D44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="2"/>
+      <c r="S44"/>
+      <c r="T44"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C41" s="11"/>
-      <c r="D41" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C42" s="11"/>
-      <c r="D42" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D43" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C44" s="11"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C45" s="11"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="12"/>
+      <c r="D45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="2"/>
+      <c r="S45"/>
+      <c r="T45"/>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C46" s="11"/>
-      <c r="E46" s="13"/>
+      <c r="E46" s="12"/>
       <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47"/>
+      <c r="B47" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C47" s="11"/>
-      <c r="E47" s="13"/>
+      <c r="E47" s="12"/>
       <c r="F47" s="12"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C48" s="11"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="12"/>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C49" s="12"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="12"/>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C50" s="11"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D48" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49"/>
+      <c r="D49" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C51" s="11"/>
-      <c r="E51" s="12"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="12"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="15"/>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C52" s="11"/>
+      <c r="D52" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="E52" s="13"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="13"/>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="13"/>
-      <c r="J53" s="6"/>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="13"/>
-      <c r="J54" s="6"/>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="15"/>
+      <c r="F52" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D53" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C54" s="11"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C55" s="11"/>
       <c r="E55" s="13"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="13"/>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="15"/>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C56" s="11"/>
       <c r="E56" s="13"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="13"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="15"/>
+      <c r="F56" s="12"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C57" s="11"/>
       <c r="E57" s="13"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="13"/>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="15"/>
+      <c r="F57" s="12"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C58" s="11"/>
       <c r="E58" s="13"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="13"/>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="15"/>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C59" s="12"/>
       <c r="E59" s="13"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="13"/>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="32"/>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="33"/>
-      <c r="G61" s="32"/>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C60" s="11"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C61" s="11"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="15"/>
@@ -2370,21 +1941,23 @@
       <c r="F62" s="16"/>
       <c r="G62" s="13"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" s="13"/>
       <c r="C63" s="13"/>
       <c r="D63" s="15"/>
       <c r="E63" s="13"/>
       <c r="F63" s="16"/>
       <c r="G63" s="13"/>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J63" s="6"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
       <c r="D64" s="15"/>
       <c r="E64" s="13"/>
       <c r="F64" s="16"/>
       <c r="G64" s="13"/>
+      <c r="J64" s="6"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B65" s="13"/>
@@ -2419,54 +1992,84 @@
       <c r="G68" s="13"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="12"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="13"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="12"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="29"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="12"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="29"/>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="12"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="13"/>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="12"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="13"/>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="12"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="13"/>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="12"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="13"/>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="12"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="13"/>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="12"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="13"/>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="12"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="13"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D79" s="11"/>
@@ -2563,15 +2166,65 @@
       <c r="E97" s="11"/>
       <c r="F97" s="12"/>
     </row>
+    <row r="98" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="102" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="12"/>
+    </row>
+    <row r="103" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="12"/>
+    </row>
+    <row r="104" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="12"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2586,7 +2239,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultColWidth="21.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.75" style="2" customWidth="1"/>
@@ -2633,7 +2286,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2644,7 +2297,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2685,1146 +2338,327 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>165</v>
-      </c>
+      <c r="A22" s="1"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>167</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>168</v>
+      <c r="A24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>121</v>
+      <c r="A25" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>171</v>
+      <c r="A26" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>173</v>
+      <c r="A27" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="2">
+        <v>4</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>174</v>
+      <c r="A28" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" s="2">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>176</v>
-      </c>
+      <c r="A29" s="1"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>178</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>180</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="C31" s="1"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>182</v>
-      </c>
+      <c r="A32" s="1"/>
+      <c r="C32" s="1"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="C33" s="1"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="A34" s="1"/>
+      <c r="C34" s="1"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>186</v>
-      </c>
+      <c r="A35" s="1"/>
+      <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>188</v>
-      </c>
+      <c r="A36" s="1"/>
+      <c r="C36" s="1"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>190</v>
-      </c>
+      <c r="A37" s="1"/>
+      <c r="C37" s="1"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="A38" s="1"/>
+      <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>193</v>
-      </c>
+      <c r="A39" s="1"/>
+      <c r="C39" s="1"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="A40" s="1"/>
+      <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>197</v>
-      </c>
+      <c r="A41" s="1"/>
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="C42" s="1"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>198</v>
-      </c>
+      <c r="A43" s="1"/>
+      <c r="C43" s="1"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="C67" s="1"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="C68" s="1"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="C69" s="1"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B70" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="C70" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="D70" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B71" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="C71" t="s">
-        <v>238</v>
-      </c>
-      <c r="D71" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C72" t="s">
-        <v>239</v>
-      </c>
-      <c r="D72" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B73" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="C73" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B75" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B76" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B77" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="C77" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B78" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="C78" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B79" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="C79" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B80" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="C80" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B81" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B82" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B83" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="C83" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B84" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="C84" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="D84" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B85" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="C85" t="s">
-        <v>267</v>
-      </c>
-      <c r="D85" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B86" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="C86" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D86" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B87" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="C87" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="D87" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B88" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="C88" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="D88" t="s">
-        <v>215</v>
-      </c>
-      <c r="E88" s="26"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B89" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="C89" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="D89" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B90" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="C90" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="D90" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C91" s="24" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="C94" s="1"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B95" s="2">
-        <v>1</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B96" s="2">
-        <v>2</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B97" s="2">
-        <v>3</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B98" s="2">
-        <v>4</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B99" s="2">
-        <v>5</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="1"/>
-      <c r="C101" s="1"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="1"/>
-      <c r="C102" s="1"/>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="1"/>
-      <c r="C103" s="1"/>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-      <c r="C104" s="1"/>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="1"/>
-      <c r="C105" s="1"/>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="1"/>
-      <c r="C106" s="1"/>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="1"/>
-      <c r="C107" s="1"/>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="1"/>
-      <c r="C108" s="1"/>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="1"/>
-      <c r="C109" s="1"/>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="1"/>
-      <c r="C110" s="1"/>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="1"/>
-      <c r="C111" s="1"/>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="1"/>
-      <c r="C112" s="1"/>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="1"/>
-      <c r="C113" s="1"/>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="1"/>
-      <c r="C114" s="1"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="1"/>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="1"/>
-      <c r="C191" s="1"/>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="1"/>
-      <c r="C192" s="1"/>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="1"/>
-      <c r="C193" s="1"/>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="1"/>
-      <c r="C194" s="1"/>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="1"/>
-      <c r="C195" s="1"/>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="1"/>
-      <c r="C196" s="1"/>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="1"/>
-      <c r="C197" s="1"/>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="1"/>
-      <c r="C198" s="1"/>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="1"/>
-      <c r="C199" s="1"/>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="1"/>
-      <c r="C200" s="1"/>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="1"/>
-      <c r="C201" s="1"/>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="1"/>
-      <c r="C202" s="1"/>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="1"/>
-      <c r="C203" s="1"/>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="1"/>
-      <c r="C204" s="1"/>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="1"/>
-      <c r="C205" s="1"/>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="1"/>
-      <c r="C206" s="1"/>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="1"/>
-      <c r="C207" s="1"/>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="1"/>
-      <c r="C208" s="1"/>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="1"/>
-      <c r="C209" s="1"/>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="1"/>
-      <c r="C210" s="1"/>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="1"/>
-      <c r="C211" s="1"/>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="1"/>
-      <c r="C212" s="1"/>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="1"/>
-      <c r="C213" s="1"/>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="1"/>
-      <c r="C214" s="1"/>
+      <c r="A44" s="1"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1"/>
+      <c r="C120" s="1"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1"/>
+      <c r="C121" s="1"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1"/>
+      <c r="C122" s="1"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1"/>
+      <c r="C123" s="1"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1"/>
+      <c r="C124" s="1"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1"/>
+      <c r="C125" s="1"/>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1"/>
+      <c r="C126" s="1"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1"/>
+      <c r="C127" s="1"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1"/>
+      <c r="C128" s="1"/>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="1"/>
+      <c r="C129" s="1"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="1"/>
+      <c r="C130" s="1"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="1"/>
+      <c r="C131" s="1"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="1"/>
+      <c r="C132" s="1"/>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="1"/>
+      <c r="C133" s="1"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="1"/>
+      <c r="C134" s="1"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="1"/>
+      <c r="C135" s="1"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="1"/>
+      <c r="C136" s="1"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="1"/>
+      <c r="C137" s="1"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="1"/>
+      <c r="C138" s="1"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="1"/>
+      <c r="C139" s="1"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="1"/>
+      <c r="C140" s="1"/>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="1"/>
+      <c r="C141" s="1"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="1"/>
+      <c r="C142" s="1"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="1"/>
+      <c r="C143" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B22:C52">
-    <sortCondition ref="C22:C52"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <extLst>
@@ -3896,51 +2730,51 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
         <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="H2" s="21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
-        <v>302</v>
+        <v>165</v>
       </c>
       <c r="D3" s="2"/>
       <c r="J3" t="s">
-        <v>303</v>
+        <v>166</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>305</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>304</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>302</v>
+        <v>165</v>
       </c>
       <c r="J4" t="s">
-        <v>303</v>
+        <v>166</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>308</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4045,23 +2879,31 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -4092,7 +2934,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -4120,7 +2962,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4128,7 +2970,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4229,7 +3071,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>96</v>
@@ -4237,7 +3079,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>98</v>
@@ -4256,7 +3098,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -4264,7 +3106,7 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4272,7 +3114,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -4280,7 +3122,7 @@
         <v>58</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4288,7 +3130,7 @@
         <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -4296,7 +3138,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -4304,7 +3146,7 @@
         <v>58</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -4312,7 +3154,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>299</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4320,7 +3162,7 @@
         <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>300</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -4328,15 +3170,31 @@
         <v>58</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>297</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FA5717-D633-4A7D-AA2E-0E60BE19C3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FDFFA9-A774-48A4-B78D-7C4DA4287404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="175">
   <si>
     <t>type</t>
   </si>
@@ -336,12 +336,6 @@
     <t>Diagnósticos secundarios</t>
   </si>
   <si>
-    <t>hospitaliza</t>
-  </si>
-  <si>
-    <t>Hospitalização</t>
-  </si>
-  <si>
     <t>resultado</t>
   </si>
   <si>
@@ -502,9 +496,6 @@
   </si>
   <si>
     <t>choice_item.diagnostico === data('diagno_secund')</t>
-  </si>
-  <si>
-    <t>data('hospitaliza')==2</t>
   </si>
   <si>
     <t>default</t>
@@ -562,19 +553,22 @@
     <t>choice_item.diagnostico === data('diagnostico')</t>
   </si>
   <si>
-    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "otro"].indexOf(data('diagno_secund'))&lt;0</t>
-  </si>
-  <si>
-    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "otro"].indexOf(data('diagnostico'))&lt;0 ? 1 : 0</t>
-  </si>
-  <si>
     <t>ysubdx</t>
   </si>
   <si>
     <t>calculates.ysubdx() == 1</t>
   </si>
   <si>
-    <t>Paciente foi {{data.hospitaliza}}:</t>
+    <t>Hospitalizado</t>
+  </si>
+  <si>
+    <t>Paciente foi</t>
+  </si>
+  <si>
+    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro"].indexOf(data('diagno_secund'))&lt;0</t>
+  </si>
+  <si>
+    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro"].indexOf(data('diagnostico'))&lt;0 ? 1 : 0</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1245,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>53</v>
@@ -1270,7 +1264,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z107"/>
+  <dimension ref="A1:Z99"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1327,7 +1321,7 @@
         <v>3</v>
       </c>
       <c r="L1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M1" t="s">
         <v>30</v>
@@ -1409,7 +1403,7 @@
         <v>53</v>
       </c>
       <c r="N5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -1430,7 +1424,7 @@
         <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -1490,7 +1484,7 @@
         <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -1517,7 +1511,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>96</v>
@@ -1534,7 +1528,7 @@
         <v>49</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1546,13 +1540,13 @@
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="K18" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L18" s="12"/>
     </row>
@@ -1571,10 +1565,10 @@
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1585,16 +1579,16 @@
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
@@ -1631,7 +1625,7 @@
         <v>10</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>98</v>
@@ -1650,7 +1644,7 @@
         <v>49</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -1662,13 +1656,13 @@
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="K31" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L31" s="12"/>
     </row>
@@ -1687,10 +1681,10 @@
     </row>
     <row r="34" spans="1:20" ht="63" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -1701,17 +1695,17 @@
         <v>10</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J35" s="27"/>
       <c r="O35" s="24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P35" s="28"/>
       <c r="Q35" s="28"/>
@@ -1744,19 +1738,16 @@
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>46</v>
+        <v>145</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="S40"/>
       <c r="T40"/>
     </row>
@@ -1772,192 +1763,181 @@
       <c r="T41"/>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="2"/>
-      <c r="S42"/>
-      <c r="T42"/>
+      <c r="D42" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D43" s="2" t="s">
-        <v>10</v>
+      <c r="A43"/>
+      <c r="D43" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I43" s="7"/>
-      <c r="J43" s="2"/>
-      <c r="S43"/>
-      <c r="T43"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="2"/>
-      <c r="S44"/>
-      <c r="T44"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
+      <c r="D45" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="2"/>
-      <c r="S45"/>
-      <c r="T45"/>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C46" s="11"/>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-      <c r="B47" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C47" s="11"/>
-      <c r="E47" s="12"/>
+      <c r="E47" s="13"/>
       <c r="F47" s="12"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D48" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-      <c r="D49" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C51" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C49" s="11"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="12"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C50" s="11"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C51" s="12"/>
       <c r="E51" s="13"/>
       <c r="F51" s="12"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C52" s="11"/>
-      <c r="D52" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D53" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C54" s="11"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C55" s="11"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C53" s="11"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="13"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="15"/>
       <c r="E55" s="13"/>
-      <c r="F55" s="12"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C56" s="11"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="13"/>
+      <c r="J55" s="6"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="15"/>
       <c r="E56" s="13"/>
-      <c r="F56" s="12"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C57" s="11"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="13"/>
+      <c r="J56" s="6"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="15"/>
       <c r="E57" s="13"/>
-      <c r="F57" s="12"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C58" s="11"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="13"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="15"/>
       <c r="E58" s="13"/>
-      <c r="F58" s="12"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C59" s="12"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="13"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="15"/>
       <c r="E59" s="13"/>
-      <c r="F59" s="12"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C60" s="11"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C61" s="11"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="13"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="13"/>
-      <c r="J63" s="6"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F59" s="16"/>
+      <c r="G59" s="13"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="13"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="13"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="29"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="29"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
       <c r="D64" s="15"/>
       <c r="E64" s="13"/>
       <c r="F64" s="16"/>
       <c r="G64" s="13"/>
-      <c r="J64" s="6"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B65" s="13"/>
@@ -2000,76 +1980,52 @@
       <c r="G69" s="13"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="29"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="13"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="29"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="12"/>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="13"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="12"/>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="13"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="12"/>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="13"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="12"/>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="13"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="12"/>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="13"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="12"/>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="13"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="12"/>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="13"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="12"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D79" s="11"/>
@@ -2176,55 +2132,15 @@
       <c r="E99" s="11"/>
       <c r="F99" s="12"/>
     </row>
-    <row r="100" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="12"/>
-    </row>
-    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="12"/>
-    </row>
-    <row r="102" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="12"/>
-    </row>
-    <row r="103" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="12"/>
-    </row>
-    <row r="104" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="12"/>
-    </row>
-    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="12"/>
-    </row>
-    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="12"/>
-    </row>
-    <row r="107" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="12"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2239,16 +2155,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr defaultColWidth="21.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.5" style="2"/>
     <col min="3" max="3" width="51.125" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="21.5" style="2"/>
+    <col min="4" max="16384" width="21.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -2258,11 +2174,8 @@
       <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -2273,7 +2186,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -2284,9 +2197,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2295,9 +2208,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2306,11 +2219,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,7 +2234,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>46</v>
       </c>
@@ -2332,107 +2245,107 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,62 +2355,69 @@
       <c r="A22" s="1"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B25" s="2">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B27" s="2">
         <v>4</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2724,25 +2644,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" t="s">
         <v>129</v>
-      </c>
-      <c r="F2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G2" t="s">
-        <v>131</v>
       </c>
       <c r="H2" s="21" t="s">
         <v>73</v>
@@ -2750,31 +2670,31 @@
     </row>
     <row r="3" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D3" s="2"/>
       <c r="J3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="B4" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2879,31 +2799,31 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>174</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2962,7 +2882,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2970,7 +2890,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3086,19 +3006,15 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>100</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3106,7 +3022,7 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3114,7 +3030,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3122,7 +3038,7 @@
         <v>58</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3130,7 +3046,7 @@
         <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3138,7 +3054,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3146,7 +3062,7 @@
         <v>58</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -3154,7 +3070,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3162,7 +3078,7 @@
         <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3170,7 +3086,7 @@
         <v>58</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3178,7 +3094,7 @@
         <v>10</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3186,7 +3102,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3194,7 +3110,7 @@
         <v>10</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FDFFA9-A774-48A4-B78D-7C4DA4287404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D6E9BF-EADD-49BE-A383-B3423F59167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="203">
   <si>
     <t>type</t>
   </si>
@@ -569,6 +569,90 @@
   </si>
   <si>
     <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro"].indexOf(data('diagnostico'))&lt;0 ? 1 : 0</t>
+  </si>
+  <si>
+    <t>Coartem</t>
+  </si>
+  <si>
+    <t>Quinino comp.</t>
+  </si>
+  <si>
+    <t>Quinina injet</t>
+  </si>
+  <si>
+    <t>Artusunato injet</t>
+  </si>
+  <si>
+    <t>tto</t>
+  </si>
+  <si>
+    <t>Outros</t>
+  </si>
+  <si>
+    <t>6/6h</t>
+  </si>
+  <si>
+    <t>8/8h</t>
+  </si>
+  <si>
+    <t>12/12h</t>
+  </si>
+  <si>
+    <t>freq</t>
+  </si>
+  <si>
+    <t>24/24h ou uma vez por dia</t>
+  </si>
+  <si>
+    <t>Oral</t>
+  </si>
+  <si>
+    <t>Intra Venosa</t>
+  </si>
+  <si>
+    <t>vo</t>
+  </si>
+  <si>
+    <t>vm</t>
+  </si>
+  <si>
+    <t>vi</t>
+  </si>
+  <si>
+    <t>via</t>
+  </si>
+  <si>
+    <t>Intra Muscular</t>
+  </si>
+  <si>
+    <t>dose/Kg</t>
+  </si>
+  <si>
+    <t>dose/ml</t>
+  </si>
+  <si>
+    <t>doses</t>
+  </si>
+  <si>
+    <t>Medicamento</t>
+  </si>
+  <si>
+    <t>quanti</t>
+  </si>
+  <si>
+    <t>Doses</t>
+  </si>
+  <si>
+    <t>unidade</t>
+  </si>
+  <si>
+    <t>Unidade de medida de dosis</t>
+  </si>
+  <si>
+    <t>Frequência</t>
+  </si>
+  <si>
+    <t>Via de Administração</t>
   </si>
 </sst>
 </file>
@@ -1782,69 +1866,101 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C44" s="11"/>
-      <c r="D44" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D45" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>74</v>
+      <c r="B45" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C46" s="11"/>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C47" s="11"/>
       <c r="E47" s="13"/>
       <c r="F47" s="12"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C48" s="11"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="12"/>
+      <c r="D48" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C49" s="11"/>
+      <c r="D49" s="12" t="s">
+        <v>90</v>
+      </c>
       <c r="E49" s="13"/>
-      <c r="F49" s="12"/>
+      <c r="F49" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C50" s="11"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="12"/>
+      <c r="D50" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C51" s="12"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="12"/>
+      <c r="D51" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C52" s="11"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
+      <c r="D52" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="C53" s="11"/>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -1867,7 +1983,9 @@
       <c r="J55" s="6"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="13"/>
+      <c r="B56" s="13" t="s">
+        <v>50</v>
+      </c>
       <c r="C56" s="13"/>
       <c r="D56" s="15"/>
       <c r="E56" s="13"/>
@@ -1876,20 +1994,28 @@
       <c r="J56" s="6"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="15"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="E57" s="13"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="13"/>
+      <c r="F57" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="13"/>
+      <c r="D58" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="13"/>
@@ -1900,7 +2026,9 @@
       <c r="G59" s="13"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="13"/>
+      <c r="B60" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="C60" s="13"/>
       <c r="D60" s="15"/>
       <c r="E60" s="13"/>
@@ -2424,63 +2552,169 @@
       <c r="A29" s="1"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="C30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B30" s="2">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="C31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" s="2">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" s="2">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="C34" s="1"/>
+      <c r="A34" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" s="2">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="C36" s="1"/>
+      <c r="A36" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="2">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="A37" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" s="2">
+        <v>3</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="C38" s="1"/>
+      <c r="A38" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="A39" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="C41" s="1"/>
+      <c r="A41" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="C42" s="1"/>
+      <c r="A42" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="C43" s="1"/>
+      <c r="A43" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B45" s="2">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B46" s="2">
+        <v>2</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
@@ -2854,7 +3088,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -3111,6 +3345,46 @@
       </c>
       <c r="B35" s="2" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D6E9BF-EADD-49BE-A383-B3423F59167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C415206-3926-4F0C-AE8A-C06CF3EE2EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C415206-3926-4F0C-AE8A-C06CF3EE2EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6038D5C-5C4E-4EC1-9CAC-9EE217DE04F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="200">
   <si>
     <t>type</t>
   </si>
@@ -222,9 +222,6 @@
     <t>branch_label</t>
   </si>
   <si>
-    <t>note</t>
-  </si>
-  <si>
     <t>adate</t>
   </si>
   <si>
@@ -315,15 +312,9 @@
     <t>febre</t>
   </si>
   <si>
-    <t>Febre</t>
-  </si>
-  <si>
     <t>temperatura</t>
   </si>
   <si>
-    <t>Temperatura</t>
-  </si>
-  <si>
     <t>diagnostico</t>
   </si>
   <si>
@@ -378,12 +369,6 @@
     <t xml:space="preserve">resultado </t>
   </si>
   <si>
-    <t>intro_resultado</t>
-  </si>
-  <si>
-    <t>Introducão dos resultados de laboratorio</t>
-  </si>
-  <si>
     <t>DOB_idade</t>
   </si>
   <si>
@@ -502,9 +487,6 @@
   </si>
   <si>
     <t>especifique:</t>
-  </si>
-  <si>
-    <t>(data('temperatura')&lt;46 &amp; data('temperatura')&gt;25) || !data('temperatura')</t>
   </si>
   <si>
     <t>med</t>
@@ -559,18 +541,9 @@
     <t>calculates.ysubdx() == 1</t>
   </si>
   <si>
-    <t>Hospitalizado</t>
-  </si>
-  <si>
     <t>Paciente foi</t>
   </si>
   <si>
-    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro"].indexOf(data('diagno_secund'))&lt;0</t>
-  </si>
-  <si>
-    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro"].indexOf(data('diagnostico'))&lt;0 ? 1 : 0</t>
-  </si>
-  <si>
     <t>Coartem</t>
   </si>
   <si>
@@ -653,6 +626,24 @@
   </si>
   <si>
     <t>Via de Administração</t>
+  </si>
+  <si>
+    <t>hospital</t>
+  </si>
+  <si>
+    <t>O/A paciente foi hospitalizado(a)?</t>
+  </si>
+  <si>
+    <t>data('hospital')==2</t>
+  </si>
+  <si>
+    <t>select_one_integer</t>
+  </si>
+  <si>
+    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro", "",].indexOf(data('diagno_secund'))&lt;0</t>
+  </si>
+  <si>
+    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro", ""].indexOf(data('diagnostico'))&lt;0 ? 1 : 0</t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1291,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1316,7 +1307,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1324,12 +1315,12 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>53</v>
@@ -1348,7 +1339,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z99"/>
+  <dimension ref="A1:Z94"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1405,7 +1396,7 @@
         <v>3</v>
       </c>
       <c r="L1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M1" t="s">
         <v>30</v>
@@ -1417,10 +1408,10 @@
         <v>29</v>
       </c>
       <c r="P1" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q1" s="19" t="s">
         <v>81</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>82</v>
       </c>
       <c r="R1" t="s">
         <v>32</v>
@@ -1480,14 +1471,14 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="12" t="s">
         <v>53</v>
       </c>
       <c r="N5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -1508,21 +1499,21 @@
         <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D8" s="12" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -1537,40 +1528,6 @@
       <c r="F10" s="17"/>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C11" s="12"/>
-      <c r="D11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K11" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="C12" s="11"/>
-      <c r="D12" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>51</v>
@@ -1595,13 +1552,13 @@
         <v>10</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K16" s="2" t="b">
         <v>1</v>
@@ -1612,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1624,13 +1581,13 @@
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="L18" s="12"/>
     </row>
@@ -1649,10 +1606,10 @@
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1663,16 +1620,16 @@
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
@@ -1709,13 +1666,13 @@
         <v>10</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
@@ -1728,7 +1685,7 @@
         <v>49</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -1740,13 +1697,13 @@
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="L31" s="12"/>
     </row>
@@ -1758,43 +1715,43 @@
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C33" s="12"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:20" ht="63" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" ht="63" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C35" s="25"/>
       <c r="D35" s="25" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J35" s="27"/>
       <c r="O35" s="24" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="P35" s="28"/>
       <c r="Q35" s="28"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>52</v>
       </c>
@@ -1802,42 +1759,57 @@
       <c r="E36" s="1"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C37" s="12"/>
       <c r="E37" s="1"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C38" s="12"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C39" s="12"/>
+      <c r="D38" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>196</v>
+      </c>
       <c r="E39" s="1"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="D40" s="2" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="2"/>
       <c r="S40"/>
       <c r="T40"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D41" s="2"/>
       <c r="F41" s="2"/>
@@ -1846,124 +1818,146 @@
       <c r="S41"/>
       <c r="T41"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D42" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43"/>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="11"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C43" s="11"/>
       <c r="D43" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C44" s="11"/>
+      <c r="D44" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C45" s="11"/>
+      <c r="D45" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C46" s="12"/>
+      <c r="D46" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C47" s="11"/>
+      <c r="D47" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C46" s="11"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+      <c r="C48" s="11"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="13"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="13"/>
+      <c r="J50" s="6"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="11"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="12"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C48" s="11"/>
-      <c r="D48" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C49" s="11"/>
-      <c r="D49" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C50" s="11"/>
-      <c r="D50" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C51" s="12"/>
-      <c r="D51" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>201</v>
-      </c>
+      <c r="C51" s="13"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="13"/>
+      <c r="J51" s="6"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C52" s="11"/>
       <c r="D52" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>191</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E52" s="13"/>
       <c r="F52" s="12" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>202</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" s="11"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
+      <c r="D53" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="13"/>
@@ -1974,48 +1968,38 @@
       <c r="G54" s="13"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55" s="13"/>
+      <c r="B55" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="C55" s="13"/>
       <c r="D55" s="15"/>
       <c r="E55" s="13"/>
       <c r="F55" s="16"/>
       <c r="G55" s="13"/>
-      <c r="J55" s="6"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="13" t="s">
-        <v>50</v>
-      </c>
+      <c r="B56" s="13"/>
       <c r="C56" s="13"/>
       <c r="D56" s="15"/>
       <c r="E56" s="13"/>
       <c r="F56" s="16"/>
       <c r="G56" s="13"/>
-      <c r="J56" s="6"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C57" s="11"/>
-      <c r="D57" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="29"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D58" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="29"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="13"/>
@@ -2026,9 +2010,7 @@
       <c r="G59" s="13"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="13" t="s">
-        <v>51</v>
-      </c>
+      <c r="B60" s="13"/>
       <c r="C60" s="13"/>
       <c r="D60" s="15"/>
       <c r="E60" s="13"/>
@@ -2044,20 +2026,20 @@
       <c r="G61" s="13"/>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="30"/>
-      <c r="G62" s="29"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="13"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="29"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="13"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="13"/>
@@ -2076,44 +2058,29 @@
       <c r="G65" s="13"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="13"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="12"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="13"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="12"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="13"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="12"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="13"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="12"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="13"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="12"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D71" s="11"/>
@@ -2235,40 +2202,15 @@
       <c r="E94" s="11"/>
       <c r="F94" s="12"/>
     </row>
-    <row r="95" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="12"/>
-    </row>
-    <row r="96" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="12"/>
-    </row>
-    <row r="97" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="12"/>
-    </row>
-    <row r="98" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="12"/>
-    </row>
-    <row r="99" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="12"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="F57:F58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2327,7 +2269,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2338,7 +2280,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2379,101 +2321,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2483,69 +2425,62 @@
       <c r="A22" s="1"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="2">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>171</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B27" s="2">
         <v>4</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2553,57 +2488,57 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B31" s="2">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B32" s="2">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B33" s="2">
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2612,46 +2547,46 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B36" s="2">
         <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B37" s="2">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B38" s="2">
         <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2660,35 +2595,35 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2696,24 +2631,24 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B45" s="2">
         <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B46" s="2">
         <v>2</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2849,25 +2784,25 @@
         <v>41</v>
       </c>
       <c r="C1" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>70</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>71</v>
       </c>
       <c r="J1" s="22" t="s">
         <v>40</v>
@@ -2878,57 +2813,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D3" s="2"/>
       <c r="J3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2978,7 +2913,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -2987,7 +2922,7 @@
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3014,50 +2949,50 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
         <v>79</v>
-      </c>
-      <c r="B3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3105,10 +3040,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3116,20 +3051,20 @@
         <v>10</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>26</v>
@@ -3153,7 +3088,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>53</v>
@@ -3177,7 +3112,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>24</v>
@@ -3185,18 +3120,18 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3204,23 +3139,23 @@
         <v>58</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3228,7 +3163,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3236,7 +3171,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3248,7 +3183,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3256,7 +3191,7 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3264,7 +3199,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3272,7 +3207,7 @@
         <v>58</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3280,7 +3215,7 @@
         <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3288,7 +3223,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3296,15 +3231,15 @@
         <v>58</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3312,7 +3247,7 @@
         <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3320,7 +3255,7 @@
         <v>58</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3328,7 +3263,7 @@
         <v>10</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3336,47 +3271,47 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -3384,7 +3319,7 @@
         <v>10</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6038D5C-5C4E-4EC1-9CAC-9EE217DE04F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBE6243-D2C5-4D08-8A44-C2154EDB6A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="200">
   <si>
     <t>type</t>
   </si>
@@ -720,7 +720,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -768,7 +768,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -827,6 +827,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -840,10 +846,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1730,26 +1733,26 @@
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="2:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="25"/>
-      <c r="D35" s="25" t="s">
+    <row r="35" spans="2:20" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="12"/>
+      <c r="D35" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="26" t="s">
+      <c r="E35" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="F35" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="G35" s="24" t="s">
+      <c r="G35" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="J35" s="27"/>
-      <c r="O35" s="24" t="s">
+      <c r="J35" s="31"/>
+      <c r="O35" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
@@ -1779,44 +1782,48 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="D40" s="2" t="s">
+      <c r="D39" s="27"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="27"/>
+      <c r="J39" s="29"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+    </row>
+    <row r="40" spans="2:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="2"/>
-      <c r="S40"/>
-      <c r="T40"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
+      <c r="I40" s="29"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+    </row>
+    <row r="41" spans="2:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="2"/>
-      <c r="S41"/>
-      <c r="T41"/>
+      <c r="I41" s="29"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="30"/>
+      <c r="S41" s="30"/>
+      <c r="T41" s="30"/>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
@@ -1986,20 +1993,20 @@
       <c r="G56" s="13"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="29"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="24"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="29"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="24"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="13"/>
@@ -3023,7 +3030,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -3320,6 +3327,14 @@
       </c>
       <c r="B41" s="12" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBE6243-D2C5-4D08-8A44-C2154EDB6A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE50E8F1-FC1F-49CC-9BE5-837AC76074B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="200">
   <si>
     <t>type</t>
   </si>
@@ -768,21 +768,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1342,19 +1333,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z94"/>
+  <dimension ref="A1:Z84"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="94.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="25.375" style="9" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.5" style="11" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="8" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
     <col min="8" max="8" width="29.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="24.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.75" style="7"/>
+    <col min="10" max="10" width="10.75" style="4"/>
     <col min="11" max="11" width="28.5" style="2" customWidth="1"/>
     <col min="12" max="12" width="13.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="17" style="2" customWidth="1"/>
@@ -1374,13 +1365,13 @@
       <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1410,10 +1401,10 @@
       <c r="O1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="16" t="s">
         <v>81</v>
       </c>
       <c r="R1" t="s">
@@ -1445,779 +1436,714 @@
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="4"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D4" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C5" s="11"/>
-      <c r="D5" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" t="s">
-        <v>126</v>
+      <c r="B5" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="5"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>120</v>
-      </c>
+      <c r="C7" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D8" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>87</v>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="C9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C10" s="11"/>
-      <c r="D10" s="9"/>
-      <c r="E10"/>
-      <c r="F10" s="17"/>
-      <c r="G10"/>
+      <c r="C10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C14" s="9"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C18" s="8"/>
+      <c r="D18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C19" s="8"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="2:20" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="2:20" ht="63" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="2:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="9"/>
+      <c r="D25" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="28"/>
+      <c r="O25" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C27" s="9"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C28" s="9"/>
+      <c r="D28" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="24"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="24"/>
+      <c r="J29" s="26"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+    </row>
+    <row r="30" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="I30" s="26"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+    </row>
+    <row r="31" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31" s="26"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C33" s="8"/>
+      <c r="D33" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C34" s="8"/>
+      <c r="D34" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C35" s="8"/>
+      <c r="D35" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C36" s="9"/>
+      <c r="D36" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C37" s="8"/>
+      <c r="D37" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C16" s="12"/>
-      <c r="D16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K16" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C18" s="12"/>
-      <c r="D18" s="12" t="s">
+      <c r="C38" s="8"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="10"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="10"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="10"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C42" s="8"/>
+      <c r="D42" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="L18" s="12"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="12"/>
-      <c r="D22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="12"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C24" s="12"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C28" s="11"/>
-      <c r="D28" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C29" s="11"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="2:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C31" s="12"/>
-      <c r="D31" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="L31" s="12"/>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="2:20" ht="63" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="2:20" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="12"/>
-      <c r="D35" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="J35" s="31"/>
-      <c r="O35" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-    </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="12"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C37" s="12"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C38" s="12"/>
-      <c r="D38" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="27"/>
-      <c r="J39" s="29"/>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="30"/>
-    </row>
-    <row r="40" spans="2:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="I40" s="29"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-    </row>
-    <row r="41" spans="2:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="I41" s="29"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="30"/>
-      <c r="S41" s="30"/>
-      <c r="T41" s="30"/>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="11"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="12"/>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C43" s="11"/>
-      <c r="D43" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>170</v>
+      <c r="E42" s="10"/>
+      <c r="F42" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D43" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C44" s="11"/>
-      <c r="D44" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C45" s="11"/>
-      <c r="D45" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C46" s="12"/>
-      <c r="D46" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C47" s="11"/>
-      <c r="D47" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="13"/>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="13"/>
-      <c r="J50" s="6"/>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" s="13"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="13"/>
-      <c r="J51" s="6"/>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C52" s="11"/>
-      <c r="D52" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D53" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="13"/>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C55" s="13"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="13"/>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="13"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="24"/>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="24"/>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="13"/>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="13"/>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="13"/>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="13"/>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="13"/>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="13"/>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="13"/>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="12"/>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="12"/>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="12"/>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="12"/>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="12"/>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="12"/>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="12"/>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="12"/>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="12"/>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="12"/>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="12"/>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="12"/>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="12"/>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="12"/>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="12"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="10"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="21"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="21"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="10"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="10"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="10"/>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="10"/>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="10"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="10"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="9"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="9"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="9"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="9"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="9"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="9"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="9"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="9"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="9"/>
+    </row>
+    <row r="65" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="9"/>
+    </row>
+    <row r="66" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="9"/>
+    </row>
+    <row r="67" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="9"/>
+    </row>
+    <row r="68" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="9"/>
+    </row>
+    <row r="69" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="9"/>
+    </row>
+    <row r="70" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="9"/>
+    </row>
+    <row r="71" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="9"/>
+    </row>
+    <row r="72" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="9"/>
+    </row>
+    <row r="73" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="9"/>
+    </row>
+    <row r="74" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="9"/>
+    </row>
+    <row r="75" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="9"/>
+    </row>
+    <row r="76" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="9"/>
+    </row>
+    <row r="77" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="9"/>
+    </row>
+    <row r="78" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="9"/>
+    </row>
+    <row r="79" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="9"/>
+    </row>
+    <row r="80" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="9"/>
     </row>
     <row r="81" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="12"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="9"/>
     </row>
     <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="12"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="9"/>
     </row>
     <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="12"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="9"/>
     </row>
     <row r="84" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="12"/>
-    </row>
-    <row r="85" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="12"/>
-    </row>
-    <row r="86" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="12"/>
-    </row>
-    <row r="87" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="12"/>
-    </row>
-    <row r="88" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="12"/>
-    </row>
-    <row r="89" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="12"/>
-    </row>
-    <row r="90" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D90" s="11"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="12"/>
-    </row>
-    <row r="91" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="12"/>
-    </row>
-    <row r="92" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="12"/>
-    </row>
-    <row r="93" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="12"/>
-    </row>
-    <row r="94" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="12"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="D1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2327,7 +2253,7 @@
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="9" t="s">
         <v>112</v>
       </c>
       <c r="B11" s="2">
@@ -2338,7 +2264,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="9" t="s">
         <v>112</v>
       </c>
       <c r="B12" s="2">
@@ -2349,7 +2275,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="9" t="s">
         <v>112</v>
       </c>
       <c r="B13" s="2">
@@ -2360,7 +2286,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="9" t="s">
         <v>112</v>
       </c>
       <c r="B14" s="2">
@@ -2783,38 +2709,38 @@
     <col min="11" max="11" width="87.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="19" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2840,7 +2766,7 @@
       <c r="G2" t="s">
         <v>124</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="18" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2890,17 +2816,17 @@
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="16" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2998,7 +2924,7 @@
       <c r="A8" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3038,10 +2964,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3049,47 +2975,47 @@
       <c r="A2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3097,87 +3023,87 @@
       <c r="A8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="8" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3186,15 +3112,15 @@
       <c r="B19" s="2"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="8" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="9" t="s">
         <v>58</v>
       </c>
       <c r="B21" t="s">
@@ -3202,18 +3128,18 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="7" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3226,18 +3152,18 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="9" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3258,18 +3184,18 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="9" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3290,50 +3216,50 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="9" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="9" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="9" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="9" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="9" t="s">
         <v>194</v>
       </c>
     </row>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE50E8F1-FC1F-49CC-9BE5-837AC76074B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D799F2E2-E1FA-4D5C-A1C0-3E5C4FD8CA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="200">
   <si>
     <t>type</t>
   </si>
@@ -541,9 +541,6 @@
     <t>calculates.ysubdx() == 1</t>
   </si>
   <si>
-    <t>Paciente foi</t>
-  </si>
-  <si>
     <t>Coartem</t>
   </si>
   <si>
@@ -634,16 +631,19 @@
     <t>O/A paciente foi hospitalizado(a)?</t>
   </si>
   <si>
-    <t>data('hospital')==2</t>
-  </si>
-  <si>
     <t>select_one_integer</t>
   </si>
   <si>
-    <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro", "",].indexOf(data('diagno_secund'))&lt;0</t>
-  </si>
-  <si>
     <t>["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro", ""].indexOf(data('diagnostico'))&lt;0 ? 1 : 0</t>
+  </si>
+  <si>
+    <t>N de Comprimidos</t>
+  </si>
+  <si>
+    <t>m_envio</t>
+  </si>
+  <si>
+    <t>(["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro", "",].indexOf(data('diagno_secund'))&lt;0) &amp;&amp; data('diagno_secund')</t>
   </si>
 </sst>
 </file>
@@ -711,18 +711,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -768,7 +762,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -818,26 +812,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1333,7 +1314,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z84"/>
+  <dimension ref="A1:Z81"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1458,7 +1439,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D4" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>46</v>
@@ -1584,12 +1565,12 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
         <v>10</v>
@@ -1604,12 +1585,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C19" s="8"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>49</v>
       </c>
@@ -1619,7 +1600,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="2:20" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
         <v>58</v>
@@ -1636,7 +1617,7 @@
       </c>
       <c r="L21" s="9"/>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>52</v>
       </c>
@@ -1644,22 +1625,22 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="2:20" ht="63" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" ht="63" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="2:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C25" s="9"/>
       <c r="D25" s="9" t="s">
         <v>10</v>
@@ -1673,14 +1654,14 @@
       <c r="G25" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="J25" s="28"/>
+      <c r="J25" s="21"/>
       <c r="O25" s="8" t="s">
         <v>148</v>
       </c>
       <c r="P25" s="14"/>
       <c r="Q25" s="14"/>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>52</v>
       </c>
@@ -1688,229 +1669,213 @@
       <c r="E26" s="1"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C27" s="9"/>
       <c r="E27" s="1"/>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C28" s="9"/>
       <c r="D28" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F28" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G28" s="2" t="s">
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C30" s="8"/>
+      <c r="D30" s="9" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="29" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="24"/>
-      <c r="J29" s="26"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-    </row>
-    <row r="30" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="G30" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="I30" s="26"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-    </row>
-    <row r="31" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="I31" s="26"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="E30" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C31" s="8"/>
+      <c r="D31" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C32" s="8"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="8"/>
+      <c r="D32" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C33" s="9"/>
       <c r="D33" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C34" s="8"/>
       <c r="D34" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E34" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>181</v>
+      </c>
       <c r="F34" s="9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="C35" s="8"/>
-      <c r="D35" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="9"/>
-      <c r="D36" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C37" s="8"/>
-      <c r="D37" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="12"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="10"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="10"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C39" s="8"/>
+      <c r="D39" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="E39" s="10"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="10"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="10"/>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="10" t="s">
-        <v>50</v>
-      </c>
+      <c r="F39" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K39" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D40" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="10"/>
       <c r="C41" s="10"/>
       <c r="D41" s="12"/>
       <c r="E41" s="10"/>
       <c r="F41" s="13"/>
       <c r="G41" s="10"/>
-      <c r="J41" s="3"/>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C42" s="8"/>
-      <c r="D42" s="9" t="s">
-        <v>58</v>
-      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="10"/>
+      <c r="D42" s="12"/>
       <c r="E42" s="10"/>
-      <c r="F42" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D43" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="10"/>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="10"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F42" s="13"/>
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="10"/>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="22"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
       <c r="D46" s="12"/>
@@ -1918,21 +1883,21 @@
       <c r="F46" s="13"/>
       <c r="G46" s="10"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="21"/>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="21"/>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="10"/>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="10"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49" s="10"/>
@@ -1967,28 +1932,19 @@
       <c r="G52" s="10"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="10"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="9"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="10"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="9"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="10"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="9"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D56" s="8"/>
@@ -2120,30 +2076,15 @@
       <c r="E81" s="8"/>
       <c r="F81" s="9"/>
     </row>
-    <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="9"/>
-    </row>
-    <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="9"/>
-    </row>
-    <row r="84" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="9"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2421,57 +2362,57 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B31" s="2">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B32" s="2">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B33" s="2">
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2480,46 +2421,46 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B36" s="2">
         <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B37" s="2">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B38" s="2">
         <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2528,35 +2469,35 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2564,24 +2505,35 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B45" s="2">
         <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B46" s="2">
         <v>2</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>185</v>
+      </c>
+      <c r="B47" s="2">
+        <v>3</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2925,7 +2877,7 @@
         <v>163</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2956,7 +2908,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
@@ -2989,7 +2941,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>111</v>
@@ -3045,7 +2997,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>24</v>
@@ -3053,7 +3005,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>87</v>
@@ -3077,7 +3029,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>91</v>
@@ -3169,7 +3121,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>153</v>
@@ -3207,60 +3159,60 @@
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>140</v>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D799F2E2-E1FA-4D5C-A1C0-3E5C4FD8CA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F065D0B4-BFA9-44F9-8BA7-D9C3872F08B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2022022800</v>
+        <v>2020030801</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F065D0B4-BFA9-44F9-8BA7-D9C3872F08B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C540B774-327D-4E8D-AD5B-D2B953AA32F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="204">
   <si>
     <t>type</t>
   </si>
@@ -644,6 +644,18 @@
   </si>
   <si>
     <t>(["1B75", "MA01", "PJ20", "4A8Z", "JA40_0", "CA23", "CA20", "CA07", "CA20_Y", "CA40_Z", "CA41", "CA00", "1F23_0", "1F23_10", "MD81_4", "EB7Y", "1A40_Z", "GA34_3", "1A40_Z", "DA01", "1G04", "1A07_Z", "1A7Z", "BA00_Z", "BA2Z", "JA60_Z", "AAZ1_90", "1A36_0Z", "1B7Y", "1F03", "MG26", "1B1Z", "DA60", "GC02", "1A92", "1E90", "1C62_Z", "outro", "",].indexOf(data('diagno_secund'))&lt;0) &amp;&amp; data('diagno_secund')</t>
+  </si>
+  <si>
+    <t>data('febre')== 1 || data('temperatura')&gt;=37</t>
+  </si>
+  <si>
+    <t>O/A paciente foi enviada a fazer TDR</t>
+  </si>
+  <si>
+    <t>data('envio_tdr')==2</t>
+  </si>
+  <si>
+    <t>Motivo de não enviar o paciente a fazer TDR</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1286,7 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2020030801</v>
+        <v>2020040701</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1314,7 +1326,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z81"/>
+  <dimension ref="A1:Z87"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1434,128 +1446,164 @@
         <v>49</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>120</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="4"/>
+      <c r="P3" s="2"/>
+      <c r="R3"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="2" t="s">
         <v>195</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>87</v>
+      <c r="F4" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="4"/>
+      <c r="P4" s="2"/>
+      <c r="R4"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="D5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="4"/>
+      <c r="P5" s="2"/>
+      <c r="R5"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C6" s="9"/>
-      <c r="D6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K6" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="C6" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="4"/>
+      <c r="P6" s="2"/>
+      <c r="R6"/>
+    </row>
+    <row r="7" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="O7"/>
+      <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C8" s="9"/>
-      <c r="D8" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="L8" s="9"/>
+      <c r="B8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="4"/>
+      <c r="O8"/>
+      <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C12" s="9"/>
       <c r="D12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>158</v>
+      <c r="E12" s="9" t="s">
+        <v>155</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>162</v>
+        <v>94</v>
+      </c>
+      <c r="K12" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="E13" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="9"/>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C14" s="9"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="9"/>
+      <c r="D14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L14" s="9"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="C15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
@@ -1566,61 +1614,52 @@
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C17" s="9"/>
+      <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>164</v>
+      </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C18" s="8"/>
+    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="9"/>
       <c r="D18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>155</v>
+      <c r="E18" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>96</v>
+        <v>150</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C19" s="8"/>
-      <c r="E19" s="9"/>
+      <c r="B19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="E19" s="1"/>
       <c r="F19" s="9"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="E20" s="1"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
-      <c r="D21" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="E21" s="9"/>
-      <c r="F21" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="L21" s="9"/>
+      <c r="F21" s="9"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -1630,221 +1669,216 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="2:17" ht="63" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C24" s="8"/>
+      <c r="D24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="J25" s="21"/>
-      <c r="O25" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
+      <c r="E24" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C25" s="8"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C27" s="9"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C28" s="9"/>
-      <c r="D28" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>194</v>
-      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="E29" s="10"/>
+      <c r="C29" s="9"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C30" s="8"/>
-      <c r="D30" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C31" s="8"/>
+    <row r="30" spans="2:17" ht="63" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="9"/>
       <c r="D31" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="F31" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J31" s="21"/>
+      <c r="O31" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C32" s="8"/>
-      <c r="D32" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="B32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="9"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C33" s="9"/>
-      <c r="D33" s="9" t="s">
+      <c r="E33" s="1"/>
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C34" s="9"/>
+      <c r="D34" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C34" s="8"/>
-      <c r="D34" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>181</v>
+      <c r="E34" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="9"/>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C36" s="8"/>
+      <c r="D36" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C37" s="8"/>
+      <c r="D37" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C38" s="8"/>
+      <c r="D38" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C39" s="9"/>
+      <c r="D39" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C40" s="8"/>
+      <c r="D40" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="10"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="10"/>
-      <c r="J37" s="3"/>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="10"/>
-      <c r="J38" s="3"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C39" s="8"/>
-      <c r="D39" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="K39" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D40" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="10"/>
+      <c r="C41" s="8"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="10" t="s">
-        <v>51</v>
-      </c>
+      <c r="B42" s="10"/>
       <c r="C42" s="10"/>
       <c r="D42" s="12"/>
       <c r="E42" s="10"/>
@@ -1858,30 +1892,45 @@
       <c r="E43" s="10"/>
       <c r="F43" s="13"/>
       <c r="G43" s="10"/>
+      <c r="J43" s="3"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="22"/>
+      <c r="B44" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="10"/>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="22"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="F45" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K45" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="10"/>
+      <c r="D46" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="10"/>
@@ -1892,7 +1941,9 @@
       <c r="G47" s="10"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="10"/>
+      <c r="B48" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="C48" s="10"/>
       <c r="D48" s="12"/>
       <c r="E48" s="10"/>
@@ -1908,20 +1959,20 @@
       <c r="G49" s="10"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="10"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="22"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="10"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="22"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52" s="10"/>
@@ -1932,34 +1983,52 @@
       <c r="G52" s="10"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="10"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="10"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="10"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="10"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="9"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="10"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="10"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D59" s="8"/>
@@ -2076,15 +2145,45 @@
       <c r="E81" s="8"/>
       <c r="F81" s="9"/>
     </row>
+    <row r="82" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="9"/>
+    </row>
+    <row r="83" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="9"/>
+    </row>
+    <row r="84" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="9"/>
+    </row>
+    <row r="85" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="9"/>
+    </row>
+    <row r="86" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="9"/>
+    </row>
+    <row r="87" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="9"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C540B774-327D-4E8D-AD5B-D2B953AA32F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C69952D-CBE2-43D8-96D0-59DDCE607D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="205">
   <si>
     <t>type</t>
   </si>
@@ -656,6 +656,9 @@
   </si>
   <si>
     <t>Motivo de não enviar o paciente a fazer TDR</t>
+  </si>
+  <si>
+    <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
   </si>
 </sst>
 </file>
@@ -774,7 +777,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -825,6 +828,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1326,7 +1335,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z87"/>
+  <dimension ref="A1:Z90"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1529,450 +1538,472 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="R9"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="22"/>
+      <c r="F10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="4"/>
+      <c r="N10" t="s">
+        <v>126</v>
+      </c>
+      <c r="O10"/>
+      <c r="P10" s="2"/>
+      <c r="R10"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D11" s="2"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="4"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11" s="2"/>
+      <c r="R11"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D10" s="9" t="s">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D13" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C12" s="9"/>
-      <c r="D12" s="9" t="s">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C15" s="9"/>
+      <c r="D15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K12" s="2" t="b">
+      <c r="K15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C14" s="9"/>
-      <c r="D14" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="9"/>
-      <c r="D18" s="9" t="s">
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C20" s="9"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C24" s="8"/>
-      <c r="D24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C25" s="8"/>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>134</v>
-      </c>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C27" s="9"/>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C27" s="8"/>
       <c r="D27" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>155</v>
+      </c>
       <c r="F27" s="9" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="L27" s="9"/>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="9"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C28" s="8"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C29" s="9"/>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>134</v>
+      </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="2:17" ht="63" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C30" s="9"/>
+      <c r="D30" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="2:17" ht="63" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C33" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="9"/>
-      <c r="D31" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="J31" s="21"/>
-      <c r="O31" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C33" s="9"/>
-      <c r="E33" s="1"/>
+      <c r="E33" s="9"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C34" s="9"/>
       <c r="D34" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J34" s="21"/>
+      <c r="O34" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="9"/>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C36" s="9"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="9"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C37" s="9"/>
+      <c r="D37" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F37" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
-      <c r="D36" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C37" s="8"/>
-      <c r="D37" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="10"/>
-      <c r="F37" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C38" s="8"/>
-      <c r="D38" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C39" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="9"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C39" s="8"/>
       <c r="D39" s="9" t="s">
         <v>195</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C40" s="8"/>
       <c r="D40" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C41" s="8"/>
+      <c r="D41" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C42" s="9"/>
+      <c r="D42" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C43" s="8"/>
+      <c r="D43" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E43" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F43" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G43" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="8"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="10"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="10"/>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="10" t="s">
+      <c r="C44" s="8"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="10"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="10"/>
-      <c r="J44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C45" s="8"/>
-      <c r="D45" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="K45" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D46" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="10"/>
       <c r="C47" s="10"/>
       <c r="D47" s="12"/>
       <c r="E47" s="10"/>
       <c r="F47" s="13"/>
       <c r="G47" s="10"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="10" t="s">
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C48" s="8"/>
+      <c r="D48" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" s="10"/>
+      <c r="F48" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K48" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D49" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="10"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="10"/>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="10"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="22"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="22"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="10"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52" s="10"/>
@@ -1983,20 +2014,20 @@
       <c r="G52" s="10"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="10"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="24"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="10"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="24"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="10"/>
@@ -2031,19 +2062,28 @@
       <c r="G58" s="10"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="9"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="10"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="10"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="9"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="10"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D62" s="8"/>
@@ -2175,15 +2215,30 @@
       <c r="E87" s="8"/>
       <c r="F87" s="9"/>
     </row>
+    <row r="88" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="9"/>
+    </row>
+    <row r="89" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="9"/>
+    </row>
+    <row r="90" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="9"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:F54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>

--- a/app/config/tables/sentinela/forms/consulta/consulta.xlsx
+++ b/app/config/tables/sentinela/forms/consulta/consulta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C69952D-CBE2-43D8-96D0-59DDCE607D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4336DF-80A7-48A6-BE66-639CE48AF669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">survey!$D$1:$J$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -34,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="207">
   <si>
     <t>type</t>
   </si>
@@ -659,6 +667,12 @@
   </si>
   <si>
     <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
+  </si>
+  <si>
+    <t>else</t>
+  </si>
+  <si>
+    <t>data('envio_tdr')==1</t>
   </si>
 </sst>
 </file>
@@ -1507,7 +1521,7 @@
       <c r="P6" s="2"/>
       <c r="R6"/>
     </row>
-    <row r="7" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="D7" s="2" t="s">
         <v>4</v>
@@ -1519,8 +1533,7 @@
         <v>203</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>202</v>
       </c>
       <c r="O7"/>
@@ -1528,12 +1541,11 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="D8" s="2"/>
       <c r="F8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="4"/>
       <c r="O8"/>
       <c r="Q8" s="2"/>
     </row>
@@ -1548,9 +1560,8 @@
         <v>204</v>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="2" t="b">
-        <v>1</v>
+      <c r="K9" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="P9" s="2"/>
       <c r="R9"/>
@@ -1573,6 +1584,9 @@
       <c r="R10"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="23"/>
       <c r="F11" s="2"/>
